--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C00FE9-A348-4239-98B9-FD8CCD4ACD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD81D157-9A36-433D-9F92-B9799B94459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>40.56</v>
+        <v>40.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>126093.07920768001</v>
+        <v>125906.550984</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.27360139854124743</v>
+        <v>0.27247777422564884</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1399999999999999</v>
+        <v>1.1352800000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>83.238038787288104</v>
+        <v>82.893404100379342</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>38.618382143756079</v>
+        <v>37.988158443504474</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>48.378502156057706</v>
+        <v>48.26984033586767</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>60.004319038841288</v>
+        <v>59.757298545206034</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>67.843944259284271</v>
+        <v>67.564582418467111</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.8857178008784046E-2</v>
+        <v>5.8700323438171748E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.500986193293885E-3</v>
+        <v>3.5061728395061726E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11587737004926801</v>
+        <v>-0.11539759707853772</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5558255134693706</v>
+        <v>9.5162610429223751</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.136366805077377</v>
+        <v>6.1109600933931976</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.576314948497481</v>
+        <v>15.511823539237037</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.46632245675176</v>
+        <v>11.418847858509771</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>176.68 HKD</v>
+        <v>175.95 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.2208258089424035</v>
+        <v>-0.22082142598529775</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>90.74 HKD</v>
+        <v>90.37 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-2.6751397706007488E-2</v>
+        <v>-2.6744700303756166E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>64.99 HKD</v>
+        <v>64.72 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>8.8015310712306213E-2</v>
+        <v>8.8023696375720828E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>55.93 HKD</v>
+        <v>55.7 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.14395214407005177</v>
+        <v>0.14396144679045039</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>48.73 HKD</v>
+        <v>48.53 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.19781548386391307</v>
+        <v>0.19782573108072321</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>83.238038787288104</v>
+        <v>82.893404100379342</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>38.358543219948444</v>
+        <v>37.730270414373841</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>38.618382143756079</v>
+        <v>37.988158443504474</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>48.079733595545498</v>
+        <v>47.970719965497302</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>48.378502156057706</v>
+        <v>48.26984033586767</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>59.661729394958002</v>
+        <v>59.414708901322747</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>60.004319038841288</v>
+        <v>59.757298545206034</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>67.472986977025698</v>
+        <v>67.193625136208539</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>67.843944259284271</v>
+        <v>67.564582418467111</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9958,11 +9958,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.441286104891081</v>
+        <v>29.319388850141006</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.46632245675176</v>
+        <v>11.418847858509771</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-360.23999999999995</v>
+        <v>-358.74848000000003</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11587737004926801</v>
+        <v>-0.11539759707853772</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10385,11 +10385,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29707.185980391096</v>
+        <v>29584.187806858252</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5558255134693706</v>
+        <v>9.5162610429223768</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10402,11 +10402,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19076.759999999998</v>
+        <v>18997.775520000003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.136366805077377</v>
+        <v>6.1109600933931985</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10419,11 +10419,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48423.705980391096</v>
+        <v>48223.21484685826</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.57631494849748</v>
+        <v>15.511823539237039</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14006,16 +14006,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.500986193293885E-3</v>
+        <v>3.5061728395061726E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.500986193293885E-3</v>
+        <v>3.5061728395061726E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.8984220907297829E-3</v>
+        <v>1.9012345679012346E-3</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15170,18 +15170,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3872471400362811</v>
+        <v>2.3773630992459558</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.809039418225427</v>
+        <v>2.7974090094061079</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0403508509286472</v>
+        <v>2.0319030824932236</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15227,18 +15227,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.8857178008784046E-2</v>
+        <v>5.8700323438171748E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9256395912855692E-2</v>
+        <v>6.907182739274341E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.0304508158990312E-2</v>
+        <v>5.0170446481314163E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15284,11 +15284,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0036662371462794E-2</v>
+        <v>9.0170050019420522E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6378986417575001E-2</v>
+        <v>5.6462510841897337E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.576314948497481</v>
+        <v>15.511823539237037</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1399999999999999</v>
+        <v>1.1352800000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>192612.5148332325</v>
+        <v>191815.03143848441</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>57.518430380279121</v>
+        <v>57.280283896599371</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18592,23 +18592,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18623,23 +18623,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>49.117895213616194</v>
+        <v>48.914529893082637</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>49.788726818918555</v>
+        <v>49.58258402015953</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>50.459558424220937</v>
+        <v>50.250638147236444</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>51.801221634825708</v>
+        <v>51.5867464013903</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>54.149132253383996</v>
+        <v>53.924935846159464</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18654,23 +18654,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>49.076387121136179</v>
+        <v>48.873193658669727</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>50.384382259142264</v>
+        <v>50.175773237858799</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>51.717396757719044</v>
+        <v>51.503268588687092</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>54.458483836584804</v>
+        <v>54.233006605261409</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>59.496197570093024</v>
+        <v>59.249862436294052</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>49.037684937005622</v>
+        <v>48.834651715161179</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>50.950879740753592</v>
+        <v>50.739925221125212</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.937118778080858</v>
+        <v>52.717940531911971</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>57.134328291503074</v>
+        <v>56.897772125243527</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>65.229647560037421</v>
+        <v>64.959573931543233</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18716,23 +18716,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>49.001598984436328</v>
+        <v>48.798715171097264</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.489646576411928</v>
+        <v>51.276461373042928</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.119879525098362</v>
+        <v>53.895804234433051</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.828884945406791</v>
+        <v>59.581172369141612</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>71.37740279401045</v>
+        <v>71.081875301740524</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18747,23 +18747,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>48.967952408614146</v>
+        <v>48.765207903904802</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.002040210324736</v>
+        <v>51.786733517524105</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>55.266799037357771</v>
+        <v>55.037975097483802</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.542284652834297</v>
+        <v>62.28333764971029</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>77.96940141318899</v>
+        <v>77.646580733653693</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18778,23 +18778,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>48.936580309945448</v>
+        <v>48.733965696732348</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>52.489351638381684</v>
+        <v>52.272027305282428</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>56.37896341288203</v>
+        <v>56.14553472226028</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>65.274659183390668</v>
+        <v>65.004399190982255</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>85.037744920932838</v>
+        <v>84.685658819154952</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18810,23 +18810,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>48.907328935895386</v>
+        <v>48.704835433634493</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>52.952808660869422</v>
+        <v>52.733565453080566</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>57.45742583763284</v>
+        <v>57.219531934164756</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>68.026141228146756</v>
+        <v>67.744489134640759</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>92.616854509655909</v>
+        <v>92.233388234844014</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18841,23 +18841,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>48.880054927457095</v>
+        <v>48.677674349160959</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>53.393578975962647</v>
+        <v>53.17251082441306</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>58.503207582845725</v>
+        <v>58.260983776011493</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>70.796864406082932</v>
+        <v>70.503740546436703</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>100.74363868404424</v>
+        <v>100.32652467124716</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18873,23 +18873,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>48.854624616558922</v>
+        <v>48.652349328672827</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>53.812773121785568</v>
+        <v>53.5899693593866</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>59.517298972143088</v>
+        <v>59.27087647113563</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>73.58696327057811</v>
+        <v>73.282287422650825</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>109.45767299690819</v>
+        <v>109.00447982449995</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18905,23 +18905,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>48.830913370966222</v>
+        <v>48.628736255956611</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>54.211447274456326</v>
+        <v>53.986992861179637</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>60.50066031934054</v>
+        <v>60.250166357316616</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>76.396573315943897</v>
+        <v>76.080264696600693</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>118.80139277293947</v>
+        <v>118.30951332216029</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18937,23 +18937,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>48.73433990998074</v>
+        <v>48.532562642985035</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>55.930503544673947</v>
+        <v>55.698931635260919</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>64.988139018831902</v>
+        <v>64.719065320438148</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>90.742100254978439</v>
+        <v>90.366396120589414</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>176.67802582514463</v>
+        <v>175.94651680593878</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18969,23 +18969,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.666283146544664</v>
+        <v>48.464787658429152</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>57.268036364293195</v>
+        <v>57.030926599697182</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>68.835674135536408</v>
+        <v>68.550670291747181</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>105.59628354527925</v>
+        <v>105.15907788007425</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>258.71430526953952</v>
+        <v>257.64313726877441</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19001,23 +19001,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>48.618322526700155</v>
+        <v>48.417025612379092</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>58.308720182823507</v>
+        <v>58.067301622066566</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>72.134525777094538</v>
+        <v>71.835863530017463</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>120.97715886338734</v>
+        <v>120.47627097756701</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>374.99527722947317</v>
+        <v>373.44266520445296</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19033,23 +19033,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>48.584523960037039</v>
+        <v>48.383366983641103</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>59.118436994452232</v>
+        <v>58.873665921983985</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>74.962939767590342</v>
+        <v>74.65256689416664</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>136.90340138563079</v>
+        <v>136.33657326761312</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>539.81582408413328</v>
+        <v>537.58079716336397</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19096,7 +19096,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>176.67802582514463</v>
+        <v>175.94651680593878</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>90.742100254978439</v>
+        <v>90.366396120589414</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>64.988139018831902</v>
+        <v>64.719065320438148</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>55.930503544673947</v>
+        <v>55.698931635260919</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19208,7 +19208,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>48.73433990998074</v>
+        <v>48.532562642985035</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>90.742100254978439</v>
+        <v>90.366396120589414</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>64.988139018831902</v>
+        <v>64.719065320438148</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>55.930503544673947</v>
+        <v>55.698931635260919</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>67.874522397521716</v>
+        <v>67.593498059174095</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>176.67802582514463</v>
+        <v>175.94651680593878</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>48.73433990998074</v>
+        <v>48.532562642985035</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>40.56</v>
+        <v>40.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.27360139854124743</v>
+        <v>0.27247777422564884</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.1055109003969992</v>
+        <v>0.10551956605004355</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>83.238038787288104</v>
+        <v>82.893404100379342</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>57.518430380279121</v>
+        <v>57.280283896599371</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.18712976873833137</v>
+        <v>0.1871297687383314</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20030,23 +20030,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763701</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>38.358543219948444</v>
+        <v>37.730270414373841</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>38.618382143756079</v>
+        <v>37.988158443504474</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.53604887012722635</v>
+        <v>0.54172278414935271</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20055,23 +20055,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220924</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>48.079733595545498</v>
+        <v>47.970719965497302</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>48.378502156057706</v>
+        <v>48.26984033586767</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41879334423427161</v>
+        <v>0.41768780206666922</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20105,11 +20105,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>59.661729394958002</v>
+        <v>59.414708901322747</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>60.004319038841288</v>
+        <v>59.757298545206034</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27912382471936625</v>
+        <v>0.27910671308849566</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20130,11 +20130,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>67.472986977025698</v>
+        <v>67.193625136208539</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>67.843944259284271</v>
+        <v>67.564582418467111</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18494062032555691</v>
+        <v>0.18492209179092067</v>
       </c>
     </row>
   </sheetData>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>40.56</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20271,14 +20271,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>126093.07920768001</v>
+        <v>125906.550984</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.27360139854124743</v>
+        <v>0.27247777422564884</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20286,13 +20286,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1399999999999999</v>
+        <v>1.1352800000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>83.238038787288104</v>
+        <v>82.893404100379342</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20408,14 +20408,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>38.618382143756079</v>
+        <v>37.988158443504474</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20424,14 +20424,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>48.378502156057706</v>
+        <v>48.26984033586767</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>60.004319038841288</v>
+        <v>59.757298545206034</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>67.843944259284271</v>
+        <v>67.564582418467111</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20477,22 +20477,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20682,10 +20682,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20701,22 +20701,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.8857178008784046E-2</v>
+        <v>5.8700323438171748E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20760,7 +20760,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.500986193293885E-3</v>
+        <v>3.5061728395061726E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20851,22 +20851,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20874,13 +20874,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11587737004926801</v>
+        <v>-0.11539759707853772</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5558255134693706</v>
+        <v>9.5162610429223751</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.136366805077377</v>
+        <v>6.1109600933931976</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.576314948497481</v>
+        <v>15.511823539237037</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21029,33 +21029,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21118,23 +21118,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.46632245675176</v>
+        <v>11.418847858509771</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.957116526345246</v>
+        <v>61.700592324587049</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21178,13 +21178,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>176.68 HKD</v>
+        <v>175.95 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>90.74 HKD</v>
+        <v>90.37 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>64.99 HKD</v>
+        <v>64.72 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21296,7 +21296,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>55.93 HKD</v>
+        <v>55.7 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>48.73 HKD</v>
+        <v>48.53 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>83.238038787288104</v>
+        <v>82.893404100379342</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21348,13 +21348,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21367,22 +21367,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21443,19 +21443,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>38.358543219948444</v>
+        <v>37.730270414373841</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>38.618382143756079</v>
+        <v>37.988158443504474</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21464,19 +21464,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>48.079733595545498</v>
+        <v>47.970719965497302</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>48.378502156057706</v>
+        <v>48.26984033586767</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21508,11 +21508,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>59.661729394958002</v>
+        <v>59.414708901322747</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>60.004319038841288</v>
+        <v>59.757298545206034</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21529,11 +21529,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>67.472986977025698</v>
+        <v>67.193625136208539</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>67.843944259284271</v>
+        <v>67.564582418467111</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21551,13 +21551,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21565,13 +21565,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21608,22 +21608,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21647,15 +21647,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21670,12 +21667,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD81D157-9A36-433D-9F92-B9799B94459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394D5F9D-93E4-4CB5-8849-C3BDEA8E2460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5357,7 +5357,7 @@
         <v>538</v>
       </c>
       <c r="F3" s="429">
-        <v>46101</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.27247777422564884</v>
+        <v>0.20690450680305575</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>82.893404100379342</v>
+        <v>70.678756184465314</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>37.988158443504474</v>
+        <v>32.428464353420708</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>48.26984033586767</v>
+        <v>41.201178347491499</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>59.757298545206034</v>
+        <v>51.002322704458052</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>67.564582418467111</v>
+        <v>57.663354665305718</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
-        <v>9345.3202704130126</v>
+        <v>9207.3202704130126</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
-        <v>0</v>
+        <v>-650.63867420757288</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>71.994389576888963</v>
+        <v>72.408389576888965</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-2349.5886649974755</v>
+        <v>-2315.1921649974752</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>7660.3089609457529</v>
+        <v>7662.219886375362</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.8700323438171748E-2</v>
+        <v>5.776987959196641E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>6.7810323148000395E-2</v>
+        <v>6.8902478754484062E-2</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5940,11 +5940,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.11316501697760267</v>
+        <v>0.11150835231775919</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11898024034853405</v>
+        <v>0.11900324968543483</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5954,11 +5954,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.30032548054664621</v>
+        <v>0.30038355985579485</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.3813715405821454E-2</v>
+        <v>3.432051788351935E-2</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>26058.935070518506</v>
+        <v>25989.935070518506</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5162610429223751</v>
+        <v>9.4910634663450999</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.511823539237037</v>
+        <v>15.486625962659762</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6360,15 +6360,15 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (15yrs)</v>
+        <v>Snowball Scenario (10yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>175.95 HKD</v>
+        <v>87.99 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,21 +6376,21 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.22082142598529775</v>
+        <v>-6.8679003736245997E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (15yrs)</v>
+        <v>Optimistic (10yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>90.37 HKD</v>
+        <v>82.71 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,21 +6398,21 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-2.6744700303756166E-2</v>
+        <v>-4.9231373085065401E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (15yrs)</v>
+        <v>Base (10yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>64.72 HKD</v>
+        <v>69.04 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,21 +6420,21 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>8.8023696375720828E-2</v>
+        <v>9.8833378149183783E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (15yrs)</v>
+        <v>Pessimistic (10yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>55.7 HKD</v>
+        <v>58.15 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,13 +6442,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.14396144679045039</v>
+        <v>6.9479432488544338E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (15yrs)</v>
+        <v>Devil's advocate (10yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>48.53 HKD</v>
+        <v>44.77 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.19782573108072321</v>
+        <v>0.1671519111623998</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>82.893404100379342</v>
+        <v>70.678756184465314</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>37.730270414373841</v>
+        <v>32.170576324290074</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>37.988158443504474</v>
+        <v>32.428464353420708</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>47.970719965497302</v>
+        <v>40.902057977121132</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>48.26984033586767</v>
+        <v>41.201178347491499</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>59.414708901322747</v>
+        <v>50.659733060574766</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>59.757298545206034</v>
+        <v>51.002322704458052</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>67.193625136208539</v>
+        <v>57.292397383047152</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>67.564582418467111</v>
+        <v>57.663354665305718</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6942,11 +6942,21 @@
       <c r="D4" s="287">
         <v>28401</v>
       </c>
-      <c r="E4" s="287"/>
-      <c r="F4" s="287"/>
-      <c r="G4" s="287"/>
-      <c r="H4" s="287"/>
-      <c r="I4" s="287"/>
+      <c r="E4" s="287">
+        <v>27752</v>
+      </c>
+      <c r="F4" s="287">
+        <v>28339</v>
+      </c>
+      <c r="G4" s="287">
+        <v>31244</v>
+      </c>
+      <c r="H4" s="287">
+        <v>29153</v>
+      </c>
+      <c r="I4" s="287">
+        <v>25434</v>
+      </c>
       <c r="J4" s="287"/>
       <c r="K4" s="287"/>
       <c r="L4" s="287"/>
@@ -6962,11 +6972,21 @@
       <c r="D5" s="287">
         <v>16376</v>
       </c>
-      <c r="E5" s="287"/>
-      <c r="F5" s="287"/>
-      <c r="G5" s="287"/>
-      <c r="H5" s="287"/>
-      <c r="I5" s="287"/>
+      <c r="E5" s="287">
+        <v>17957</v>
+      </c>
+      <c r="F5" s="287">
+        <v>19566</v>
+      </c>
+      <c r="G5" s="287">
+        <v>21840</v>
+      </c>
+      <c r="H5" s="287">
+        <v>19851</v>
+      </c>
+      <c r="I5" s="287">
+        <v>16761</v>
+      </c>
       <c r="J5" s="287"/>
       <c r="K5" s="287"/>
       <c r="L5" s="287"/>
@@ -6984,11 +7004,26 @@
         <f>3811+D7</f>
         <v>4676</v>
       </c>
-      <c r="E6" s="287"/>
-      <c r="F6" s="287"/>
-      <c r="G6" s="287"/>
-      <c r="H6" s="287"/>
-      <c r="I6" s="287"/>
+      <c r="E6" s="287">
+        <f>4121+E7</f>
+        <v>5018</v>
+      </c>
+      <c r="F6" s="287">
+        <f>4413+F7</f>
+        <v>5557</v>
+      </c>
+      <c r="G6" s="287">
+        <f>4009+G7</f>
+        <v>6687</v>
+      </c>
+      <c r="H6" s="287">
+        <f>3101+H7</f>
+        <v>5576</v>
+      </c>
+      <c r="I6" s="287">
+        <f>2703+I7</f>
+        <v>4744</v>
+      </c>
       <c r="J6" s="287"/>
       <c r="K6" s="287"/>
       <c r="L6" s="287"/>
@@ -7004,11 +7039,21 @@
       <c r="D7" s="288">
         <v>865</v>
       </c>
-      <c r="E7" s="288"/>
-      <c r="F7" s="288"/>
-      <c r="G7" s="288"/>
-      <c r="H7" s="288"/>
-      <c r="I7" s="288"/>
+      <c r="E7" s="288">
+        <v>897</v>
+      </c>
+      <c r="F7" s="288">
+        <v>1144</v>
+      </c>
+      <c r="G7" s="288">
+        <v>2678</v>
+      </c>
+      <c r="H7" s="288">
+        <v>2475</v>
+      </c>
+      <c r="I7" s="288">
+        <v>2041</v>
+      </c>
       <c r="J7" s="288"/>
       <c r="K7" s="288"/>
       <c r="L7" s="288"/>
@@ -7088,11 +7133,21 @@
       <c r="D12" s="287">
         <v>94</v>
       </c>
-      <c r="E12" s="287"/>
-      <c r="F12" s="287"/>
-      <c r="G12" s="287"/>
-      <c r="H12" s="287"/>
-      <c r="I12" s="287"/>
+      <c r="E12" s="287">
+        <v>141</v>
+      </c>
+      <c r="F12" s="287">
+        <v>108</v>
+      </c>
+      <c r="G12" s="287">
+        <v>121</v>
+      </c>
+      <c r="H12" s="287">
+        <v>97</v>
+      </c>
+      <c r="I12" s="287">
+        <v>64</v>
+      </c>
       <c r="J12" s="287"/>
       <c r="K12" s="287"/>
       <c r="L12" s="287"/>
@@ -7108,11 +7163,21 @@
       <c r="D13" s="287">
         <v>1196</v>
       </c>
-      <c r="E13" s="287"/>
-      <c r="F13" s="287"/>
-      <c r="G13" s="287"/>
-      <c r="H13" s="287"/>
-      <c r="I13" s="287"/>
+      <c r="E13" s="287">
+        <v>1052</v>
+      </c>
+      <c r="F13" s="287">
+        <v>711</v>
+      </c>
+      <c r="G13" s="287">
+        <v>530</v>
+      </c>
+      <c r="H13" s="287">
+        <v>622</v>
+      </c>
+      <c r="I13" s="287">
+        <v>615</v>
+      </c>
       <c r="J13" s="287"/>
       <c r="K13" s="287"/>
       <c r="L13" s="287"/>
@@ -7128,11 +7193,21 @@
       <c r="D14" s="287">
         <v>1603</v>
       </c>
-      <c r="E14" s="287"/>
-      <c r="F14" s="287"/>
-      <c r="G14" s="287"/>
-      <c r="H14" s="287"/>
-      <c r="I14" s="287"/>
+      <c r="E14" s="287">
+        <v>825</v>
+      </c>
+      <c r="F14" s="287">
+        <v>534</v>
+      </c>
+      <c r="G14" s="287">
+        <v>417</v>
+      </c>
+      <c r="H14" s="287">
+        <v>637</v>
+      </c>
+      <c r="I14" s="287">
+        <v>564</v>
+      </c>
       <c r="J14" s="287"/>
       <c r="K14" s="287"/>
       <c r="L14" s="287"/>
@@ -7148,11 +7223,21 @@
       <c r="D15" s="289">
         <v>7109</v>
       </c>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="289"/>
-      <c r="I15" s="289"/>
+      <c r="E15" s="289">
+        <v>5220</v>
+      </c>
+      <c r="F15" s="289">
+        <v>3839</v>
+      </c>
+      <c r="G15" s="289">
+        <v>3215</v>
+      </c>
+      <c r="H15" s="289">
+        <v>4176</v>
+      </c>
+      <c r="I15" s="289">
+        <v>3977</v>
+      </c>
       <c r="J15" s="289"/>
       <c r="K15" s="289"/>
       <c r="L15" s="289"/>
@@ -7168,11 +7253,21 @@
       <c r="D16" s="287">
         <v>465</v>
       </c>
-      <c r="E16" s="287"/>
-      <c r="F16" s="287"/>
-      <c r="G16" s="287"/>
-      <c r="H16" s="287"/>
-      <c r="I16" s="287"/>
+      <c r="E16" s="287">
+        <v>300</v>
+      </c>
+      <c r="F16" s="287">
+        <v>162</v>
+      </c>
+      <c r="G16" s="287">
+        <v>186</v>
+      </c>
+      <c r="H16" s="287">
+        <v>21</v>
+      </c>
+      <c r="I16" s="287">
+        <v>5</v>
+      </c>
       <c r="J16" s="287"/>
       <c r="K16" s="287"/>
       <c r="L16" s="287"/>
@@ -7190,11 +7285,21 @@
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
-      <c r="E19" s="287"/>
-      <c r="F19" s="287"/>
-      <c r="G19" s="287"/>
-      <c r="H19" s="287"/>
-      <c r="I19" s="287"/>
+      <c r="E19" s="287">
+        <v>1004</v>
+      </c>
+      <c r="F19" s="287">
+        <v>1160</v>
+      </c>
+      <c r="G19" s="287">
+        <v>1001</v>
+      </c>
+      <c r="H19" s="287">
+        <v>824</v>
+      </c>
+      <c r="I19" s="287">
+        <v>583</v>
+      </c>
       <c r="J19" s="287"/>
       <c r="K19" s="287"/>
       <c r="L19" s="287"/>
@@ -7206,11 +7311,21 @@
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
-      <c r="E20" s="287"/>
-      <c r="F20" s="287"/>
-      <c r="G20" s="287"/>
-      <c r="H20" s="287"/>
-      <c r="I20" s="287"/>
+      <c r="E20" s="287">
+        <v>1164</v>
+      </c>
+      <c r="F20" s="287">
+        <v>1053</v>
+      </c>
+      <c r="G20" s="287">
+        <v>2758</v>
+      </c>
+      <c r="H20" s="287">
+        <v>501</v>
+      </c>
+      <c r="I20" s="287">
+        <v>286</v>
+      </c>
       <c r="J20" s="287"/>
       <c r="K20" s="287"/>
       <c r="L20" s="287"/>
@@ -7222,11 +7337,21 @@
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
-      <c r="E21" s="287"/>
-      <c r="F21" s="287"/>
-      <c r="G21" s="287"/>
-      <c r="H21" s="287"/>
-      <c r="I21" s="287"/>
+      <c r="E21" s="287">
+        <v>-786</v>
+      </c>
+      <c r="F21" s="287">
+        <v>-875</v>
+      </c>
+      <c r="G21" s="287">
+        <v>-579</v>
+      </c>
+      <c r="H21" s="287">
+        <v>505</v>
+      </c>
+      <c r="I21" s="287">
+        <v>-1148</v>
+      </c>
       <c r="J21" s="287"/>
       <c r="K21" s="287"/>
       <c r="L21" s="287"/>
@@ -7237,16 +7362,26 @@
         <v>286</v>
       </c>
       <c r="C22" s="287">
-        <v>859017</v>
+        <v>10231</v>
       </c>
       <c r="D22" s="287">
-        <v>790543</v>
-      </c>
-      <c r="E22" s="287"/>
-      <c r="F22" s="287"/>
-      <c r="G22" s="287"/>
-      <c r="H22" s="287"/>
-      <c r="I22" s="287"/>
+        <v>10275</v>
+      </c>
+      <c r="E22" s="287">
+        <v>7337</v>
+      </c>
+      <c r="F22" s="287">
+        <v>7481</v>
+      </c>
+      <c r="G22" s="287">
+        <v>5239</v>
+      </c>
+      <c r="H22" s="287">
+        <v>4885</v>
+      </c>
+      <c r="I22" s="287">
+        <v>6200</v>
+      </c>
       <c r="J22" s="287"/>
       <c r="K22" s="287"/>
       <c r="L22" s="287"/>
@@ -7257,16 +7392,26 @@
         <v>288</v>
       </c>
       <c r="C23" s="287">
-        <v>65893</v>
+        <v>-10227</v>
       </c>
       <c r="D23" s="287">
-        <v>-294294</v>
-      </c>
-      <c r="E23" s="287"/>
-      <c r="F23" s="287"/>
-      <c r="G23" s="287"/>
-      <c r="H23" s="287"/>
-      <c r="I23" s="287"/>
+        <v>-6818</v>
+      </c>
+      <c r="E23" s="287">
+        <v>-1863</v>
+      </c>
+      <c r="F23" s="287">
+        <v>-1446</v>
+      </c>
+      <c r="G23" s="287">
+        <v>-5999</v>
+      </c>
+      <c r="H23" s="287">
+        <v>-14206</v>
+      </c>
+      <c r="I23" s="287">
+        <v>-8102</v>
+      </c>
       <c r="J23" s="287"/>
       <c r="K23" s="287"/>
       <c r="L23" s="287"/>
@@ -7277,16 +7422,26 @@
         <v>287</v>
       </c>
       <c r="C24" s="287">
-        <v>-298236</v>
+        <v>-4649</v>
       </c>
       <c r="D24" s="287">
-        <v>-403493</v>
-      </c>
-      <c r="E24" s="287"/>
-      <c r="F24" s="287"/>
-      <c r="G24" s="287"/>
-      <c r="H24" s="287"/>
-      <c r="I24" s="287"/>
+        <v>-3830</v>
+      </c>
+      <c r="E24" s="287">
+        <v>-1538</v>
+      </c>
+      <c r="F24" s="287">
+        <v>-3419</v>
+      </c>
+      <c r="G24" s="287">
+        <v>-3710</v>
+      </c>
+      <c r="H24" s="287">
+        <v>-5292</v>
+      </c>
+      <c r="I24" s="287">
+        <v>-31</v>
+      </c>
       <c r="J24" s="287"/>
       <c r="K24" s="287"/>
       <c r="L24" s="287"/>
@@ -7332,13 +7487,23 @@
         <v>3903</v>
       </c>
       <c r="D28" s="287">
-        <v>715301</v>
-      </c>
-      <c r="E28" s="287"/>
-      <c r="F28" s="287"/>
-      <c r="G28" s="287"/>
-      <c r="H28" s="287"/>
-      <c r="I28" s="287"/>
+        <v>3508</v>
+      </c>
+      <c r="E28" s="287">
+        <v>2918</v>
+      </c>
+      <c r="F28" s="287">
+        <v>2670</v>
+      </c>
+      <c r="G28" s="287">
+        <v>3610</v>
+      </c>
+      <c r="H28" s="287">
+        <v>2800</v>
+      </c>
+      <c r="I28" s="287">
+        <v>2198</v>
+      </c>
       <c r="J28" s="287"/>
       <c r="K28" s="287"/>
       <c r="L28" s="287"/>
@@ -7353,13 +7518,23 @@
         <v>41</v>
       </c>
       <c r="D29" s="287">
-        <v>23</v>
-      </c>
-      <c r="E29" s="287"/>
-      <c r="F29" s="287"/>
-      <c r="G29" s="287"/>
-      <c r="H29" s="287"/>
-      <c r="I29" s="287"/>
+        <v>2</v>
+      </c>
+      <c r="E29" s="287">
+        <v>8</v>
+      </c>
+      <c r="F29" s="287">
+        <v>8</v>
+      </c>
+      <c r="G29" s="287">
+        <v>24</v>
+      </c>
+      <c r="H29" s="287">
+        <v>18</v>
+      </c>
+      <c r="I29" s="287">
+        <v>26</v>
+      </c>
       <c r="J29" s="287"/>
       <c r="K29" s="287"/>
       <c r="L29" s="287"/>
@@ -7374,13 +7549,23 @@
         <v>19472</v>
       </c>
       <c r="D30" s="289">
-        <v>2524058</v>
-      </c>
-      <c r="E30" s="289"/>
-      <c r="F30" s="289"/>
-      <c r="G30" s="289"/>
-      <c r="H30" s="289"/>
-      <c r="I30" s="289"/>
+        <v>20718</v>
+      </c>
+      <c r="E30" s="289">
+        <v>18334</v>
+      </c>
+      <c r="F30" s="289">
+        <v>17882</v>
+      </c>
+      <c r="G30" s="289">
+        <v>16199</v>
+      </c>
+      <c r="H30" s="289">
+        <v>15542</v>
+      </c>
+      <c r="I30" s="289">
+        <v>9000</v>
+      </c>
       <c r="J30" s="289"/>
       <c r="K30" s="289"/>
       <c r="L30" s="289"/>
@@ -7395,13 +7580,23 @@
         <v>83050</v>
       </c>
       <c r="D31" s="289">
-        <v>3112637</v>
-      </c>
-      <c r="E31" s="289"/>
-      <c r="F31" s="289"/>
-      <c r="G31" s="289"/>
-      <c r="H31" s="289"/>
-      <c r="I31" s="289"/>
+        <v>69726</v>
+      </c>
+      <c r="E31" s="289">
+        <v>57202</v>
+      </c>
+      <c r="F31" s="289">
+        <v>49127</v>
+      </c>
+      <c r="G31" s="289">
+        <v>51055</v>
+      </c>
+      <c r="H31" s="289">
+        <v>52731</v>
+      </c>
+      <c r="I31" s="289">
+        <v>43678</v>
+      </c>
       <c r="J31" s="289"/>
       <c r="K31" s="289"/>
       <c r="L31" s="289"/>
@@ -7418,11 +7613,21 @@
       <c r="D32" s="287">
         <v>1863</v>
       </c>
-      <c r="E32" s="287"/>
-      <c r="F32" s="287"/>
-      <c r="G32" s="287"/>
-      <c r="H32" s="287"/>
-      <c r="I32" s="287"/>
+      <c r="E32" s="287">
+        <v>1295</v>
+      </c>
+      <c r="F32" s="287">
+        <v>1028</v>
+      </c>
+      <c r="G32" s="287">
+        <v>738</v>
+      </c>
+      <c r="H32" s="287">
+        <v>486</v>
+      </c>
+      <c r="I32" s="287">
+        <v>88</v>
+      </c>
       <c r="J32" s="287"/>
       <c r="K32" s="287"/>
       <c r="L32" s="287"/>
@@ -7461,25 +7666,25 @@
         <f t="shared" si="1"/>
         <v>28401</v>
       </c>
-      <c r="E36" s="270" t="str">
+      <c r="E36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="270" t="str">
+        <v>27752</v>
+      </c>
+      <c r="F36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G36" s="270" t="str">
+        <v>28339</v>
+      </c>
+      <c r="G36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H36" s="270" t="str">
+        <v>31244</v>
+      </c>
+      <c r="H36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I36" s="270" t="str">
+        <v>29153</v>
+      </c>
+      <c r="I36" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>25434</v>
       </c>
       <c r="J36" s="270" t="str">
         <f t="shared" si="1"/>
@@ -7510,25 +7715,25 @@
         <f t="shared" si="2"/>
         <v>-16376</v>
       </c>
-      <c r="E37" s="270" t="str">
+      <c r="E37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F37" s="270" t="str">
+        <v>-17957</v>
+      </c>
+      <c r="F37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G37" s="270" t="str">
+        <v>-19566</v>
+      </c>
+      <c r="G37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H37" s="270" t="str">
+        <v>-21840</v>
+      </c>
+      <c r="H37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I37" s="270" t="str">
+        <v>-19851</v>
+      </c>
+      <c r="I37" s="270">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-16761</v>
       </c>
       <c r="J37" s="270" t="str">
         <f t="shared" si="2"/>
@@ -7559,25 +7764,25 @@
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>12025</v>
       </c>
-      <c r="E38" s="267" t="str">
+      <c r="E38" s="267">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="267" t="str">
+        <v>9795</v>
+      </c>
+      <c r="F38" s="267">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="267" t="str">
+        <v>8773</v>
+      </c>
+      <c r="G38" s="267">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="267" t="str">
+        <v>9404</v>
+      </c>
+      <c r="H38" s="267">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="267" t="str">
+        <v>9302</v>
+      </c>
+      <c r="I38" s="267">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
-        <v/>
+        <v>8673</v>
       </c>
       <c r="J38" s="267" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
@@ -7608,25 +7813,25 @@
         <f t="shared" si="13"/>
         <v>-4676</v>
       </c>
-      <c r="E39" s="270" t="str">
+      <c r="E39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="F39" s="270" t="str">
+        <v>-5018</v>
+      </c>
+      <c r="F39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G39" s="270" t="str">
+        <v>-5557</v>
+      </c>
+      <c r="G39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H39" s="270" t="str">
+        <v>-6687</v>
+      </c>
+      <c r="H39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="I39" s="270" t="str">
+        <v>-5576</v>
+      </c>
+      <c r="I39" s="270">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-4744</v>
       </c>
       <c r="J39" s="270" t="str">
         <f t="shared" si="13"/>
@@ -7657,25 +7862,25 @@
         <f t="shared" si="14"/>
         <v>-865</v>
       </c>
-      <c r="E40" s="282" t="str">
+      <c r="E40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F40" s="282" t="str">
+        <v>-897</v>
+      </c>
+      <c r="F40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G40" s="282" t="str">
+        <v>-1144</v>
+      </c>
+      <c r="G40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="H40" s="282" t="str">
+        <v>-2678</v>
+      </c>
+      <c r="H40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I40" s="282" t="str">
+        <v>-2475</v>
+      </c>
+      <c r="I40" s="282">
         <f t="shared" si="14"/>
-        <v/>
+        <v>-2041</v>
       </c>
       <c r="J40" s="282" t="str">
         <f t="shared" si="14"/>
@@ -7706,25 +7911,25 @@
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-3811</v>
       </c>
-      <c r="E41" s="282" t="str">
+      <c r="E41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="F41" s="282" t="str">
+        <v>-4121</v>
+      </c>
+      <c r="F41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G41" s="282" t="str">
+        <v>-4413</v>
+      </c>
+      <c r="G41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H41" s="282" t="str">
+        <v>-4009</v>
+      </c>
+      <c r="H41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I41" s="282" t="str">
+        <v>-3101</v>
+      </c>
+      <c r="I41" s="282">
         <f t="shared" si="15"/>
-        <v/>
+        <v>-2703</v>
       </c>
       <c r="J41" s="282" t="str">
         <f t="shared" si="15"/>
@@ -7755,25 +7960,25 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="270" t="str">
+      <c r="E42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F42" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="F42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="G42" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="H42" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="H42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="I42" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="I42" s="270">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J42" s="270" t="str">
         <f t="shared" si="16"/>
@@ -7804,25 +8009,25 @@
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>7349</v>
       </c>
-      <c r="E43" s="271" t="str">
+      <c r="E43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F43" s="271" t="str">
+        <v>4777</v>
+      </c>
+      <c r="F43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="G43" s="271" t="str">
+        <v>3216</v>
+      </c>
+      <c r="G43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="H43" s="271" t="str">
+        <v>2717</v>
+      </c>
+      <c r="H43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="I43" s="271" t="str">
+        <v>3726</v>
+      </c>
+      <c r="I43" s="271">
         <f t="shared" si="17"/>
-        <v/>
+        <v>3929</v>
       </c>
       <c r="J43" s="271" t="str">
         <f t="shared" si="17"/>
@@ -7853,25 +8058,25 @@
         <f t="shared" si="18"/>
         <v>261</v>
       </c>
-      <c r="E44" s="290" t="str">
+      <c r="E44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="F44" s="290" t="str">
+        <v>357</v>
+      </c>
+      <c r="F44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G44" s="290" t="str">
+        <v>554</v>
+      </c>
+      <c r="G44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H44" s="290" t="str">
+        <v>506</v>
+      </c>
+      <c r="H44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="I44" s="290" t="str">
+        <v>562</v>
+      </c>
+      <c r="I44" s="290">
         <f t="shared" si="18"/>
-        <v/>
+        <v>61</v>
       </c>
       <c r="J44" s="290" t="str">
         <f t="shared" si="18"/>
@@ -7902,25 +8107,25 @@
         <f t="shared" si="19"/>
         <v>1102</v>
       </c>
-      <c r="E45" s="285" t="str">
+      <c r="E45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="F45" s="285" t="str">
+        <v>911</v>
+      </c>
+      <c r="F45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="G45" s="285" t="str">
+        <v>603</v>
+      </c>
+      <c r="G45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="H45" s="285" t="str">
+        <v>409</v>
+      </c>
+      <c r="H45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I45" s="285" t="str">
+        <v>525</v>
+      </c>
+      <c r="I45" s="285">
         <f t="shared" si="19"/>
-        <v/>
+        <v>551</v>
       </c>
       <c r="J45" s="285" t="str">
         <f t="shared" si="19"/>
@@ -7951,25 +8156,25 @@
         <f t="shared" ref="D46:M46" si="20">IF(D$4="","",-D14)</f>
         <v>-1603</v>
       </c>
-      <c r="E46" s="270" t="str">
+      <c r="E46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="F46" s="270" t="str">
+        <v>-825</v>
+      </c>
+      <c r="F46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="G46" s="270" t="str">
+        <v>-534</v>
+      </c>
+      <c r="G46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="H46" s="270" t="str">
+        <v>-417</v>
+      </c>
+      <c r="H46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="I46" s="270" t="str">
+        <v>-637</v>
+      </c>
+      <c r="I46" s="270">
         <f t="shared" si="20"/>
-        <v/>
+        <v>-564</v>
       </c>
       <c r="J46" s="270" t="str">
         <f t="shared" si="20"/>
@@ -8000,25 +8205,25 @@
         <f t="shared" si="21"/>
         <v>7109</v>
       </c>
-      <c r="E47" s="271" t="str">
+      <c r="E47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="F47" s="271" t="str">
+        <v>5220</v>
+      </c>
+      <c r="F47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="G47" s="271" t="str">
+        <v>3839</v>
+      </c>
+      <c r="G47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="H47" s="271" t="str">
+        <v>3215</v>
+      </c>
+      <c r="H47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="I47" s="271" t="str">
+        <v>4176</v>
+      </c>
+      <c r="I47" s="271">
         <f t="shared" si="21"/>
-        <v/>
+        <v>3977</v>
       </c>
       <c r="J47" s="271" t="str">
         <f t="shared" si="21"/>
@@ -8049,25 +8254,25 @@
         <f t="shared" si="22"/>
         <v>-465</v>
       </c>
-      <c r="E48" s="270" t="str">
+      <c r="E48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="F48" s="270" t="str">
+        <v>-300</v>
+      </c>
+      <c r="F48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="G48" s="270" t="str">
+        <v>-162</v>
+      </c>
+      <c r="G48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="H48" s="270" t="str">
+        <v>-186</v>
+      </c>
+      <c r="H48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="I48" s="270" t="str">
+        <v>-21</v>
+      </c>
+      <c r="I48" s="270">
         <f t="shared" si="22"/>
-        <v/>
+        <v>-5</v>
       </c>
       <c r="J48" s="270" t="str">
         <f t="shared" si="22"/>
@@ -8103,25 +8308,25 @@
         <f t="shared" si="23"/>
         <v>-94</v>
       </c>
-      <c r="E51" s="270" t="str">
+      <c r="E51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="F51" s="270" t="str">
+        <v>-141</v>
+      </c>
+      <c r="F51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="G51" s="270" t="str">
+        <v>-108</v>
+      </c>
+      <c r="G51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="H51" s="270" t="str">
+        <v>-121</v>
+      </c>
+      <c r="H51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I51" s="270" t="str">
+        <v>-97</v>
+      </c>
+      <c r="I51" s="270">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-64</v>
       </c>
       <c r="J51" s="270" t="str">
         <f t="shared" si="23"/>
@@ -8152,25 +8357,25 @@
         <f t="shared" ref="D52:M52" si="24">IF(D$4="","",D13)</f>
         <v>1196</v>
       </c>
-      <c r="E52" s="270" t="str">
+      <c r="E52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="F52" s="270" t="str">
+        <v>1052</v>
+      </c>
+      <c r="F52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="G52" s="270" t="str">
+        <v>711</v>
+      </c>
+      <c r="G52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="H52" s="270" t="str">
+        <v>530</v>
+      </c>
+      <c r="H52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="I52" s="270" t="str">
+        <v>622</v>
+      </c>
+      <c r="I52" s="270">
         <f t="shared" si="24"/>
-        <v/>
+        <v>615</v>
       </c>
       <c r="J52" s="270" t="str">
         <f t="shared" si="24"/>
@@ -8206,25 +8411,25 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="E55" s="285" t="str">
+      <c r="E55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="F55" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="F55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="G55" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="H55" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="H55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="I55" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="I55" s="285">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J55" s="285" t="str">
         <f t="shared" si="25"/>
@@ -8255,25 +8460,25 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="285" t="str">
+      <c r="E56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="F56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="F56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="G56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="H56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="H56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="I56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="I56" s="285">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J56" s="285" t="str">
         <f t="shared" si="26"/>
@@ -8304,25 +8509,25 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="E57" s="285" t="str">
+      <c r="E57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="F57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="F57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="G57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="H57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="H57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="I57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="I57" s="285">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J57" s="285" t="str">
         <f t="shared" si="27"/>
@@ -8353,25 +8558,25 @@
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>261</v>
       </c>
-      <c r="E58" s="285" t="str">
+      <c r="E58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="F58" s="285" t="str">
+        <v>357</v>
+      </c>
+      <c r="F58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="G58" s="285" t="str">
+        <v>554</v>
+      </c>
+      <c r="G58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="H58" s="285" t="str">
+        <v>506</v>
+      </c>
+      <c r="H58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="I58" s="285" t="str">
+        <v>562</v>
+      </c>
+      <c r="I58" s="285">
         <f t="shared" si="28"/>
-        <v/>
+        <v>61</v>
       </c>
       <c r="J58" s="285" t="str">
         <f t="shared" si="28"/>
@@ -8408,25 +8613,25 @@
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="270" t="str">
+      <c r="E61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="F61" s="270" t="str">
+        <v>-1004</v>
+      </c>
+      <c r="F61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="G61" s="270" t="str">
+        <v>-1160</v>
+      </c>
+      <c r="G61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="H61" s="270" t="str">
+        <v>-1001</v>
+      </c>
+      <c r="H61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="I61" s="270" t="str">
+        <v>-824</v>
+      </c>
+      <c r="I61" s="270">
         <f t="shared" si="29"/>
-        <v/>
+        <v>-583</v>
       </c>
       <c r="J61" s="270" t="str">
         <f t="shared" si="29"/>
@@ -8457,25 +8662,25 @@
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="270" t="str">
+      <c r="E62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="F62" s="270" t="str">
+        <v>-1164</v>
+      </c>
+      <c r="F62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="G62" s="270" t="str">
+        <v>-1053</v>
+      </c>
+      <c r="G62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="H62" s="270" t="str">
+        <v>-2758</v>
+      </c>
+      <c r="H62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="I62" s="270" t="str">
+        <v>-501</v>
+      </c>
+      <c r="I62" s="270">
         <f t="shared" si="30"/>
-        <v/>
+        <v>-286</v>
       </c>
       <c r="J62" s="270" t="str">
         <f t="shared" si="30"/>
@@ -8506,25 +8711,25 @@
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="270" t="str">
+      <c r="E63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="F63" s="270" t="str">
+        <v>786</v>
+      </c>
+      <c r="F63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="G63" s="270" t="str">
+        <v>875</v>
+      </c>
+      <c r="G63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H63" s="270" t="str">
+        <v>579</v>
+      </c>
+      <c r="H63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="I63" s="270" t="str">
+        <v>-505</v>
+      </c>
+      <c r="I63" s="270">
         <f t="shared" si="31"/>
-        <v/>
+        <v>1148</v>
       </c>
       <c r="J63" s="270" t="str">
         <f t="shared" si="31"/>
@@ -8549,31 +8754,31 @@
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
-        <v>626674</v>
+        <v>-4645</v>
       </c>
       <c r="D64" s="270">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
-        <v>92756</v>
-      </c>
-      <c r="E64" s="270" t="str">
+        <v>-373</v>
+      </c>
+      <c r="E64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="F64" s="270" t="str">
+        <v>3936</v>
+      </c>
+      <c r="F64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="G64" s="270" t="str">
+        <v>2616</v>
+      </c>
+      <c r="G64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="H64" s="270" t="str">
+        <v>-4470</v>
+      </c>
+      <c r="H64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="270" t="str">
+        <v>-14613</v>
+      </c>
+      <c r="I64" s="270">
         <f t="shared" si="32"/>
-        <v/>
+        <v>-1933</v>
       </c>
       <c r="J64" s="270" t="str">
         <f t="shared" si="32"/>
@@ -8604,25 +8809,25 @@
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="E65" s="70" t="str">
+      <c r="E65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="F65" s="70" t="str">
+        <v>0</v>
+      </c>
+      <c r="F65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="G65" s="70" t="str">
+        <v>0</v>
+      </c>
+      <c r="G65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H65" s="70" t="str">
+        <v>0</v>
+      </c>
+      <c r="H65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I65" s="70" t="str">
+        <v>0</v>
+      </c>
+      <c r="I65" s="70">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J65" s="70" t="str">
         <f t="shared" si="33"/>
@@ -8655,25 +8860,25 @@
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>0.15848033519946481</v>
       </c>
-      <c r="D68" s="89" t="str">
+      <c r="D68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="E68" s="89" t="str">
+        <v>2.3385701931392333E-2</v>
+      </c>
+      <c r="E68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="F68" s="89" t="str">
+        <v>-2.071350435795194E-2</v>
+      </c>
+      <c r="F68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="G68" s="89" t="str">
+        <v>-9.2977851747535478E-2</v>
+      </c>
+      <c r="G68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="89" t="str">
+        <v>7.1725036874421111E-2</v>
+      </c>
+      <c r="H68" s="89">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0.14622159314303684</v>
       </c>
       <c r="I68" s="89" t="str">
         <f t="shared" si="34"/>
@@ -8704,25 +8909,25 @@
         <f>IF(D$36="","",C38/D38-1)</f>
         <v>0.20873180873180863</v>
       </c>
-      <c r="D69" s="89" t="str">
+      <c r="D69" s="89">
         <f t="shared" ref="D69:M69" si="35">IF(E$36="","",D38/E38-1)</f>
-        <v/>
-      </c>
-      <c r="E69" s="89" t="str">
+        <v>0.22766717713118934</v>
+      </c>
+      <c r="E69" s="89">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="F69" s="89" t="str">
+        <v>0.11649378775789354</v>
+      </c>
+      <c r="F69" s="89">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="G69" s="89" t="str">
+        <v>-6.7099106763079508E-2</v>
+      </c>
+      <c r="G69" s="89">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="89" t="str">
+        <v>1.0965383788432703E-2</v>
+      </c>
+      <c r="H69" s="89">
         <f t="shared" si="35"/>
-        <v/>
+        <v>7.2523924824166919E-2</v>
       </c>
       <c r="I69" s="89" t="str">
         <f t="shared" si="35"/>
@@ -8754,25 +8959,25 @@
         <f>IF(D$36="","",C43/D43-1)</f>
         <v>0.31691386583208603</v>
       </c>
-      <c r="D70" s="98" t="str">
+      <c r="D70" s="98">
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
-        <v/>
-      </c>
-      <c r="E70" s="98" t="str">
+        <v>0.53841323006070763</v>
+      </c>
+      <c r="E70" s="98">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="F70" s="98" t="str">
+        <v>0.48538557213930345</v>
+      </c>
+      <c r="F70" s="98">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="G70" s="98" t="str">
+        <v>0.18365844681634158</v>
+      </c>
+      <c r="G70" s="98">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="98" t="str">
+        <v>-0.2707997852925389</v>
+      </c>
+      <c r="H70" s="98">
         <f t="shared" si="36"/>
-        <v/>
+        <v>-5.1667090862814957E-2</v>
       </c>
       <c r="I70" s="98" t="str">
         <f t="shared" si="36"/>
@@ -8803,25 +9008,25 @@
         <f>IF(D$36="","",C44/D44-1)</f>
         <v>9.245210727969349</v>
       </c>
-      <c r="D71" s="98" t="str">
+      <c r="D71" s="98">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
-        <v/>
-      </c>
-      <c r="E71" s="98" t="str">
+        <v>-0.26890756302521013</v>
+      </c>
+      <c r="E71" s="98">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="F71" s="98" t="str">
+        <v>-0.35559566787003605</v>
+      </c>
+      <c r="F71" s="98">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="G71" s="98" t="str">
+        <v>9.486166007905128E-2</v>
+      </c>
+      <c r="G71" s="98">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="98" t="str">
+        <v>-9.9644128113879016E-2</v>
+      </c>
+      <c r="H71" s="98">
         <f t="shared" si="37"/>
-        <v/>
+        <v>8.2131147540983598</v>
       </c>
       <c r="I71" s="98" t="str">
         <f t="shared" si="37"/>
@@ -8853,25 +9058,25 @@
         <f>IF(D$36="","",C47/D47-1)</f>
         <v>0.59698973132648758</v>
       </c>
-      <c r="D72" s="98" t="str">
+      <c r="D72" s="98">
         <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D47/E47-1)</f>
-        <v/>
-      </c>
-      <c r="E72" s="98" t="str">
+        <v>0.36187739463601543</v>
+      </c>
+      <c r="E72" s="98">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="F72" s="98" t="str">
+        <v>0.3597290961187809</v>
+      </c>
+      <c r="F72" s="98">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="G72" s="98" t="str">
+        <v>0.19409020217729389</v>
+      </c>
+      <c r="G72" s="98">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="H72" s="98" t="str">
+        <v>-0.23012452107279691</v>
+      </c>
+      <c r="H72" s="98">
         <f t="shared" si="38"/>
-        <v/>
+        <v>5.0037716872014082E-2</v>
       </c>
       <c r="I72" s="98" t="str">
         <f t="shared" si="38"/>
@@ -8926,27 +9131,27 @@
       </c>
       <c r="D76" s="285">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
-        <v>5636695</v>
-      </c>
-      <c r="E76" s="285" t="str">
+        <v>90444</v>
+      </c>
+      <c r="E76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="F76" s="285" t="str">
+        <v>75536</v>
+      </c>
+      <c r="F76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="G76" s="285" t="str">
+        <v>67009</v>
+      </c>
+      <c r="G76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="H76" s="285" t="str">
+        <v>67254</v>
+      </c>
+      <c r="H76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="I76" s="285" t="str">
+        <v>68273</v>
+      </c>
+      <c r="I76" s="285">
         <f t="shared" si="39"/>
-        <v/>
+        <v>52678</v>
       </c>
       <c r="J76" s="285" t="str">
         <f t="shared" si="39"/>
@@ -8975,23 +9180,23 @@
       </c>
       <c r="D77" s="282">
         <f t="shared" si="40"/>
-        <v>715301</v>
-      </c>
-      <c r="E77" s="282" t="str">
+        <v>3508</v>
+      </c>
+      <c r="E77" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="F77" s="282" t="str">
+        <v>2918</v>
+      </c>
+      <c r="F77" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="G77" s="282" t="str">
+        <v>2670</v>
+      </c>
+      <c r="G77" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="H77" s="282" t="str">
+        <v>3610</v>
+      </c>
+      <c r="H77" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="I77" s="291"/>
       <c r="J77" s="291"/>
@@ -9009,23 +9214,23 @@
       </c>
       <c r="D78" s="282">
         <f t="shared" si="40"/>
-        <v>23</v>
-      </c>
-      <c r="E78" s="282" t="str">
+        <v>2</v>
+      </c>
+      <c r="E78" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="F78" s="282" t="str">
+        <v>8</v>
+      </c>
+      <c r="F78" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="G78" s="282" t="str">
+        <v>8</v>
+      </c>
+      <c r="G78" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="H78" s="282" t="str">
+        <v>24</v>
+      </c>
+      <c r="H78" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>18</v>
       </c>
       <c r="I78" s="291"/>
       <c r="J78" s="291"/>
@@ -9043,27 +9248,27 @@
       </c>
       <c r="D79" s="270">
         <f t="shared" si="41"/>
-        <v>2524058</v>
-      </c>
-      <c r="E79" s="270" t="str">
+        <v>20718</v>
+      </c>
+      <c r="E79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="F79" s="270" t="str">
+        <v>18334</v>
+      </c>
+      <c r="F79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="G79" s="270" t="str">
+        <v>17882</v>
+      </c>
+      <c r="G79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="H79" s="270" t="str">
+        <v>16199</v>
+      </c>
+      <c r="H79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="I79" s="270" t="str">
+        <v>15542</v>
+      </c>
+      <c r="I79" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="J79" s="270" t="str">
         <f t="shared" si="41"/>
@@ -9092,27 +9297,27 @@
       </c>
       <c r="D80" s="270">
         <f t="shared" si="42"/>
-        <v>3112637</v>
-      </c>
-      <c r="E80" s="270" t="str">
+        <v>69726</v>
+      </c>
+      <c r="E80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="F80" s="270" t="str">
+        <v>57202</v>
+      </c>
+      <c r="F80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="G80" s="270" t="str">
+        <v>49127</v>
+      </c>
+      <c r="G80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="H80" s="270" t="str">
+        <v>51055</v>
+      </c>
+      <c r="H80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="I80" s="270" t="str">
+        <v>52731</v>
+      </c>
+      <c r="I80" s="270">
         <f t="shared" si="42"/>
-        <v/>
+        <v>43678</v>
       </c>
       <c r="J80" s="270" t="str">
         <f t="shared" si="42"/>
@@ -9988,7 +10193,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>3.3813715405821454E-2</v>
+        <v>3.432051788351935E-2</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10028,7 +10233,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.25551813502523685</v>
+        <v>0.25174496282640707</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10153,7 +10358,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>26058.935070518506</v>
+        <v>25989.935070518506</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10224,7 +10429,7 @@
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-1999.8441549135823</v>
+        <v>-2011.3441549135823</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10240,7 +10445,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>19.030482903626343</v>
+        <v>18.921674794950825</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10253,7 +10458,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>11999.064929481494</v>
+        <v>12068.064929481494</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10385,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29584.187806858252</v>
+        <v>29505.85348685825</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5162610429223768</v>
+        <v>9.4910634663450999</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10419,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48223.21484685826</v>
+        <v>48144.880526858251</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.511823539237039</v>
+        <v>15.486625962659762</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10581,25 +10786,25 @@
         <f>Data!D36</f>
         <v>28401</v>
       </c>
-      <c r="I4" s="270" t="str">
+      <c r="I4" s="270">
         <f>Data!E36</f>
-        <v/>
-      </c>
-      <c r="J4" s="270" t="str">
+        <v>27752</v>
+      </c>
+      <c r="J4" s="270">
         <f>Data!F36</f>
-        <v/>
-      </c>
-      <c r="K4" s="270" t="str">
+        <v>28339</v>
+      </c>
+      <c r="K4" s="270">
         <f>Data!G36</f>
-        <v/>
-      </c>
-      <c r="L4" s="270" t="str">
+        <v>31244</v>
+      </c>
+      <c r="L4" s="270">
         <f>Data!H36</f>
-        <v/>
-      </c>
-      <c r="M4" s="270" t="str">
+        <v>29153</v>
+      </c>
+      <c r="M4" s="270">
         <f>Data!I36</f>
-        <v/>
+        <v>25434</v>
       </c>
       <c r="N4" s="270" t="str">
         <f>Data!J36</f>
@@ -10636,25 +10841,25 @@
         <f t="shared" si="1"/>
         <v>-17241</v>
       </c>
-      <c r="I5" s="270" t="str">
+      <c r="I5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J5" s="270" t="str">
+        <v>-18854</v>
+      </c>
+      <c r="J5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K5" s="270" t="str">
+        <v>-20710</v>
+      </c>
+      <c r="K5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L5" s="270" t="str">
+        <v>-24518</v>
+      </c>
+      <c r="L5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M5" s="270" t="str">
+        <v>-22326</v>
+      </c>
+      <c r="M5" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-18802</v>
       </c>
       <c r="N5" s="270" t="str">
         <f t="shared" si="1"/>
@@ -10691,25 +10896,25 @@
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>11160</v>
       </c>
-      <c r="I6" s="267" t="str">
+      <c r="I6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J6" s="267" t="str">
+        <v>8898</v>
+      </c>
+      <c r="J6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K6" s="267" t="str">
+        <v>7629</v>
+      </c>
+      <c r="K6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L6" s="267" t="str">
+        <v>6726</v>
+      </c>
+      <c r="L6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M6" s="267" t="str">
+        <v>6827</v>
+      </c>
+      <c r="M6" s="267">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6632</v>
       </c>
       <c r="N6" s="267" t="str">
         <f t="shared" si="2"/>
@@ -10735,7 +10940,7 @@
       </c>
       <c r="C7" s="266">
         <f>C35</f>
-        <v>-3916</v>
+        <v>-4054</v>
       </c>
       <c r="E7" s="237"/>
       <c r="G7" s="266">
@@ -10746,25 +10951,25 @@
         <f t="shared" si="3"/>
         <v>-3811</v>
       </c>
-      <c r="I7" s="266" t="str">
+      <c r="I7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J7" s="266" t="str">
+        <v>-4121</v>
+      </c>
+      <c r="J7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K7" s="266" t="str">
+        <v>-4413</v>
+      </c>
+      <c r="K7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L7" s="266" t="str">
+        <v>-4009</v>
+      </c>
+      <c r="L7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M7" s="266" t="str">
+        <v>-3101</v>
+      </c>
+      <c r="M7" s="266">
         <f t="shared" si="3"/>
-        <v/>
+        <v>-2703</v>
       </c>
       <c r="N7" s="266" t="str">
         <f t="shared" si="3"/>
@@ -10790,7 +10995,7 @@
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
-        <v>9345.3202704130126</v>
+        <v>9207.3202704130126</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="241"/>
@@ -10803,25 +11008,25 @@
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>7349</v>
       </c>
-      <c r="I8" s="267" t="str">
+      <c r="I8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J8" s="267" t="str">
+        <v>4777</v>
+      </c>
+      <c r="J8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K8" s="267" t="str">
+        <v>3216</v>
+      </c>
+      <c r="K8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L8" s="267" t="str">
+        <v>2717</v>
+      </c>
+      <c r="L8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M8" s="267" t="str">
+        <v>3726</v>
+      </c>
+      <c r="M8" s="267">
         <f t="shared" si="4"/>
-        <v/>
+        <v>3929</v>
       </c>
       <c r="N8" s="267" t="str">
         <f t="shared" si="4"/>
@@ -10860,25 +11065,25 @@
         <f t="shared" ref="H9:Q9" si="5">H59</f>
         <v>0</v>
       </c>
-      <c r="I9" s="270" t="str">
+      <c r="I9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J9" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="J9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K9" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="L9" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="L9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M9" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="M9" s="270">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N9" s="270" t="str">
         <f t="shared" si="5"/>
@@ -10904,36 +11109,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>203.30896094575371</v>
+        <v>205.21988637536117</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>283.07923841662375</v>
-      </c>
-      <c r="I10" s="266" t="str">
+        <v>285.24761300278175</v>
+      </c>
+      <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J10" s="266" t="str">
+        <v>192.5856930425806</v>
+      </c>
+      <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K10" s="266" t="str">
+        <v>117.45572980349314</v>
+      </c>
+      <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="L10" s="266" t="str">
+        <v>47.061233186851439</v>
+      </c>
+      <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="M10" s="266" t="str">
+        <v>100.23412649475773</v>
+      </c>
+      <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v/>
+        <v>131.01444983002571</v>
       </c>
       <c r="N10" s="266" t="str">
         <f t="shared" si="6"/>
@@ -10959,36 +11164,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>9398.3546599899018</v>
+        <v>9260.7686599899007</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>9881.3089609457529</v>
+        <v>9883.219886375362</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>7632.0792384166234</v>
-      </c>
-      <c r="I11" s="267" t="str">
+        <v>7634.2476130027817</v>
+      </c>
+      <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J11" s="267" t="str">
+        <v>4969.5856930425807</v>
+      </c>
+      <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K11" s="267" t="str">
+        <v>3333.4557298034933</v>
+      </c>
+      <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="L11" s="267" t="str">
+        <v>2764.0612331868515</v>
+      </c>
+      <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M11" s="267" t="str">
+        <v>3826.2341264947577</v>
+      </c>
+      <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v/>
+        <v>4060.0144498300256</v>
       </c>
       <c r="N11" s="267" t="str">
         <f t="shared" si="7"/>
@@ -11014,7 +11219,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-2349.5886649974755</v>
+        <v>-2315.1921649974752</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11025,25 +11230,25 @@
         <f>Data!D46</f>
         <v>-1603</v>
       </c>
-      <c r="I12" s="266" t="str">
+      <c r="I12" s="266">
         <f>Data!E46</f>
-        <v/>
-      </c>
-      <c r="J12" s="266" t="str">
+        <v>-825</v>
+      </c>
+      <c r="J12" s="266">
         <f>Data!F46</f>
-        <v/>
-      </c>
-      <c r="K12" s="266" t="str">
+        <v>-534</v>
+      </c>
+      <c r="K12" s="266">
         <f>Data!G46</f>
-        <v/>
-      </c>
-      <c r="L12" s="266" t="str">
+        <v>-417</v>
+      </c>
+      <c r="L12" s="266">
         <f>Data!H46</f>
-        <v/>
-      </c>
-      <c r="M12" s="266" t="str">
+        <v>-637</v>
+      </c>
+      <c r="M12" s="266">
         <f>Data!I46</f>
-        <v/>
+        <v>-564</v>
       </c>
       <c r="N12" s="266" t="str">
         <f>Data!J46</f>
@@ -11082,25 +11287,25 @@
         <f>Data!D48</f>
         <v>-465</v>
       </c>
-      <c r="I13" s="270" t="str">
+      <c r="I13" s="270">
         <f>Data!E48</f>
-        <v/>
-      </c>
-      <c r="J13" s="270" t="str">
+        <v>-300</v>
+      </c>
+      <c r="J13" s="270">
         <f>Data!F48</f>
-        <v/>
-      </c>
-      <c r="K13" s="270" t="str">
+        <v>-162</v>
+      </c>
+      <c r="K13" s="270">
         <f>Data!G48</f>
-        <v/>
-      </c>
-      <c r="L13" s="270" t="str">
+        <v>-186</v>
+      </c>
+      <c r="L13" s="270">
         <f>Data!H48</f>
-        <v/>
-      </c>
-      <c r="M13" s="270" t="str">
+        <v>-21</v>
+      </c>
+      <c r="M13" s="270">
         <f>Data!I48</f>
-        <v/>
+        <v>-5</v>
       </c>
       <c r="N13" s="270" t="str">
         <f>Data!J48</f>
@@ -11126,38 +11331,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>7660.3089609457529</v>
+        <v>7662.219886375362</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>5564.0792384166234</v>
-      </c>
-      <c r="I14" s="267" t="str">
+        <v>5566.2476130027817</v>
+      </c>
+      <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J14" s="267" t="str">
+        <v>3844.5856930425807</v>
+      </c>
+      <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K14" s="267" t="str">
+        <v>2637.4557298034933</v>
+      </c>
+      <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="L14" s="267" t="str">
+        <v>2161.0612331868515</v>
+      </c>
+      <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="M14" s="267" t="str">
+        <v>3168.2341264947577</v>
+      </c>
+      <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3491.0144498300256</v>
       </c>
       <c r="N14" s="267" t="str">
         <f t="shared" si="8"/>
@@ -11194,25 +11399,25 @@
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="266" t="str">
+      <c r="I15" s="266">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v/>
-      </c>
-      <c r="J15" s="266" t="str">
+        <v>1004</v>
+      </c>
+      <c r="J15" s="266">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v/>
-      </c>
-      <c r="K15" s="266" t="str">
+        <v>1160</v>
+      </c>
+      <c r="K15" s="266">
         <f>IF(Data!G61="","",-Data!G61)</f>
-        <v/>
-      </c>
-      <c r="L15" s="266" t="str">
+        <v>1001</v>
+      </c>
+      <c r="L15" s="266">
         <f>IF(Data!H61="","",-Data!H61)</f>
-        <v/>
-      </c>
-      <c r="M15" s="266" t="str">
+        <v>824</v>
+      </c>
+      <c r="M15" s="266">
         <f>IF(Data!I61="","",-Data!I61)</f>
-        <v/>
+        <v>583</v>
       </c>
       <c r="N15" s="266" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
@@ -11238,7 +11443,7 @@
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
-        <v>0</v>
+        <v>-650.63867420757288</v>
       </c>
       <c r="E16" s="237"/>
       <c r="G16" s="266">
@@ -11249,25 +11454,25 @@
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I16" s="266" t="str">
+      <c r="I16" s="266">
         <f>Data!E62</f>
-        <v/>
-      </c>
-      <c r="J16" s="266" t="str">
+        <v>-1164</v>
+      </c>
+      <c r="J16" s="266">
         <f>Data!F62</f>
-        <v/>
-      </c>
-      <c r="K16" s="266" t="str">
+        <v>-1053</v>
+      </c>
+      <c r="K16" s="266">
         <f>Data!G62</f>
-        <v/>
-      </c>
-      <c r="L16" s="266" t="str">
+        <v>-2758</v>
+      </c>
+      <c r="L16" s="266">
         <f>Data!H62</f>
-        <v/>
-      </c>
-      <c r="M16" s="266" t="str">
+        <v>-501</v>
+      </c>
+      <c r="M16" s="266">
         <f>Data!I62</f>
-        <v/>
+        <v>-286</v>
       </c>
       <c r="N16" s="266" t="str">
         <f>Data!J62</f>
@@ -11344,38 +11549,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>7660.3089609457529</v>
+        <v>7662.219886375362</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>5564.0792384166234</v>
-      </c>
-      <c r="I19" s="271" t="str">
+        <v>5566.2476130027817</v>
+      </c>
+      <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="J19" s="271" t="str">
+        <v>3844.5856930425807</v>
+      </c>
+      <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K19" s="271" t="str">
+        <v>2637.4557298034933</v>
+      </c>
+      <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="L19" s="271" t="str">
+        <v>2161.0612331868515</v>
+      </c>
+      <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="M19" s="271" t="str">
+        <v>3168.2341264947577</v>
+      </c>
+      <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3491.0144498300256</v>
       </c>
       <c r="N19" s="271" t="str">
         <f t="shared" si="9"/>
@@ -11477,25 +11682,25 @@
         <f>Data!D37</f>
         <v>-16376</v>
       </c>
-      <c r="I23" s="270" t="str">
+      <c r="I23" s="270">
         <f>Data!E37</f>
-        <v/>
-      </c>
-      <c r="J23" s="270" t="str">
+        <v>-17957</v>
+      </c>
+      <c r="J23" s="270">
         <f>Data!F37</f>
-        <v/>
-      </c>
-      <c r="K23" s="270" t="str">
+        <v>-19566</v>
+      </c>
+      <c r="K23" s="270">
         <f>Data!G37</f>
-        <v/>
-      </c>
-      <c r="L23" s="270" t="str">
+        <v>-21840</v>
+      </c>
+      <c r="L23" s="270">
         <f>Data!H37</f>
-        <v/>
-      </c>
-      <c r="M23" s="270" t="str">
+        <v>-19851</v>
+      </c>
+      <c r="M23" s="270">
         <f>Data!I37</f>
-        <v/>
+        <v>-16761</v>
       </c>
       <c r="N23" s="270" t="str">
         <f>Data!J37</f>
@@ -11534,25 +11739,25 @@
         <f>Data!D40</f>
         <v>-865</v>
       </c>
-      <c r="I24" s="270" t="str">
+      <c r="I24" s="270">
         <f>Data!E40</f>
-        <v/>
-      </c>
-      <c r="J24" s="270" t="str">
+        <v>-897</v>
+      </c>
+      <c r="J24" s="270">
         <f>Data!F40</f>
-        <v/>
-      </c>
-      <c r="K24" s="270" t="str">
+        <v>-1144</v>
+      </c>
+      <c r="K24" s="270">
         <f>Data!G40</f>
-        <v/>
-      </c>
-      <c r="L24" s="270" t="str">
+        <v>-2678</v>
+      </c>
+      <c r="L24" s="270">
         <f>Data!H40</f>
-        <v/>
-      </c>
-      <c r="M24" s="270" t="str">
+        <v>-2475</v>
+      </c>
+      <c r="M24" s="270">
         <f>Data!I40</f>
-        <v/>
+        <v>-2041</v>
       </c>
       <c r="N24" s="270" t="str">
         <f>Data!J40</f>
@@ -11591,25 +11796,25 @@
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I25" s="270" t="str">
+      <c r="I25" s="270">
         <f>Data!E42</f>
-        <v/>
-      </c>
-      <c r="J25" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="J25" s="270">
         <f>Data!F42</f>
-        <v/>
-      </c>
-      <c r="K25" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K25" s="270">
         <f>Data!G42</f>
-        <v/>
-      </c>
-      <c r="L25" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="L25" s="270">
         <f>Data!H42</f>
-        <v/>
-      </c>
-      <c r="M25" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="M25" s="270">
         <f>Data!I42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N25" s="270" t="str">
         <f>Data!J42</f>
@@ -11648,25 +11853,25 @@
         <f t="shared" ref="H26:Q26" si="10">IF(H$4="","",SUM(H23:H25))</f>
         <v>-17241</v>
       </c>
-      <c r="I26" s="267" t="str">
+      <c r="I26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J26" s="267" t="str">
+        <v>-18854</v>
+      </c>
+      <c r="J26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K26" s="267" t="str">
+        <v>-20710</v>
+      </c>
+      <c r="K26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L26" s="267" t="str">
+        <v>-24518</v>
+      </c>
+      <c r="L26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M26" s="267" t="str">
+        <v>-22326</v>
+      </c>
+      <c r="M26" s="267">
         <f t="shared" si="10"/>
-        <v/>
+        <v>-18802</v>
       </c>
       <c r="N26" s="267" t="str">
         <f t="shared" si="10"/>
@@ -11716,25 +11921,25 @@
         <f t="shared" si="11"/>
         <v>0.57659941551353822</v>
       </c>
-      <c r="I29" s="13" t="str">
+      <c r="I29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="J29" s="13" t="str">
+        <v>0.64705246468722977</v>
+      </c>
+      <c r="J29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K29" s="13" t="str">
+        <v>0.69042662055824133</v>
+      </c>
+      <c r="K29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="L29" s="13" t="str">
+        <v>0.69901421072845982</v>
+      </c>
+      <c r="L29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M29" s="13" t="str">
+        <v>0.68092477618083902</v>
+      </c>
+      <c r="M29" s="13">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.65899976409530547</v>
       </c>
       <c r="N29" s="13" t="str">
         <f t="shared" si="11"/>
@@ -11774,25 +11979,25 @@
         <f t="shared" si="12"/>
         <v>3.0456674060772508E-2</v>
       </c>
-      <c r="I30" s="13" t="str">
+      <c r="I30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J30" s="13" t="str">
+        <v>3.2321994811184779E-2</v>
+      </c>
+      <c r="J30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K30" s="13" t="str">
+        <v>4.0368396908853521E-2</v>
+      </c>
+      <c r="K30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="L30" s="13" t="str">
+        <v>8.5712456791704E-2</v>
+      </c>
+      <c r="L30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="M30" s="13" t="str">
+        <v>8.4896923129695059E-2</v>
+      </c>
+      <c r="M30" s="13">
         <f t="shared" si="12"/>
-        <v/>
+        <v>8.0246913580246909E-2</v>
       </c>
       <c r="N30" s="13" t="str">
         <f t="shared" si="12"/>
@@ -11831,25 +12036,25 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I31" s="13" t="str">
+      <c r="I31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="L31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="M31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="M31" s="13">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N31" s="13" t="str">
         <f t="shared" si="13"/>
@@ -11886,25 +12091,25 @@
         <f t="shared" si="14"/>
         <v>0.60705608957431079</v>
       </c>
-      <c r="I32" s="29" t="str">
+      <c r="I32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J32" s="29" t="str">
+        <v>0.67937445949841457</v>
+      </c>
+      <c r="J32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="K32" s="29" t="str">
+        <v>0.73079501746709485</v>
+      </c>
+      <c r="K32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="L32" s="29" t="str">
+        <v>0.78472666752016385</v>
+      </c>
+      <c r="L32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="M32" s="29" t="str">
+        <v>0.76582169931053412</v>
+      </c>
+      <c r="M32" s="29">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0.73924667767555241</v>
       </c>
       <c r="N32" s="29" t="str">
         <f t="shared" si="14"/>
@@ -11940,8 +12145,8 @@
         <v>396</v>
       </c>
       <c r="C35" s="276">
-        <f>G35</f>
-        <v>-3916</v>
+        <f>AVERAGE(G35:K35)</f>
+        <v>-4054</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="236"/>
@@ -11954,25 +12159,25 @@
         <f>IF(H4="","",Data!D41)</f>
         <v>-3811</v>
       </c>
-      <c r="I35" s="267" t="str">
+      <c r="I35" s="267">
         <f>IF(I4="","",Data!E41)</f>
-        <v/>
-      </c>
-      <c r="J35" s="267" t="str">
+        <v>-4121</v>
+      </c>
+      <c r="J35" s="267">
         <f>IF(J4="","",Data!F41)</f>
-        <v/>
-      </c>
-      <c r="K35" s="267" t="str">
+        <v>-4413</v>
+      </c>
+      <c r="K35" s="267">
         <f>IF(K4="","",Data!G41)</f>
-        <v/>
-      </c>
-      <c r="L35" s="267" t="str">
+        <v>-4009</v>
+      </c>
+      <c r="L35" s="267">
         <f>IF(L4="","",Data!H41)</f>
-        <v/>
-      </c>
-      <c r="M35" s="267" t="str">
+        <v>-3101</v>
+      </c>
+      <c r="M35" s="267">
         <f>IF(M4="","",Data!I41)</f>
-        <v/>
+        <v>-2703</v>
       </c>
       <c r="N35" s="267" t="str">
         <f>IF(N4="","",Data!J41)</f>
@@ -12009,7 +12214,7 @@
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
-        <v>0.11902012035742508</v>
+        <v>0.123214394261747</v>
       </c>
       <c r="E38" s="237"/>
       <c r="G38" s="29">
@@ -12020,25 +12225,25 @@
         <f t="shared" si="15"/>
         <v>0.13418541600647865</v>
       </c>
-      <c r="I38" s="29" t="str">
+      <c r="I38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="J38" s="29" t="str">
+        <v>0.1484938022484866</v>
+      </c>
+      <c r="J38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K38" s="29" t="str">
+        <v>0.15572179681710716</v>
+      </c>
+      <c r="K38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="L38" s="29" t="str">
+        <v>0.12831263602611701</v>
+      </c>
+      <c r="L38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="M38" s="29" t="str">
+        <v>0.10636984186876136</v>
+      </c>
+      <c r="M38" s="29">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0.10627506487379099</v>
       </c>
       <c r="N38" s="29" t="str">
         <f t="shared" si="15"/>
@@ -12083,31 +12288,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>0.19471104563214178</v>
+        <v>0.19467339815563089</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.21003450697041817</v>
-      </c>
-      <c r="I41" s="6" t="str">
+        <v>0.20997485034016225</v>
+      </c>
+      <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="J41" s="6" t="str">
+        <v>0.16600981469239978</v>
+      </c>
+      <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="K41" s="6" t="str">
+        <v>0.16019411784163073</v>
+      </c>
+      <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L41" s="6" t="str">
+        <v>0.15086496456491877</v>
+      </c>
+      <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="M41" s="6" t="str">
+        <v>0.16648223264465015</v>
+      </c>
+      <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0.13891576174651599</v>
       </c>
       <c r="N41" s="6" t="str">
         <f t="shared" si="16"/>
@@ -12177,25 +12382,25 @@
         <f>Data!D51</f>
         <v>-94</v>
       </c>
-      <c r="I45" s="266" t="str">
+      <c r="I45" s="266">
         <f>Data!E51</f>
-        <v/>
-      </c>
-      <c r="J45" s="266" t="str">
+        <v>-141</v>
+      </c>
+      <c r="J45" s="266">
         <f>Data!F51</f>
-        <v/>
-      </c>
-      <c r="K45" s="266" t="str">
+        <v>-108</v>
+      </c>
+      <c r="K45" s="266">
         <f>Data!G51</f>
-        <v/>
-      </c>
-      <c r="L45" s="266" t="str">
+        <v>-121</v>
+      </c>
+      <c r="L45" s="266">
         <f>Data!H51</f>
-        <v/>
-      </c>
-      <c r="M45" s="266" t="str">
+        <v>-97</v>
+      </c>
+      <c r="M45" s="266">
         <f>Data!I51</f>
-        <v/>
+        <v>-64</v>
       </c>
       <c r="N45" s="266" t="str">
         <f>Data!J51</f>
@@ -12221,36 +12426,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>71.994389576888963</v>
+        <v>72.408389576888965</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>332.30896094575371</v>
+        <v>334.21988637536117</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>377.07923841662375</v>
-      </c>
-      <c r="I46" s="274" t="str">
+        <v>379.24761300278175</v>
+      </c>
+      <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="J46" s="274" t="str">
+        <v>333.5856930425806</v>
+      </c>
+      <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="K46" s="274" t="str">
+        <v>225.45572980349314</v>
+      </c>
+      <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="L46" s="274" t="str">
+        <v>168.06123318685144</v>
+      </c>
+      <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="M46" s="274" t="str">
+        <v>197.23412649475773</v>
+      </c>
+      <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v/>
+        <v>195.01444983002571</v>
       </c>
       <c r="N46" s="274" t="str">
         <f t="shared" si="17"/>
@@ -12289,25 +12494,25 @@
         <f>Data!D52</f>
         <v>1196</v>
       </c>
-      <c r="I47" s="278" t="str">
+      <c r="I47" s="278">
         <f>Data!E52</f>
-        <v/>
-      </c>
-      <c r="J47" s="278" t="str">
+        <v>1052</v>
+      </c>
+      <c r="J47" s="278">
         <f>Data!F52</f>
-        <v/>
-      </c>
-      <c r="K47" s="278" t="str">
+        <v>711</v>
+      </c>
+      <c r="K47" s="278">
         <f>Data!G52</f>
-        <v/>
-      </c>
-      <c r="L47" s="278" t="str">
+        <v>530</v>
+      </c>
+      <c r="L47" s="278">
         <f>Data!H52</f>
-        <v/>
-      </c>
-      <c r="M47" s="278" t="str">
+        <v>622</v>
+      </c>
+      <c r="M47" s="278">
         <f>Data!I52</f>
-        <v/>
+        <v>615</v>
       </c>
       <c r="N47" s="278" t="str">
         <f>Data!J52</f>
@@ -12333,36 +12538,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>203.30896094575371</v>
+        <v>205.21988637536117</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>283.07923841662375</v>
-      </c>
-      <c r="I48" s="267" t="str">
+        <v>285.24761300278175</v>
+      </c>
+      <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="J48" s="267" t="str">
+        <v>192.5856930425806</v>
+      </c>
+      <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="K48" s="267" t="str">
+        <v>117.45572980349314</v>
+      </c>
+      <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="L48" s="267" t="str">
+        <v>47.061233186851439</v>
+      </c>
+      <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="M48" s="267" t="str">
+        <v>100.23412649475773</v>
+      </c>
+      <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v/>
+        <v>131.01444983002571</v>
       </c>
       <c r="N48" s="267" t="str">
         <f t="shared" si="18"/>
@@ -12450,7 +12655,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>492.89663873486353</v>
+        <v>485.6181577222053</v>
       </c>
       <c r="E53" s="237"/>
       <c r="G53" s="40">
@@ -12461,25 +12666,25 @@
         <f t="shared" si="19"/>
         <v>78.180851063829792</v>
       </c>
-      <c r="I53" s="40" t="str">
+      <c r="I53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J53" s="40" t="str">
+        <v>33.879432624113477</v>
+      </c>
+      <c r="J53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="K53" s="40" t="str">
+        <v>29.777777777777779</v>
+      </c>
+      <c r="K53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="L53" s="40" t="str">
+        <v>22.454545454545453</v>
+      </c>
+      <c r="L53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="M53" s="40" t="str">
+        <v>38.412371134020617</v>
+      </c>
+      <c r="M53" s="40">
         <f t="shared" si="19"/>
-        <v/>
+        <v>61.390625</v>
       </c>
       <c r="N53" s="40" t="str">
         <f t="shared" si="19"/>
@@ -12530,25 +12735,25 @@
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="266" t="str">
+      <c r="I56" s="266">
         <f>Data!E56</f>
-        <v/>
-      </c>
-      <c r="J56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" s="266">
         <f>Data!F56</f>
-        <v/>
-      </c>
-      <c r="K56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K56" s="266">
         <f>Data!G56</f>
-        <v/>
-      </c>
-      <c r="L56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="L56" s="266">
         <f>Data!H56</f>
-        <v/>
-      </c>
-      <c r="M56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="M56" s="266">
         <f>Data!I56</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N56" s="266" t="str">
         <f>Data!J56</f>
@@ -12585,25 +12790,25 @@
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I57" s="266" t="str">
+      <c r="I57" s="266">
         <f>Data!E55</f>
-        <v/>
-      </c>
-      <c r="J57" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" s="266">
         <f>Data!F55</f>
-        <v/>
-      </c>
-      <c r="K57" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K57" s="266">
         <f>Data!G55</f>
-        <v/>
-      </c>
-      <c r="L57" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="L57" s="266">
         <f>Data!H55</f>
-        <v/>
-      </c>
-      <c r="M57" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="M57" s="266">
         <f>Data!I55</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N57" s="266" t="str">
         <f>Data!J55</f>
@@ -12640,25 +12845,25 @@
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I58" s="266" t="str">
+      <c r="I58" s="266">
         <f>Data!E57</f>
-        <v/>
-      </c>
-      <c r="J58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" s="266">
         <f>Data!F57</f>
-        <v/>
-      </c>
-      <c r="K58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K58" s="266">
         <f>Data!G57</f>
-        <v/>
-      </c>
-      <c r="L58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="L58" s="266">
         <f>Data!H57</f>
-        <v/>
-      </c>
-      <c r="M58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="M58" s="266">
         <f>Data!I57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N58" s="266" t="str">
         <f>Data!J57</f>
@@ -12695,25 +12900,25 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="I59" s="267" t="str">
+      <c r="I59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J59" s="267" t="str">
+        <v>0</v>
+      </c>
+      <c r="J59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K59" s="267" t="str">
+        <v>0</v>
+      </c>
+      <c r="K59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="L59" s="267" t="str">
+        <v>0</v>
+      </c>
+      <c r="L59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="M59" s="267" t="str">
+        <v>0</v>
+      </c>
+      <c r="M59" s="267">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N59" s="267" t="str">
         <f t="shared" si="20"/>
@@ -12751,25 +12956,25 @@
         <f>Data!D58</f>
         <v>261</v>
       </c>
-      <c r="I60" s="266" t="str">
+      <c r="I60" s="266">
         <f>Data!E58</f>
-        <v/>
-      </c>
-      <c r="J60" s="266" t="str">
+        <v>357</v>
+      </c>
+      <c r="J60" s="266">
         <f>Data!F58</f>
-        <v/>
-      </c>
-      <c r="K60" s="266" t="str">
+        <v>554</v>
+      </c>
+      <c r="K60" s="266">
         <f>Data!G58</f>
-        <v/>
-      </c>
-      <c r="L60" s="266" t="str">
+        <v>506</v>
+      </c>
+      <c r="L60" s="266">
         <f>Data!H58</f>
-        <v/>
-      </c>
-      <c r="M60" s="266" t="str">
+        <v>562</v>
+      </c>
+      <c r="M60" s="266">
         <f>Data!I58</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="N60" s="266" t="str">
         <f>Data!J58</f>
@@ -12806,25 +13011,25 @@
         <f t="shared" si="21"/>
         <v>261</v>
       </c>
-      <c r="I61" s="267" t="str">
+      <c r="I61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="J61" s="267" t="str">
+        <v>357</v>
+      </c>
+      <c r="J61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K61" s="267" t="str">
+        <v>554</v>
+      </c>
+      <c r="K61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="L61" s="267" t="str">
+        <v>506</v>
+      </c>
+      <c r="L61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="M61" s="267" t="str">
+        <v>562</v>
+      </c>
+      <c r="M61" s="267">
         <f t="shared" si="21"/>
-        <v/>
+        <v>61</v>
       </c>
       <c r="N61" s="267" t="str">
         <f t="shared" si="21"/>
@@ -13026,25 +13231,25 @@
         <f t="shared" si="23"/>
         <v>0.60705608957431079</v>
       </c>
-      <c r="I71" s="6" t="str">
+      <c r="I71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="J71" s="6" t="str">
+        <v>0.67937445949841457</v>
+      </c>
+      <c r="J71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="K71" s="6" t="str">
+        <v>0.73079501746709485</v>
+      </c>
+      <c r="K71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="L71" s="6" t="str">
+        <v>0.78472666752016385</v>
+      </c>
+      <c r="L71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M71" s="6" t="str">
+        <v>0.76582169931053412</v>
+      </c>
+      <c r="M71" s="6">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.73924667767555241</v>
       </c>
       <c r="N71" s="6" t="str">
         <f t="shared" si="23"/>
@@ -13083,25 +13288,25 @@
         <f t="shared" si="24"/>
         <v>0.39294391042568921</v>
       </c>
-      <c r="I72" s="62" t="str">
+      <c r="I72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="J72" s="62" t="str">
+        <v>0.32062554050158548</v>
+      </c>
+      <c r="J72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="K72" s="62" t="str">
+        <v>0.2692049825329052</v>
+      </c>
+      <c r="K72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L72" s="62" t="str">
+        <v>0.21527333247983613</v>
+      </c>
+      <c r="L72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="M72" s="62" t="str">
+        <v>0.23417830068946593</v>
+      </c>
+      <c r="M72" s="62">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0.26075332232444759</v>
       </c>
       <c r="N72" s="62" t="str">
         <f t="shared" si="24"/>
@@ -13127,7 +13332,7 @@
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
-        <v>0.11902012035742508</v>
+        <v>0.123214394261747</v>
       </c>
       <c r="D73" s="26"/>
       <c r="E73" s="234"/>
@@ -13140,25 +13345,25 @@
         <f t="shared" si="25"/>
         <v>0.13418541600647865</v>
       </c>
-      <c r="I73" s="6" t="str">
+      <c r="I73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="J73" s="6" t="str">
+        <v>0.1484938022484866</v>
+      </c>
+      <c r="J73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="K73" s="6" t="str">
+        <v>0.15572179681710716</v>
+      </c>
+      <c r="K73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="L73" s="6" t="str">
+        <v>0.12831263602611701</v>
+      </c>
+      <c r="L73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="M73" s="6" t="str">
+        <v>0.10636984186876136</v>
+      </c>
+      <c r="M73" s="6">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0.10627506487379099</v>
       </c>
       <c r="N73" s="6" t="str">
         <f t="shared" si="25"/>
@@ -13184,7 +13389,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>0.28403502128785524</v>
+        <v>0.27984074738353332</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="234"/>
@@ -13197,25 +13402,25 @@
         <f t="shared" si="26"/>
         <v>0.25875849441921062</v>
       </c>
-      <c r="I74" s="62" t="str">
+      <c r="I74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="J74" s="62" t="str">
+        <v>0.17213173825309888</v>
+      </c>
+      <c r="J74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="K74" s="62" t="str">
+        <v>0.11348318571579802</v>
+      </c>
+      <c r="K74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="L74" s="62" t="str">
+        <v>8.6960696453719108E-2</v>
+      </c>
+      <c r="L74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="M74" s="62" t="str">
+        <v>0.12780845882070455</v>
+      </c>
+      <c r="M74" s="62">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.1544782574506566</v>
       </c>
       <c r="N74" s="62" t="str">
         <f t="shared" si="26"/>
@@ -13254,25 +13459,25 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="I75" s="6" t="str">
+      <c r="I75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="J75" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="K75" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="K75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="L75" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="L75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="M75" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="M75" s="6">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N75" s="6" t="str">
         <f t="shared" si="27"/>
@@ -13298,38 +13503,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>1.61188953792745E-3</v>
+        <v>1.6244723596404158E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>6.1792280391998571E-3</v>
+        <v>6.2373073483484639E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.9672278587593314E-3</v>
-      </c>
-      <c r="I76" s="6" t="str">
+        <v>1.0043576388253293E-2</v>
+      </c>
+      <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="J76" s="6" t="str">
+        <v>6.9395248285738179E-3</v>
+      </c>
+      <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="K76" s="6" t="str">
+        <v>4.1446674125231358E-3</v>
+      </c>
+      <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="L76" s="6" t="str">
+        <v>1.5062486617222967E-3</v>
+      </c>
+      <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="M76" s="6" t="str">
+        <v>3.4382096694939709E-3</v>
+      </c>
+      <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v/>
+        <v>5.1511539604476575E-3</v>
       </c>
       <c r="N76" s="6" t="str">
         <f t="shared" si="28"/>
@@ -13355,38 +13560,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.30032548054664621</v>
+        <v>0.30038355985579485</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.26872572227796993</v>
-      </c>
-      <c r="I77" s="62" t="str">
+        <v>0.26880207080746388</v>
+      </c>
+      <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J77" s="62" t="str">
+        <v>0.1790712630816727</v>
+      </c>
+      <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="K77" s="62" t="str">
+        <v>0.11762785312832116</v>
+      </c>
+      <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="L77" s="62" t="str">
+        <v>8.8466945115441412E-2</v>
+      </c>
+      <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="M77" s="62" t="str">
+        <v>0.13124666849019853</v>
+      </c>
+      <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0.15962941141110426</v>
       </c>
       <c r="N77" s="62" t="str">
         <f t="shared" si="29"/>
@@ -13412,7 +13617,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>7.1411727706445674E-2</v>
+        <v>7.0366304935793419E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13425,25 +13630,25 @@
         <f t="shared" si="30"/>
         <v>5.6441674588922928E-2</v>
       </c>
-      <c r="I78" s="6" t="str">
+      <c r="I78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="J78" s="6" t="str">
+        <v>2.9727587200922456E-2</v>
+      </c>
+      <c r="J78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K78" s="6" t="str">
+        <v>1.8843290165496313E-2</v>
+      </c>
+      <c r="K78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="L78" s="6" t="str">
+        <v>1.3346562540007682E-2</v>
+      </c>
+      <c r="L78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="M78" s="6" t="str">
+        <v>2.1850238397420507E-2</v>
+      </c>
+      <c r="M78" s="6">
         <f t="shared" si="30"/>
-        <v/>
+        <v>2.2175041283321539E-2</v>
       </c>
       <c r="N78" s="6" t="str">
         <f t="shared" si="30"/>
@@ -13483,25 +13688,25 @@
         <f t="shared" si="31"/>
         <v>1.6372662934403717E-2</v>
       </c>
-      <c r="I79" s="6" t="str">
+      <c r="I79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J79" s="6" t="str">
+        <v>1.0810031709426347E-2</v>
+      </c>
+      <c r="J79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K79" s="6" t="str">
+        <v>5.7165037580719147E-3</v>
+      </c>
+      <c r="K79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L79" s="6" t="str">
+        <v>5.9531430034566639E-3</v>
+      </c>
+      <c r="L79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="M79" s="6" t="str">
+        <v>7.2033752958529135E-4</v>
+      </c>
+      <c r="M79" s="6">
         <f t="shared" si="31"/>
-        <v/>
+        <v>1.9658724541951719E-4</v>
       </c>
       <c r="N79" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13527,38 +13732,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>0.1978625201849333</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>0.2328219853183926</v>
+        <v>0.23288006462754124</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.19591138475464326</v>
-      </c>
-      <c r="I80" s="62" t="str">
+        <v>0.19598773328413724</v>
+      </c>
+      <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J80" s="62" t="str">
+        <v>0.13853364417132388</v>
+      </c>
+      <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K80" s="62" t="str">
+        <v>9.3068059204752931E-2</v>
+      </c>
+      <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L80" s="62" t="str">
+        <v>6.9167239571977068E-2</v>
+      </c>
+      <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M80" s="62" t="str">
+        <v>0.10867609256319273</v>
+      </c>
+      <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v/>
+        <v>0.13725778288236321</v>
       </c>
       <c r="N80" s="62" t="str">
         <f t="shared" si="32"/>
@@ -13597,25 +13802,25 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I81" s="6" t="str">
+      <c r="I81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J81" s="6" t="str">
+        <v>3.6177572787546845E-2</v>
+      </c>
+      <c r="J81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K81" s="6" t="str">
+        <v>4.0932989872613713E-2</v>
+      </c>
+      <c r="K81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L81" s="6" t="str">
+        <v>3.2038151325054408E-2</v>
+      </c>
+      <c r="L81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M81" s="6" t="str">
+        <v>2.826467258944191E-2</v>
+      </c>
+      <c r="M81" s="6">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2.2922072815915705E-2</v>
       </c>
       <c r="N81" s="6" t="str">
         <f t="shared" si="33"/>
@@ -13641,7 +13846,7 @@
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
-        <v>0</v>
+        <v>1.9775049365010421E-2</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
@@ -13656,25 +13861,25 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="I82" s="6" t="str">
+      <c r="I82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J82" s="6" t="str">
+        <v>4.1942923032574228E-2</v>
+      </c>
+      <c r="J82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K82" s="6" t="str">
+        <v>3.7157274427467447E-2</v>
+      </c>
+      <c r="K82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L82" s="6" t="str">
+        <v>8.8272948406093968E-2</v>
+      </c>
+      <c r="L82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M82" s="6" t="str">
+        <v>1.7185195348677667E-2</v>
+      </c>
+      <c r="M82" s="6">
         <f t="shared" si="34"/>
-        <v/>
+        <v>1.1244790437996383E-2</v>
       </c>
       <c r="N82" s="6" t="str">
         <f t="shared" si="34"/>
@@ -13750,38 +13955,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>0.1978625201849333</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.2328219853183926</v>
+        <v>0.23288006462754124</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.19591138475464326</v>
-      </c>
-      <c r="I85" s="62" t="str">
+        <v>0.19598773328413724</v>
+      </c>
+      <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J85" s="62" t="str">
+        <v>0.13853364417132388</v>
+      </c>
+      <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K85" s="62" t="str">
+        <v>9.3068059204752931E-2</v>
+      </c>
+      <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L85" s="62" t="str">
+        <v>6.9167239571977068E-2</v>
+      </c>
+      <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M85" s="62" t="str">
+        <v>0.10867609256319273</v>
+      </c>
+      <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.13725778288236321</v>
       </c>
       <c r="N85" s="62" t="str">
         <f t="shared" si="35"/>
@@ -13830,25 +14035,25 @@
         <f>Data!D65</f>
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I88" s="109" t="str">
+      <c r="I88" s="109">
         <f>Data!E65</f>
-        <v/>
-      </c>
-      <c r="J88" s="109" t="str">
+        <v>0</v>
+      </c>
+      <c r="J88" s="109">
         <f>Data!F65</f>
-        <v/>
-      </c>
-      <c r="K88" s="109" t="str">
+        <v>0</v>
+      </c>
+      <c r="K88" s="109">
         <f>Data!G65</f>
-        <v/>
-      </c>
-      <c r="L88" s="109" t="str">
+        <v>0</v>
+      </c>
+      <c r="L88" s="109">
         <f>Data!H65</f>
-        <v/>
-      </c>
-      <c r="M88" s="109" t="str">
+        <v>0</v>
+      </c>
+      <c r="M88" s="109">
         <f>Data!I65</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N88" s="109" t="str">
         <f>Data!J65</f>
@@ -13886,25 +14091,25 @@
         <f t="shared" si="36"/>
         <v>239.37788705599999</v>
       </c>
-      <c r="I89" s="71" t="str">
+      <c r="I89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J89" s="71" t="str">
+        <v>0</v>
+      </c>
+      <c r="J89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K89" s="71" t="str">
+        <v>0</v>
+      </c>
+      <c r="K89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L89" s="71" t="str">
+        <v>0</v>
+      </c>
+      <c r="L89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M89" s="71" t="str">
+        <v>0</v>
+      </c>
+      <c r="M89" s="71">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N89" s="71" t="str">
         <f t="shared" si="36"/>
@@ -13930,36 +14135,36 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>6.7810323148000395E-2</v>
+        <v>6.8902478754484062E-2</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>5.7628240796373555E-2</v>
+        <v>5.7613868555373628E-2</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>4.3022012591632332E-2</v>
-      </c>
-      <c r="I90" s="152" t="str">
+        <v>4.3005253035601952E-2</v>
+      </c>
+      <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J90" s="152" t="str">
+        <v>0</v>
+      </c>
+      <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K90" s="152" t="str">
+        <v>0</v>
+      </c>
+      <c r="K90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L90" s="152" t="str">
+        <v>0</v>
+      </c>
+      <c r="L90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M90" s="152" t="str">
+        <v>0</v>
+      </c>
+      <c r="M90" s="152">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14017,25 +14222,25 @@
         <f t="shared" si="38"/>
         <v>1.9012345679012346E-3</v>
       </c>
-      <c r="I92" s="22" t="str">
+      <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J92" s="22" t="str">
+        <v>0</v>
+      </c>
+      <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K92" s="22" t="str">
+        <v>0</v>
+      </c>
+      <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L92" s="22" t="str">
+        <v>0</v>
+      </c>
+      <c r="L92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M92" s="22" t="str">
+        <v>0</v>
+      </c>
+      <c r="M92" s="22">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14095,25 +14300,25 @@
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
         <v>0.15848033519946481</v>
       </c>
-      <c r="H95" s="6" t="str">
+      <c r="H95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="I95" s="6" t="str">
+        <v>2.3385701931392333E-2</v>
+      </c>
+      <c r="I95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="J95" s="6" t="str">
+        <v>-2.071350435795194E-2</v>
+      </c>
+      <c r="J95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="K95" s="6" t="str">
+        <v>-9.2977851747535478E-2</v>
+      </c>
+      <c r="K95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L95" s="6" t="str">
+        <v>7.1725036874421111E-2</v>
+      </c>
+      <c r="L95" s="6">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0.14622159314303684</v>
       </c>
       <c r="M95" s="6" t="str">
         <f t="shared" si="39"/>
@@ -14143,34 +14348,34 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-4.8875538945766017E-2</v>
+        <v>-6.298061092858509E-2</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>0.29470733364604884</v>
-      </c>
-      <c r="H96" s="6" t="str">
+        <v>0.29458990425488585</v>
+      </c>
+      <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I96" s="6" t="str">
+        <v>0.5361939776369542</v>
+      </c>
+      <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="J96" s="6" t="str">
+        <v>0.49082096654559049</v>
+      </c>
+      <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K96" s="6" t="str">
+        <v>0.20599923394611364</v>
+      </c>
+      <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L96" s="6" t="str">
+        <v>-0.27760269188779907</v>
+      </c>
+      <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v/>
+        <v>-5.758115549196019E-2</v>
       </c>
       <c r="M96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -14247,27 +14452,27 @@
       </c>
       <c r="H100" s="270">
         <f t="shared" si="41"/>
-        <v>5636695</v>
-      </c>
-      <c r="I100" s="270" t="str">
+        <v>90444</v>
+      </c>
+      <c r="I100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="J100" s="270" t="str">
+        <v>75536</v>
+      </c>
+      <c r="J100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="K100" s="270" t="str">
+        <v>67009</v>
+      </c>
+      <c r="K100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="L100" s="270" t="str">
+        <v>67254</v>
+      </c>
+      <c r="L100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="M100" s="270" t="str">
+        <v>68273</v>
+      </c>
+      <c r="M100" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>52678</v>
       </c>
       <c r="N100" s="270" t="str">
         <f t="shared" si="41"/>
@@ -14300,31 +14505,31 @@
       <c r="F101" s="86"/>
       <c r="G101" s="282">
         <f>IF(G$4="","",Data!D77)</f>
-        <v>715301</v>
-      </c>
-      <c r="H101" s="282" t="str">
+        <v>3508</v>
+      </c>
+      <c r="H101" s="282">
         <f>IF(H$4="","",Data!E77)</f>
-        <v/>
-      </c>
-      <c r="I101" s="282" t="str">
+        <v>2918</v>
+      </c>
+      <c r="I101" s="282">
         <f>IF(I$4="","",Data!F77)</f>
-        <v/>
-      </c>
-      <c r="J101" s="282" t="str">
+        <v>2670</v>
+      </c>
+      <c r="J101" s="282">
         <f>IF(J$4="","",Data!G77)</f>
-        <v/>
-      </c>
-      <c r="K101" s="282" t="str">
+        <v>3610</v>
+      </c>
+      <c r="K101" s="282">
         <f>IF(K$4="","",Data!H77)</f>
-        <v/>
-      </c>
-      <c r="L101" s="282" t="str">
+        <v>2800</v>
+      </c>
+      <c r="L101" s="282">
         <f>IF(L$4="","",Data!I77)</f>
-        <v/>
-      </c>
-      <c r="M101" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="M101" s="282">
         <f>IF(M$4="","",Data!J77)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N101" s="282" t="str">
         <f>IF(N$4="","",Data!K77)</f>
@@ -14357,31 +14562,31 @@
       <c r="F102" s="86"/>
       <c r="G102" s="282">
         <f>IF(G$4="","",Data!D78)</f>
-        <v>23</v>
-      </c>
-      <c r="H102" s="282" t="str">
+        <v>2</v>
+      </c>
+      <c r="H102" s="282">
         <f>IF(H$4="","",Data!E78)</f>
-        <v/>
-      </c>
-      <c r="I102" s="282" t="str">
+        <v>8</v>
+      </c>
+      <c r="I102" s="282">
         <f>IF(I$4="","",Data!F78)</f>
-        <v/>
-      </c>
-      <c r="J102" s="282" t="str">
+        <v>8</v>
+      </c>
+      <c r="J102" s="282">
         <f>IF(J$4="","",Data!G78)</f>
-        <v/>
-      </c>
-      <c r="K102" s="282" t="str">
+        <v>24</v>
+      </c>
+      <c r="K102" s="282">
         <f>IF(K$4="","",Data!H78)</f>
-        <v/>
-      </c>
-      <c r="L102" s="282" t="str">
+        <v>18</v>
+      </c>
+      <c r="L102" s="282">
         <f>IF(L$4="","",Data!I78)</f>
-        <v/>
-      </c>
-      <c r="M102" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="M102" s="282">
         <f>IF(M$4="","",Data!J78)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N102" s="282" t="str">
         <f>IF(N$4="","",Data!K78)</f>
@@ -14418,27 +14623,27 @@
       </c>
       <c r="H103" s="270">
         <f>Data!D79</f>
-        <v>2524058</v>
-      </c>
-      <c r="I103" s="270" t="str">
+        <v>20718</v>
+      </c>
+      <c r="I103" s="270">
         <f>Data!E79</f>
-        <v/>
-      </c>
-      <c r="J103" s="270" t="str">
+        <v>18334</v>
+      </c>
+      <c r="J103" s="270">
         <f>Data!F79</f>
-        <v/>
-      </c>
-      <c r="K103" s="270" t="str">
+        <v>17882</v>
+      </c>
+      <c r="K103" s="270">
         <f>Data!G79</f>
-        <v/>
-      </c>
-      <c r="L103" s="270" t="str">
+        <v>16199</v>
+      </c>
+      <c r="L103" s="270">
         <f>Data!H79</f>
-        <v/>
-      </c>
-      <c r="M103" s="270" t="str">
+        <v>15542</v>
+      </c>
+      <c r="M103" s="270">
         <f>Data!I79</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="N103" s="270" t="str">
         <f>Data!J79</f>
@@ -14475,27 +14680,27 @@
       </c>
       <c r="H104" s="270">
         <f>Data!D80</f>
-        <v>3112637</v>
-      </c>
-      <c r="I104" s="270" t="str">
+        <v>69726</v>
+      </c>
+      <c r="I104" s="270">
         <f>Data!E80</f>
-        <v/>
-      </c>
-      <c r="J104" s="270" t="str">
+        <v>57202</v>
+      </c>
+      <c r="J104" s="270">
         <f>Data!F80</f>
-        <v/>
-      </c>
-      <c r="K104" s="270" t="str">
+        <v>49127</v>
+      </c>
+      <c r="K104" s="270">
         <f>Data!G80</f>
-        <v/>
-      </c>
-      <c r="L104" s="270" t="str">
+        <v>51055</v>
+      </c>
+      <c r="L104" s="270">
         <f>Data!H80</f>
-        <v/>
-      </c>
-      <c r="M104" s="270" t="str">
+        <v>52731</v>
+      </c>
+      <c r="M104" s="270">
         <f>Data!I80</f>
-        <v/>
+        <v>43678</v>
       </c>
       <c r="N104" s="270" t="str">
         <f>Data!J80</f>
@@ -14555,31 +14760,31 @@
       <c r="F107" s="25"/>
       <c r="G107" s="91">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
-        <v>21.740350130691144</v>
-      </c>
-      <c r="H107" s="91" t="e">
+        <v>0.10661965837942983</v>
+      </c>
+      <c r="H107" s="91">
         <f t="shared" si="42"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I107" s="91" t="str">
+        <v>0.10274286116686032</v>
+      </c>
+      <c r="I107" s="91">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="J107" s="91" t="str">
+        <v>9.6209282213894493E-2</v>
+      </c>
+      <c r="J107" s="91">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="K107" s="91" t="str">
+        <v>0.12738628744839267</v>
+      </c>
+      <c r="K107" s="91">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="L107" s="91" t="str">
+        <v>8.9617206503648697E-2</v>
+      </c>
+      <c r="L107" s="91">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="M107" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="M107" s="91">
         <f t="shared" si="42"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N107" s="91" t="str">
         <f t="shared" si="42"/>
@@ -14612,31 +14817,31 @@
       <c r="F108" s="25"/>
       <c r="G108" s="91">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>6.9904565072032097E-4</v>
-      </c>
-      <c r="H108" s="91" t="e">
+        <v>6.0786578323506167E-5</v>
+      </c>
+      <c r="H108" s="91">
         <f t="shared" si="43"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I108" s="91" t="str">
+        <v>2.8168022252737579E-4</v>
+      </c>
+      <c r="I108" s="91">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="J108" s="91" t="str">
+        <v>2.8826751225136929E-4</v>
+      </c>
+      <c r="J108" s="91">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="K108" s="91" t="str">
+        <v>8.4688944564028366E-4</v>
+      </c>
+      <c r="K108" s="91">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="L108" s="91" t="str">
+        <v>5.7611061323774163E-4</v>
+      </c>
+      <c r="L108" s="91">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="M108" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="M108" s="91">
         <f t="shared" si="43"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N108" s="91" t="str">
         <f t="shared" si="43"/>
@@ -14704,31 +14909,31 @@
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>75.664317801462175</v>
+        <v>0.90117149652074346</v>
       </c>
       <c r="H112" s="251">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>111.20312280208186</v>
-      </c>
-      <c r="I112" s="251" t="str">
+        <v>1.445350963567309</v>
+      </c>
+      <c r="I112" s="251">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v/>
-      </c>
-      <c r="J112" s="251" t="str">
+        <v>1.4055555555555554</v>
+      </c>
+      <c r="J112" s="251">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v/>
-      </c>
-      <c r="K112" s="251" t="str">
+        <v>1.9486845532690804</v>
+      </c>
+      <c r="K112" s="251">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v/>
-      </c>
-      <c r="L112" s="251" t="str">
+        <v>1.6295489891135304</v>
+      </c>
+      <c r="L112" s="251">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v/>
-      </c>
-      <c r="M112" s="251" t="str">
+        <v>1.1697796934865901</v>
+      </c>
+      <c r="M112" s="251">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v/>
+        <v>1.55896404324868</v>
       </c>
       <c r="N112" s="251" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
@@ -14759,31 +14964,31 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>112.13868844970771</v>
+        <v>1.3352527272406181</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>142.07975230506705</v>
-      </c>
-      <c r="I113" s="251" t="str">
+        <v>1.8459473444906673</v>
+      </c>
+      <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v/>
-      </c>
-      <c r="J113" s="251" t="str">
+        <v>1.9083980917053105</v>
+      </c>
+      <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v/>
-      </c>
-      <c r="K113" s="251" t="str">
+        <v>2.8364457137475365</v>
+      </c>
+      <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v/>
-      </c>
-      <c r="L113" s="251" t="str">
+        <v>2.4242718899150328</v>
+      </c>
+      <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v/>
-      </c>
-      <c r="M113" s="251" t="str">
+        <v>1.5418683736623411</v>
+      </c>
+      <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v/>
+        <v>1.7759880656758302</v>
       </c>
       <c r="N113" s="251" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -14817,7 +15022,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>16yrs Projection</v>
+        <v>11yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14872,39 +15077,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.30032548054664621</v>
+        <v>0.30038355985579485</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.26872572227796993</v>
-      </c>
-      <c r="I116" s="22" t="str">
+        <v>0.26880207080746388</v>
+      </c>
+      <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="J116" s="22" t="str">
+        <v>0.1790712630816727</v>
+      </c>
+      <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="K116" s="22" t="str">
+        <v>0.11762785312832116</v>
+      </c>
+      <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="L116" s="22" t="str">
+        <v>8.8466945115441412E-2</v>
+      </c>
+      <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="M116" s="22" t="str">
+        <v>0.13124666849019853</v>
+      </c>
+      <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v/>
+        <v>0.15962941141110426</v>
       </c>
       <c r="N116" s="22" t="str">
         <f t="shared" si="44"/>
@@ -14941,27 +15146,27 @@
       </c>
       <c r="H117" s="40">
         <f t="shared" si="45"/>
-        <v>5.0385908763912182E-3</v>
-      </c>
-      <c r="I117" s="40" t="str">
+        <v>0.31401751359957542</v>
+      </c>
+      <c r="I117" s="40">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="J117" s="40" t="str">
+        <v>0.36740097436983687</v>
+      </c>
+      <c r="J117" s="40">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="K117" s="40" t="str">
+        <v>0.42291333999910458</v>
+      </c>
+      <c r="K117" s="40">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="L117" s="40" t="str">
+        <v>0.46456716329140274</v>
+      </c>
+      <c r="L117" s="40">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="M117" s="40" t="str">
+        <v>0.42700628359673665</v>
+      </c>
+      <c r="M117" s="40">
         <f t="shared" si="45"/>
-        <v/>
+        <v>0.48282015262538441</v>
       </c>
       <c r="N117" s="40" t="str">
         <f t="shared" si="45"/>
@@ -15000,27 +15205,27 @@
       </c>
       <c r="H118" s="15">
         <f t="shared" si="46"/>
-        <v>1.810906636398655</v>
-      </c>
-      <c r="I118" s="15" t="str">
+        <v>1.2971344978917476</v>
+      </c>
+      <c r="I118" s="15">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="J118" s="15" t="str">
+        <v>1.3205132687668264</v>
+      </c>
+      <c r="J118" s="15">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="K118" s="15" t="str">
+        <v>1.3639953589675737</v>
+      </c>
+      <c r="K118" s="15">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="L118" s="15" t="str">
+        <v>1.317285280579767</v>
+      </c>
+      <c r="L118" s="15">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="M118" s="15" t="str">
+        <v>1.2947412338093343</v>
+      </c>
+      <c r="M118" s="15">
         <f t="shared" si="46"/>
-        <v/>
+        <v>1.2060533907230184</v>
       </c>
       <c r="N118" s="15" t="str">
         <f t="shared" si="46"/>
@@ -15046,41 +15251,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.11316501697760267</v>
+        <v>0.11150835231775919</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C119</f>
-        <v>0.11316501697760267</v>
+        <v>0.11150835231775919</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11898024034853405</v>
+        <v>0.11900324968543483</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>2.4519657250159986E-3</v>
-      </c>
-      <c r="I119" s="99" t="str">
+        <v>0.10948925240230017</v>
+      </c>
+      <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="J119" s="99" t="str">
+        <v>8.6877831073084513E-2</v>
+      </c>
+      <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="K119" s="99" t="str">
+        <v>6.7853842689427263E-2</v>
+      </c>
+      <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="L119" s="99" t="str">
+        <v>5.4138894000330062E-2</v>
+      </c>
+      <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="M119" s="99" t="str">
+        <v>7.2561379956662259E-2</v>
+      </c>
+      <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v/>
+        <v>9.2953304863547456E-2</v>
       </c>
       <c r="N119" s="99" t="str">
         <f t="shared" si="47"/>
@@ -15170,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3773630992459558</v>
+        <v>2.3396801234746398</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7974090094061079</v>
+        <v>2.7981068454908331</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0319030824932236</v>
-      </c>
-      <c r="I123" s="159" t="str">
+        <v>2.0326949344451499</v>
+      </c>
+      <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J123" s="159" t="str">
+        <v>1.4039745276570839</v>
+      </c>
+      <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K123" s="159" t="str">
+        <v>0.96315206841881096</v>
+      </c>
+      <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="L123" s="159" t="str">
+        <v>0.78918124509286136</v>
+      </c>
+      <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="M123" s="159" t="str">
+        <v>1.1569829277839083</v>
+      </c>
+      <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v/>
+        <v>1.2748565787241721</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15227,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.8700323438171748E-2</v>
+        <v>5.776987959196641E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.907182739274341E-2</v>
+        <v>6.9089057913353902E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.0170446481314163E-2</v>
-      </c>
-      <c r="I124" s="74" t="str">
+        <v>5.0189998381361726E-2</v>
+      </c>
+      <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="J124" s="74" t="str">
+        <v>3.4666037719927996E-2</v>
+      </c>
+      <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="K124" s="74" t="str">
+        <v>2.3781532553550887E-2</v>
+      </c>
+      <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="L124" s="74" t="str">
+        <v>1.9485956668959539E-2</v>
+      </c>
+      <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M124" s="74" t="str">
+        <v>2.8567479698368106E-2</v>
+      </c>
+      <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v/>
+        <v>3.1477940215411657E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15290,25 +15495,25 @@
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.6462510841897337E-2</v>
       </c>
-      <c r="I125" s="22" t="str">
+      <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="J125" s="22" t="str">
+        <v>4.1459320100535109E-2</v>
+      </c>
+      <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="K125" s="22" t="str">
+        <v>3.0490867790412698E-2</v>
+      </c>
+      <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="L125" s="22" t="str">
+        <v>2.5534811134716548E-2</v>
+      </c>
+      <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="M125" s="22" t="str">
+        <v>3.3167456080428086E-2</v>
+      </c>
+      <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
+        <v>3.1586918781576274E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16075,7 +16280,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16114,7 +16319,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>26058.935070518506</v>
+        <v>25989.935070518506</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16125,7 +16330,7 @@
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
-        <v>-3916</v>
+        <v>-4054</v>
       </c>
       <c r="J5" s="305"/>
     </row>
@@ -16135,7 +16340,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>126481.41127442229</v>
+        <v>124476.58670299369</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16157,7 +16362,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16168,14 +16373,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>42476.935070518506</v>
+        <v>42407.935070518506</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>42476.935070518506</v>
+        <v>42407.935070518506</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16198,7 +16403,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>168958.3463449408</v>
+        <v>166884.52177351218</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16209,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.511823539237037</v>
+        <v>15.486625962659762</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16221,7 +16426,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16259,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191815.03143848441</v>
+        <v>189460.65987903293</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16281,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16330,7 +16535,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16338,7 +16543,7 @@
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>429</v>
@@ -16371,14 +16576,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16390,21 +16595,21 @@
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="E18" s="308" t="s">
         <v>423</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H18" s="140" t="s">
         <v>97</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>57.280283896599371</v>
+        <v>50.508362188748997</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16471,27 +16676,27 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>9622.5610300838798</v>
+        <v>9481.6927898671875</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>6665.3763926295287</v>
+        <v>5893.5649559544136</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>2.3855917147759254E-2</v>
+        <v>-8.0119798039642642E-2</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>0.19786252018493328</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16499,7 +16704,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>6214.803163290936</v>
+        <v>5495.1654600973552</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16520,19 +16725,19 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>9852.1160487668203</v>
+        <v>9707.8872674827671</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>6824.3850596107313</v>
+        <v>6034.1613532486008</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16540,7 +16745,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16548,7 +16753,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>5932.9258672671695</v>
+        <v>5245.9278993255639</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16569,27 +16774,27 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>10087.147312956313</v>
+        <v>9939.4778218156243</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>6987.1870241772122</v>
+        <v>6178.1118065479104</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16597,7 +16802,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>5663.8333381822786</v>
+        <v>5007.9947045734207</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16626,19 +16831,19 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>10327.785463511442</v>
+        <v>10176.593181224849</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>7153.8727789218829</v>
+        <v>6325.4963299345109</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
@@ -16646,7 +16851,7 @@
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796611</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16654,7 +16859,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>5406.9457128547047</v>
+        <v>4780.8531574099216</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16683,19 +16888,19 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>10574.164257848806</v>
+        <v>10419.365145002605</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>7324.5349752214561</v>
+        <v>6476.3968462998864</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16703,7 +16908,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16711,7 +16916,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>5161.7094282545468</v>
+        <v>4564.0137941526327</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16740,19 +16945,19 @@
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>10826.420644290847</v>
+        <v>10667.92865663404</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>7499.2684747362055</v>
+        <v>6630.8972328812279</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
@@ -16760,7 +16965,7 @@
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16768,7 +16973,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>4927.5960286394366</v>
+        <v>4357.0093511302275</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16789,27 +16994,27 @@
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>11084.694838187843</v>
+        <v>10922.421878804909</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>7678.1704021383166</v>
+        <v>6789.0833678841482</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.19786252018493328</v>
+        <v>0.17495120250796611</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16817,7 +17022,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>4704.1010267937418</v>
+        <v>4159.3937577834995</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16838,19 +17043,19 @@
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>11349.130399855849</v>
+        <v>11182.986270198555</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>7861.3401990981074</v>
+        <v>6951.0431782176247</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
@@ -16858,7 +17063,7 @@
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796611</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16866,7 +17071,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>4490.7428169171317</v>
+        <v>3970.7411754350496</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16887,19 +17092,19 @@
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>11619.874314373928</v>
+        <v>11449.766664124945</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>8048.8796795581438</v>
+        <v>7116.8666883676842</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
@@ -16907,7 +17112,7 @@
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0.17495120250796614</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16915,7 +17120,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>4287.0616368199553</v>
+        <v>3790.6450796563408</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -16936,27 +17141,27 @@
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>11897.077073285012</v>
+        <v>11722.911349025488</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>8240.8930863259684</v>
+        <v>7286.646070437032</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.19786252018493333</v>
+        <v>0.17495120250796611</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -16964,32 +17169,32 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>4092.6185771890641</v>
+        <v>3618.7173842547172</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>42643.180432204943</v>
+        <v>0</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>12180.892758245807</v>
+        <v>0</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -16997,48 +17202,48 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>8437.4871490169044</v>
+        <v>0</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0.19786252018493333</v>
+        <v>0</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0.46305192135840806</v>
+        <v>0</v>
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>3906.994635789154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>43660.472611512581</v>
+        <v>0</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>12471.479126672262</v>
+        <v>0</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17046,48 +17251,48 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>8638.7711433791374</v>
+        <v>0</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0.19786252018493333</v>
+        <v>0</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0.43175004322462285</v>
+        <v>0</v>
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>3729.7898145615673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>44702.033228764849</v>
+        <v>0</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>12768.997699428168</v>
+        <v>0</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17095,23 +17300,23 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>8844.8569520340443</v>
+        <v>0</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0.40256414286678116</v>
+        <v>0</v>
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>3560.6222576748755</v>
+        <v>0</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17125,26 +17330,26 @@
     <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>45768.441229806653</v>
+        <v>0</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>13073.613850605658</v>
+        <v>0</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17152,23 +17357,23 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>9055.859126665553</v>
+        <v>0</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0.1978625201849333</v>
+        <v>0</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0.37535118216016894</v>
+        <v>0</v>
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>3399.1274286698704</v>
+        <v>0</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17182,26 +17387,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>46860.289371767016</v>
+        <v>0</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0.2856469108257827</v>
+        <v>0</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>13385.496899447506</v>
+        <v>0</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17209,23 +17414,23 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>9271.8949516930661</v>
+        <v>0</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0.19786252018493328</v>
+        <v>0</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0.34997779222393377</v>
+        <v>0</v>
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>3244.9573249257764</v>
+        <v>0</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18009,11 +18214,11 @@
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>47797.495159202357</v>
+        <v>42482.583059166755</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18021,19 +18226,19 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>13653.206837436453</v>
+        <v>11957.369576005998</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
-        <v>0</v>
+        <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>130445.97035485417</v>
+        <v>102515.57230132102</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18042,11 +18247,11 @@
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.34997779222393377</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>45653.19270930058</v>
+        <v>50911.610095721546</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18059,7 +18264,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>114377.02176713079</v>
+        <v>95902.071859540272</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18083,7 +18288,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>114377.02176713079</v>
+        <v>95902.071859540272</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18091,19 +18296,19 @@
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E55" s="123">
         <f>C91</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F55" s="123">
         <f>C90</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18118,19 +18323,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>91468.587518607266</v>
+        <v>80877.062331605935</v>
       </c>
       <c r="C56" s="118">
-        <v>93297.959268979408</v>
+        <v>84920.915448186221</v>
       </c>
       <c r="D56" s="118">
-        <v>95127.331019351579</v>
+        <v>87347.227318134406</v>
       </c>
       <c r="E56" s="118">
-        <v>98786.074520095892</v>
+        <v>89773.539188082563</v>
       </c>
       <c r="F56" s="118">
-        <v>105188.87564639836</v>
+        <v>90582.309811398634</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18144,19 +18349,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>91355.394086463377</v>
+        <v>80776.976034054125</v>
       </c>
       <c r="C57" s="118">
-        <v>94922.324052462645</v>
+        <v>88774.841872968304</v>
       </c>
       <c r="D57" s="118">
-        <v>98557.482335492125</v>
+        <v>93754.545012303643</v>
       </c>
       <c r="E57" s="118">
-        <v>106032.48385264167</v>
+        <v>98869.985878629072</v>
       </c>
       <c r="F57" s="118">
-        <v>119770.43405906898</v>
+        <v>100605.29677340202</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18170,19 +18375,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>91249.852424790719</v>
+        <v>80683.655476896238</v>
       </c>
       <c r="C58" s="118">
-        <v>96467.174475915221</v>
+        <v>92547.916694433254</v>
       </c>
       <c r="D58" s="118">
-        <v>101883.6896723557</v>
+        <v>100206.66912391459</v>
       </c>
       <c r="E58" s="118">
-        <v>113329.56737632416</v>
+        <v>108284.49014576804</v>
       </c>
       <c r="F58" s="118">
-        <v>135405.67151787665</v>
+        <v>111072.19224887405</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18196,19 +18401,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>91151.445281039982</v>
+        <v>80596.643302390061</v>
       </c>
       <c r="C59" s="118">
-        <v>97936.40285066732</v>
+        <v>96241.836100063287</v>
       </c>
       <c r="D59" s="118">
-        <v>105109.10284749611</v>
+        <v>106703.9129845578</v>
       </c>
       <c r="E59" s="118">
-        <v>120677.67945611634</v>
+        <v>118028.17288378603</v>
       </c>
       <c r="F59" s="118">
-        <v>152170.72800051421</v>
+        <v>122002.65652162806</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18222,19 +18427,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>91059.690368451906</v>
+        <v>80515.513069750275</v>
       </c>
       <c r="C60" s="118">
-        <v>99333.710955326649</v>
+        <v>99858.260692987795</v>
       </c>
       <c r="D60" s="118">
-        <v>108236.77622945048</v>
+        <v>113246.59211695376</v>
       </c>
       <c r="E60" s="118">
-        <v>128077.1769350679</v>
+        <v>128112.54382942703</v>
       </c>
       <c r="F60" s="118">
-        <v>170147.24544110463</v>
+        <v>133417.22061065788</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18248,19 +18453,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>90974.138002402397</v>
+        <v>80439.867165191026</v>
       </c>
       <c r="C61" s="118">
-        <v>100662.61936255509</v>
+        <v>103398.8162385083</v>
       </c>
       <c r="D61" s="118">
-        <v>111269.67163013348</v>
+        <v>119835.02425027557</v>
       </c>
       <c r="E61" s="118">
-        <v>135528.41915163447</v>
+        <v>138549.51515778276</v>
       </c>
       <c r="F61" s="118">
-        <v>189422.76530747191</v>
+        <v>145337.32483416691</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18274,19 +18479,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>90894.368896528758</v>
+        <v>80369.334853247667</v>
       </c>
       <c r="C62" s="118">
-        <v>101926.47630928988</v>
+        <v>106865.09439496195</v>
       </c>
       <c r="D62" s="118">
-        <v>114210.66110958369</v>
+        <v>126469.52933557864</v>
       </c>
       <c r="E62" s="118">
-        <v>143031.76795712812</v>
+        <v>149351.41555356351</v>
       </c>
       <c r="F62" s="118">
-        <v>210091.15490777261</v>
+        <v>157785.35908156098</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18300,19 +18505,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>90819.992107835351</v>
+        <v>80303.570459827286</v>
       </c>
       <c r="C63" s="118">
-        <v>103128.46613275789</v>
+        <v>110258.65342925221</v>
       </c>
       <c r="D63" s="118">
-        <v>117062.52969571718</v>
+        <v>133150.42956133839</v>
       </c>
       <c r="E63" s="118">
-        <v>150587.58773328952</v>
+        <v>160531.00477437157</v>
       </c>
       <c r="F63" s="118">
-        <v>232253.06450250058</v>
+        <v>170784.70486904934</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18326,19 +18531,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>90750.643120708643</v>
+        <v>80242.251678083339</v>
       </c>
       <c r="C64" s="118">
-        <v>104271.61729353867</v>
+        <v>113581.01891736855</v>
       </c>
       <c r="D64" s="118">
-        <v>119827.97802166484</v>
+        <v>139878.04936909641</v>
       </c>
       <c r="E64" s="118">
-        <v>158196.24540998353</v>
+        <v>172101.48872317988</v>
       </c>
       <c r="F64" s="118">
-        <v>256016.4174478965</v>
+        <v>184359.77925784842</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18352,19 +18557,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>90685.982060450653</v>
+        <v>80185.077988811594</v>
       </c>
       <c r="C65" s="118">
-        <v>105358.81000588962</v>
+        <v>116833.68443020975</v>
       </c>
       <c r="D65" s="118">
-        <v>122509.62488318986</v>
+        <v>146652.7154692164</v>
       </c>
       <c r="E65" s="118">
-        <v>165858.11048301807</v>
+        <v>184076.53504782065</v>
       </c>
       <c r="F65" s="118">
-        <v>281496.93575764506</v>
+        <v>198536.08071748007</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18378,19 +18583,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>90422.624222259867</v>
+        <v>79952.215441431166</v>
       </c>
       <c r="C66" s="277">
-        <v>110046.71223527062</v>
+        <v>132101.63041861926</v>
       </c>
       <c r="D66" s="118">
-        <v>134747.07269924192</v>
+        <v>181243.33604396001</v>
       </c>
       <c r="E66" s="118">
-        <v>204978.66103406638</v>
+        <v>250532.97451881587</v>
       </c>
       <c r="F66" s="118">
-        <v>439327.71873727965</v>
+        <v>279410.35540564789</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18413,19 +18618,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>90237.032011833828</v>
+        <v>79788.113718882625</v>
       </c>
       <c r="C67" s="277">
-        <v>113694.19207382732</v>
+        <v>145833.84578558247</v>
       </c>
       <c r="D67" s="118">
-        <v>145239.38104522601</v>
+        <v>217060.45313739951</v>
       </c>
       <c r="E67" s="118">
-        <v>245486.32804220889</v>
+        <v>329449.0462823055</v>
       </c>
       <c r="F67" s="118">
-        <v>663042.36028814327</v>
+        <v>379852.0445815305</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18448,19 +18653,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>90106.242403263823</v>
+        <v>79672.468778782364</v>
       </c>
       <c r="C68" s="277">
-        <v>116532.15850778905</v>
+        <v>158184.80242557934</v>
       </c>
       <c r="D68" s="118">
-        <v>154235.41813416887</v>
+        <v>254147.55523529719</v>
       </c>
       <c r="E68" s="118">
-        <v>287430.29517276818</v>
+        <v>423160.75326140609</v>
       </c>
       <c r="F68" s="118">
-        <v>980142.9910991129</v>
+        <v>504595.45604832424</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18483,19 +18688,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>90014.073008488951</v>
+        <v>79590.972058558531</v>
       </c>
       <c r="C69" s="277">
-        <v>118740.27310657469</v>
+        <v>169293.43463433982</v>
       </c>
       <c r="D69" s="118">
-        <v>161948.56195695899</v>
+        <v>292549.6728158833</v>
       </c>
       <c r="E69" s="118">
-        <v>330861.49002029671</v>
+        <v>534442.06553016673</v>
       </c>
       <c r="F69" s="118">
-        <v>1429612.0529524167</v>
+        <v>659520.35657568579</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18565,19 +18770,19 @@
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E72" s="124">
         <f>E55</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F72" s="124">
         <f>F55</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G72" s="124"/>
       <c r="H72" s="124"/>
@@ -18592,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18623,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>48.914529893082637</v>
+        <v>45.021495114047241</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>49.58258402015953</v>
+        <v>46.498238571616604</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>50.250638147236444</v>
+        <v>47.384284646158235</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>51.5867464013903</v>
+        <v>48.270330720699853</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>53.924935846159464</v>
+        <v>48.565679412213733</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18654,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>48.873193658669727</v>
+        <v>44.984945372787848</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>50.175773237858799</v>
+        <v>47.905624168886654</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>51.503268588687092</v>
+        <v>49.724123461430153</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>54.233006605261409</v>
+        <v>51.592191765136825</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>59.249862436294052</v>
+        <v>52.225896535519766</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18685,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>48.834651715161179</v>
+        <v>44.950866359958574</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>50.739925221125212</v>
+        <v>49.283484194185988</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.717940531911971</v>
+        <v>52.080324785899769</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>56.897772125243527</v>
+        <v>55.030201797141501</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>64.959573931543233</v>
+        <v>56.048221177107393</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18716,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>48.798715171097264</v>
+        <v>44.919091056621262</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.276461373042928</v>
+        <v>50.632438065108403</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>53.895804234433051</v>
+        <v>54.453003042708346</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.581172369141612</v>
+        <v>58.588421970125381</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>71.081875301740524</v>
+        <v>60.039832924033391</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18747,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>48.765207903904802</v>
+        <v>44.889463734162241</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.786733517524105</v>
+        <v>51.953092204473009</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>55.037975097483802</v>
+        <v>56.842273455158939</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.28333764971029</v>
+        <v>62.271055435870913</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>77.646580733653693</v>
+        <v>64.20822934040369</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18778,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>48.733965696732348</v>
+        <v>44.861839191076882</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>52.272027305282428</v>
+        <v>53.246040312941865</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>56.14553472226028</v>
+        <v>59.248252052311976</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>65.004399190982255</v>
+        <v>66.082452309509677</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>84.685658819154952</v>
+        <v>68.561240050272886</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18810,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>48.704835433634493</v>
+        <v>44.836082041346955</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>52.733565453080566</v>
+        <v>54.511863635918374</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>57.219531934164756</v>
+        <v>61.671055674619922</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>67.744489134640759</v>
+        <v>70.027114808100833</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>92.233388234844014</v>
+        <v>73.107041444262194</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18841,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>48.677674349160959</v>
+        <v>44.81206605092278</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>53.17251082441306</v>
+        <v>55.751131224846411</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>58.260983776011493</v>
+        <v>64.110801979601376</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>70.503740546436703</v>
+        <v>74.109702568880493</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>100.32652467124716</v>
+        <v>77.854172037519049</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18873,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>48.652349328672827</v>
+        <v>44.789673519058745</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>53.5899693593866</v>
+        <v>56.9644001930277</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>59.27087647113563</v>
+        <v>66.567609447554688</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>73.282287422650825</v>
+        <v>78.335038153463614</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>109.00447982449995</v>
+        <v>82.811548507866561</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18905,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>48.628736255956611</v>
+        <v>44.768794701469901</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>53.986992861179637</v>
+        <v>58.15221596607234</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>60.250166357316616</v>
+        <v>69.041597387311896</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>76.080264696600693</v>
+        <v>82.70811274450071</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>118.30951332216029</v>
+        <v>87.988482444266751</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18937,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>48.532562642985035</v>
+        <v>44.683757427997477</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>55.698931635260919</v>
+        <v>63.727799128690549</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>64.719065320438148</v>
+        <v>81.673478703074053</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>90.366396120589414</v>
+        <v>106.97682611585556</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>175.94651680593878</v>
+        <v>117.52233359769768</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18969,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.464787658429152</v>
+        <v>44.623830388571676</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>57.030926599697182</v>
+        <v>68.742560698033984</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>68.550670291747181</v>
+        <v>94.753254800743477</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>105.15907788007425</v>
+        <v>135.79557628162817</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>257.64313726877441</v>
+        <v>154.20185757683132</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19001,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>48.417025612379092</v>
+        <v>44.58159890692022</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>58.067301622066566</v>
+        <v>73.252911071061988</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>71.835863530017463</v>
+        <v>108.29680690423648</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>120.47627097756701</v>
+        <v>170.01743009022388</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>373.44266520445296</v>
+        <v>199.7559396485</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19033,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>48.383366983641103</v>
+        <v>44.551837749693597</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>58.873665921983985</v>
+        <v>77.309586589163928</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>74.65256689416664</v>
+        <v>122.32057934577796</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>136.33657326761312</v>
+        <v>210.65539222807635</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>537.58079716336397</v>
+        <v>256.33176638422469</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19088,15 +19293,15 @@
       </c>
       <c r="C90" s="130">
         <f>Scenarios!C29</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>175.94651680593878</v>
+        <v>87.988482444266751</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19116,15 +19321,15 @@
       </c>
       <c r="C91" s="130">
         <f>Scenarios!C22</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>90.366396120589414</v>
+        <v>82.70811274450071</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19144,15 +19349,15 @@
       </c>
       <c r="C92" s="130">
         <f>Scenarios!C23</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>64.719065320438148</v>
+        <v>69.041597387311896</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19172,15 +19377,15 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>55.698931635260919</v>
+        <v>58.15221596607234</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19204,11 +19409,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>48.532562642985035</v>
+        <v>44.768794701469901</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19417,7 +19622,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>7660.3089609457529</v>
+        <v>7662.219886375362</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19430,7 +19635,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19458,9 +19663,9 @@
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="249" t="e">
+      <c r="C12" s="249">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>8.8839846355660779E-2</v>
       </c>
       <c r="D12" s="469"/>
       <c r="E12" s="469"/>
@@ -19471,9 +19676,9 @@
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="249" t="e">
+      <c r="C13" s="249">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>0.42336141371279012</v>
       </c>
       <c r="D13" s="469"/>
       <c r="E13" s="469"/>
@@ -19484,9 +19689,9 @@
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="249" t="e">
+      <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>0.41173288969918787</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19516,7 +19721,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="450" t="s">
         <v>544</v>
@@ -19560,15 +19765,15 @@
         <v>445</v>
       </c>
       <c r="C22" s="324">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="D22" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>90.366396120589414</v>
+        <v>82.70811274450071</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19584,15 +19789,15 @@
         <v>437</v>
       </c>
       <c r="C23" s="324">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D23" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>64.719065320438148</v>
+        <v>69.041597387311896</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19607,15 +19812,15 @@
         <v>446</v>
       </c>
       <c r="C24" s="324">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D24" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>55.698931635260919</v>
+        <v>58.15221596607234</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19631,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>67.593498059174095</v>
+        <v>69.052555103439772</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19670,15 +19875,15 @@
         <v>444</v>
       </c>
       <c r="C29" s="324">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D29" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>175.94651680593878</v>
+        <v>87.988482444266751</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19697,11 +19902,11 @@
       </c>
       <c r="D30" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>48.532562642985035</v>
+        <v>44.768794701469901</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19757,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.27247777422564884</v>
+        <v>0.20690450680305575</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19766,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19777,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.10551956605004355</v>
+        <v>5.2860785284096642E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19786,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>82.893404100379342</v>
+        <v>70.678756184465314</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19824,7 +20029,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -19864,7 +20069,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -19889,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>57.280283896599371</v>
+        <v>50.508362188748997</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19956,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.1871297687383314</v>
+        <v>0.21911288198452494</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20034,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>37.730270414373841</v>
+        <v>32.170576324290074</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>37.988158443504474</v>
+        <v>32.428464353420708</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20046,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54172278414935271</v>
+        <v>0.54118512967623145</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20059,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>47.970719965497302</v>
+        <v>40.902057977121132</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>48.26984033586767</v>
+        <v>41.201178347491499</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20071,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41768780206666922</v>
+        <v>0.41706418488802965</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20105,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>59.414708901322747</v>
+        <v>50.659733060574766</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>59.757298545206034</v>
+        <v>51.002322704458052</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20117,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27910671308849566</v>
+        <v>0.27839246956544494</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20130,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>67.193625136208539</v>
+        <v>57.292397383047152</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>67.564582418467111</v>
+        <v>57.663354665305718</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20142,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18492209179092067</v>
+        <v>0.18414870636928793</v>
       </c>
     </row>
   </sheetData>
@@ -20190,7 +20395,7 @@
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
-        <v>46101</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20278,7 +20483,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.27247777422564884</v>
+        <v>0.20690450680305575</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>82.893404100379342</v>
+        <v>70.678756184465314</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20408,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>37.988158443504474</v>
+        <v>32.428464353420708</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20424,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>48.26984033586767</v>
+        <v>41.201178347491499</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20440,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>59.757298545206034</v>
+        <v>51.002322704458052</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20456,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>67.564582418467111</v>
+        <v>57.663354665305718</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20518,7 +20723,7 @@
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
-        <v>9345.3202704130126</v>
+        <v>9207.3202704130126</v>
       </c>
       <c r="D34" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20557,7 +20762,7 @@
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
-        <v>0</v>
+        <v>-650.63867420757288</v>
       </c>
       <c r="D38" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20601,7 +20806,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>71.994389576888963</v>
+        <v>72.408389576888965</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20631,7 +20836,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>53.034389576888962</v>
+        <v>53.448389576888964</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20671,7 +20876,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-2349.5886649974755</v>
+        <v>-2315.1921649974752</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20724,7 +20929,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>7660.3089609457529</v>
+        <v>7662.219886375362</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20737,7 +20942,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>6510.0726391246753</v>
+        <v>6406.883139124674</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20750,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.8700323438171748E-2</v>
+        <v>5.776987959196641E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20767,7 +20972,7 @@
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>6.7810323148000395E-2</v>
+        <v>6.8902478754484062E-2</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20787,11 +20992,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.11316501697760267</v>
+        <v>0.11150835231775919</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>0.11898024034853405</v>
+        <v>0.11900324968543483</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20801,11 +21006,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.28564691082578264</v>
+        <v>0.28146521974317368</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.30032548054664621</v>
+        <v>0.30038355985579485</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -20923,7 +21128,7 @@
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.3813715405821454E-2</v>
+        <v>3.432051788351935E-2</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -20937,7 +21142,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>26058.935070518506</v>
+        <v>25989.935070518506</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20963,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5162610429223751</v>
+        <v>9.4910634663450999</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21007,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.511823539237037</v>
+        <v>15.486625962659762</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.700592324587049</v>
+        <v>60.943268361595621</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21221,15 +21426,15 @@
       </c>
       <c r="C118" s="396">
         <f>DCF!C90</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>175.95 HKD</v>
+        <v>87.99 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21244,15 +21449,15 @@
       </c>
       <c r="C119" s="401">
         <f>DCF!C91</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>90.37 HKD</v>
+        <v>82.71 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21266,15 +21471,15 @@
       </c>
       <c r="C120" s="401">
         <f>DCF!C92</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>64.72 HKD</v>
+        <v>69.04 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21288,15 +21493,15 @@
       </c>
       <c r="C121" s="401">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>55.7 HKD</v>
+        <v>58.15 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21314,11 +21519,11 @@
       </c>
       <c r="D122" s="402">
         <f>DCF!D94</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>48.53 HKD</v>
+        <v>44.77 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21340,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>82.893404100379342</v>
+        <v>70.678756184465314</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21447,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>37.730270414373841</v>
+        <v>32.170576324290074</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>37.988158443504474</v>
+        <v>32.428464353420708</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21468,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>47.970719965497302</v>
+        <v>40.902057977121132</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>48.26984033586767</v>
+        <v>41.201178347491499</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21508,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>59.414708901322747</v>
+        <v>50.659733060574766</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>59.757298545206034</v>
+        <v>51.002322704458052</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21529,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>67.193625136208539</v>
+        <v>57.292397383047152</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>67.564582418467111</v>
+        <v>57.663354665305718</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394D5F9D-93E4-4CB5-8849-C3BDEA8E2460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9543B94-43E8-41DE-B865-8F87B6D942E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>40.5</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>125906.550984</v>
+        <v>122300.33865952</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20690450680305575</v>
+        <v>0.2189068073383065</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1352800000000001</v>
+        <v>1.1359030000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>70.678756184465314</v>
+        <v>70.717542091997316</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.428464353420708</v>
+        <v>32.446118385069326</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.201178347491499</v>
+        <v>41.223623895831778</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.002322704458052</v>
+        <v>51.030122906784129</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>57.663354665305718</v>
+        <v>57.694794630397716</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.776987959196641E-2</v>
+        <v>5.9505949518600436E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5061728395061726E-3</v>
+        <v>3.6095577020843917E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11539759707853772</v>
+        <v>-0.11546092304480152</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4910634663450999</v>
+        <v>9.4962718136598898</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1109600933931976</v>
+        <v>6.1143135640243935</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.486625962659762</v>
+        <v>15.495124454639482</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.418847858509771</v>
+        <v>11.42511410315061</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.99 HKD</v>
+        <v>88.04 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8679003736245997E-2</v>
+        <v>-6.8679957441694001E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.71 HKD</v>
+        <v>82.75 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9231373085065401E-2</v>
+        <v>-4.92323661544651E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.04 HKD</v>
+        <v>69.08 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8833378149183783E-3</v>
+        <v>9.8822185069326659E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.15 HKD</v>
+        <v>58.18 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9479432488544338E-2</v>
+        <v>6.9478175531119207E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.77 HKD</v>
+        <v>44.79 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1671519111623998</v>
+        <v>0.16715040486980687</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>70.678756184465314</v>
+        <v>70.717542091997316</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.170576324290074</v>
+        <v>32.188230355938693</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.428464353420708</v>
+        <v>32.446118385069326</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>40.902057977121132</v>
+        <v>40.924503525461411</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.201178347491499</v>
+        <v>41.223623895831778</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>50.659733060574766</v>
+        <v>50.687533262900843</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.002322704458052</v>
+        <v>51.030122906784129</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.292397383047152</v>
+        <v>57.323837348139151</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>57.663354665305718</v>
+        <v>57.694794630397716</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.319388850141006</v>
+        <v>29.335478254740437</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.418847858509771</v>
+        <v>11.42511410315061</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-358.74848000000003</v>
+        <v>-358.94534800000002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11539759707853772</v>
+        <v>-0.11546092304480149</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29505.85348685825</v>
+        <v>29522.045216407187</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.4910634663450999</v>
+        <v>9.4962718136598898</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>18997.775520000003</v>
+        <v>19008.200802000003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1109600933931985</v>
+        <v>6.1143135640243944</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48144.880526858251</v>
+        <v>48171.300670407189</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.486625962659762</v>
+        <v>15.495124454639482</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5061728395061726E-3</v>
+        <v>3.6095577020843917E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5061728395061726E-3</v>
+        <v>3.6095577020843917E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9012345679012346E-3</v>
+        <v>1.95729537366548E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3396801234746398</v>
+        <v>2.3409640540617414</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7981068454908331</v>
+        <v>2.7996423438390297</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0326949344451499</v>
+        <v>2.033810402826659</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4039745276570839</v>
+        <v>1.4047449773529566</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96315206841881096</v>
+        <v>0.96368061092693658</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.78918124509286136</v>
+        <v>0.78961431879775601</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1569829277839083</v>
+        <v>1.1576178375541935</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2748565787241721</v>
+        <v>1.275556173228211</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.776987959196641E-2</v>
+        <v>5.9505949518600436E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9089057913353902E-2</v>
+        <v>7.116528581187162E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.0189998381361726E-2</v>
+        <v>5.1698281719030473E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4666037719927996E-2</v>
+        <v>3.5707803186399503E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.3781532553550887E-2</v>
+        <v>2.4496202616343072E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>1.9485956668959539E-2</v>
+        <v>2.0071538352764512E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.8567479698368106E-2</v>
+        <v>2.9425974518408574E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.1477940215411657E-2</v>
+        <v>3.2423898658571704E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0170050019420522E-2</v>
+        <v>9.2828851697674908E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6462510841897337E-2</v>
+        <v>5.8127394232253229E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1459320100535109E-2</v>
+        <v>4.26818114913999E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0490867790412698E-2</v>
+        <v>3.1389937608330309E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5534811134716548E-2</v>
+        <v>2.6287744050737676E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3167456080428086E-2</v>
+        <v>3.4145449193119917E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1586918781576274E-2</v>
+        <v>3.2518307337413295E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.486625962659762</v>
+        <v>15.495124454639482</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1352800000000001</v>
+        <v>1.1359030000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>189460.65987903293</v>
+        <v>189564.62893609784</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.508362188748997</v>
+        <v>50.536079324295812</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.021495114047241</v>
+        <v>45.04620125830774</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.498238571616604</v>
+        <v>46.523755098491137</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.384284646158235</v>
+        <v>47.410287402601192</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.270330720699853</v>
+        <v>48.296819706711233</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.565679412213733</v>
+        <v>48.592330474747918</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>44.984945372787848</v>
+        <v>45.009631459891693</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>47.905624168886654</v>
+        <v>47.931913017326877</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>49.724123461430153</v>
+        <v>49.751410235544441</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.592191765136825</v>
+        <v>51.620503666579367</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.225896535519766</v>
+        <v>52.254556190883754</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>44.950866359958574</v>
+        <v>44.975533745750852</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.283484194185988</v>
+        <v>49.310529161641576</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.080324785899769</v>
+        <v>52.108904556829948</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.030201797141501</v>
+        <v>55.060400352316989</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.048221177107393</v>
+        <v>56.078978383957981</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>44.919091056621262</v>
+        <v>44.943741005293198</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.632438065108403</v>
+        <v>50.660223288942667</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.453003042708346</v>
+        <v>54.482884852390193</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>58.588421970125381</v>
+        <v>58.620573145947553</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.039832924033391</v>
+        <v>60.072780580921268</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>44.889463734162241</v>
+        <v>44.914097424446915</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.953092204473009</v>
+        <v>51.981602154831855</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>56.842273455158939</v>
+        <v>56.873466408758546</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.271055435870913</v>
+        <v>62.305227505788956</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.20822934040369</v>
+        <v>64.243464460267575</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>44.861839191076882</v>
+        <v>44.886457722026115</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.246040312941865</v>
+        <v>53.275259785772327</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.248252052311976</v>
+        <v>59.280765318667932</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.082452309509677</v>
+        <v>66.118715934156313</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>68.561240050272886</v>
+        <v>68.598863942661836</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>44.836082041346955</v>
+        <v>44.860686437717682</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.511863635918374</v>
+        <v>54.541777746133633</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>61.671055674619922</v>
+        <v>61.704898486688563</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.027114808100833</v>
+        <v>70.065543118760274</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.107041444262194</v>
+        <v>73.147159905628357</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>44.81206605092278</v>
+        <v>44.836657268199332</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>55.751131224846411</v>
+        <v>55.781725399634198</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.110801979601376</v>
+        <v>64.145983634905164</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.109702568880493</v>
+        <v>74.150371253874866</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>77.854172037519049</v>
+        <v>77.89689554993835</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>44.789673519058745</v>
+        <v>44.814252448135605</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>56.9644001930277</v>
+        <v>56.995660165299086</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>66.567609447554688</v>
+        <v>66.604139308633748</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.335038153463614</v>
+        <v>78.378025547559886</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>82.811548507866561</v>
+        <v>82.856992446560454</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>44.768794701469901</v>
+        <v>44.793362173017904</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.15221596607234</v>
+        <v>58.184127768047944</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.041597387311896</v>
+        <v>69.079484882178619</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>82.70811274450071</v>
+        <v>82.753499921443691</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>87.988482444266751</v>
+        <v>88.036767294315013</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.683757427997477</v>
+        <v>44.70827823421061</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>63.727799128690549</v>
+        <v>63.762770606085709</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>81.673478703074053</v>
+        <v>81.718298110825458</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>106.97682611585556</v>
+        <v>107.03553107205155</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>117.52233359769768</v>
+        <v>117.5868255413868</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.623830388571676</v>
+        <v>44.648318309024852</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>68.742560698033984</v>
+        <v>68.780284092540072</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>94.753254800743477</v>
+        <v>94.805251909598439</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>135.79557628162817</v>
+        <v>135.87009591028672</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>154.20185757683132</v>
+        <v>154.28647789716669</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.58159890692022</v>
+        <v>44.606063652286132</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.252911071061988</v>
+        <v>73.293109580326018</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>108.29680690423648</v>
+        <v>108.35623621744674</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>170.01743009022388</v>
+        <v>170.11072941633395</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>199.7559396485</v>
+        <v>199.86555837727266</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.551837749693597</v>
+        <v>44.576286163228637</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.309586589163928</v>
+        <v>77.352011253075077</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>122.32057934577796</v>
+        <v>122.38770439064128</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>210.65539222807635</v>
+        <v>210.77099217642223</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>256.33176638422469</v>
+        <v>256.47243185041577</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>87.988482444266751</v>
+        <v>88.036767294315013</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>82.70811274450071</v>
+        <v>82.753499921443691</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.041597387311896</v>
+        <v>69.079484882178619</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.15221596607234</v>
+        <v>58.184127768047944</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.768794701469901</v>
+        <v>44.793362173017904</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>82.70811274450071</v>
+        <v>82.753499921443691</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.041597387311896</v>
+        <v>69.079484882178619</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.15221596607234</v>
+        <v>58.184127768047944</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.052555103439772</v>
+        <v>69.090448611498971</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>87.988482444266751</v>
+        <v>88.036767294315013</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.768794701469901</v>
+        <v>44.793362173017904</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>40.5</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20690450680305575</v>
+        <v>0.2189068073383065</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2860785284096642E-2</v>
+        <v>5.2859567785331955E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>70.678756184465314</v>
+        <v>70.717542091997316</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.508362188748997</v>
+        <v>50.536079324295812</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.170576324290074</v>
+        <v>32.188230355938693</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.428464353420708</v>
+        <v>32.446118385069326</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54118512967623145</v>
+        <v>0.54118713086973846</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>40.902057977121132</v>
+        <v>40.924503525461411</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.201178347491499</v>
+        <v>41.223623895831778</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41706418488802965</v>
+        <v>0.41706650604169104</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>50.659733060574766</v>
+        <v>50.687533262900843</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.002322704458052</v>
+        <v>51.030122906784129</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27839246956544494</v>
+        <v>0.27839512803770217</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.292397383047152</v>
+        <v>57.323837348139151</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>57.663354665305718</v>
+        <v>57.694794630397716</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18414870636928793</v>
+        <v>0.18415158497248318</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>40.5</v>
+        <v>39.340000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>125906.550984</v>
+        <v>122300.33865952</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20690450680305575</v>
+        <v>0.2189068073383065</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1352800000000001</v>
+        <v>1.1359030000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>70.678756184465314</v>
+        <v>70.717542091997316</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.428464353420708</v>
+        <v>32.446118385069326</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.201178347491499</v>
+        <v>41.223623895831778</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.002322704458052</v>
+        <v>51.030122906784129</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>57.663354665305718</v>
+        <v>57.694794630397716</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.776987959196641E-2</v>
+        <v>5.9505949518600436E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5061728395061726E-3</v>
+        <v>3.6095577020843917E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11539759707853772</v>
+        <v>-0.11546092304480152</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4910634663450999</v>
+        <v>9.4962718136598898</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1109600933931976</v>
+        <v>6.1143135640243935</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.486625962659762</v>
+        <v>15.495124454639482</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.418847858509771</v>
+        <v>11.42511410315061</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>60.943268361595621</v>
+        <v>60.976711790696179</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.99 HKD</v>
+        <v>88.04 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.71 HKD</v>
+        <v>82.75 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.04 HKD</v>
+        <v>69.08 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.15 HKD</v>
+        <v>58.18 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.77 HKD</v>
+        <v>44.79 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>70.678756184465314</v>
+        <v>70.717542091997316</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.170576324290074</v>
+        <v>32.188230355938693</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.428464353420708</v>
+        <v>32.446118385069326</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>40.902057977121132</v>
+        <v>40.924503525461411</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.201178347491499</v>
+        <v>41.223623895831778</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>50.659733060574766</v>
+        <v>50.687533262900843</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.002322704458052</v>
+        <v>51.030122906784129</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.292397383047152</v>
+        <v>57.323837348139151</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>57.663354665305718</v>
+        <v>57.694794630397716</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9543B94-43E8-41DE-B865-8F87B6D942E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10AB4EF-BD54-4C62-AE10-3D100E61853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10AB4EF-BD54-4C62-AE10-3D100E61853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02F8D53-0B35-4051-AC02-1811B7CDCC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>39.340000000000003</v>
+        <v>39.24</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>122300.33865952</v>
+        <v>121989.45828672001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2189068073383065</v>
+        <v>0.21952005351229451</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1359030000000001</v>
+        <v>1.1347130000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>70.717542091997316</v>
+        <v>70.643456650644055</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.446118385069326</v>
+        <v>32.412397201021413</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.223623895831778</v>
+        <v>41.180750376530121</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.030122906784129</v>
+        <v>50.977021396723089</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>57.694794630397716</v>
+        <v>57.634740764491653</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9505949518600436E-2</v>
+        <v>5.9595096900573741E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.6095577020843917E-3</v>
+        <v>3.6187563710499485E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11546092304480152</v>
+        <v>-0.1153399633339606</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4962718136598898</v>
+        <v>9.4863232850810792</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1143135640243935</v>
+        <v>6.1079080583243561</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.495124454639482</v>
+        <v>15.478891380071477</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.42511410315061</v>
+        <v>11.413144871814177</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.04 HKD</v>
+        <v>87.94 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8679957441694001E-2</v>
+        <v>-6.8678134846943142E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.75 HKD</v>
+        <v>82.67 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.92323661544651E-2</v>
+        <v>-4.9230468332552721E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.08 HKD</v>
+        <v>69.01 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8822185069326659E-3</v>
+        <v>9.8843575792919528E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.18 HKD</v>
+        <v>58.12 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9478175531119207E-2</v>
+        <v>6.9480577660854359E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.79 HKD</v>
+        <v>44.75 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16715040486980687</v>
+        <v>0.1671532834959375</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>70.717542091997316</v>
+        <v>70.643456650644055</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.188230355938693</v>
+        <v>32.15450917189078</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.446118385069326</v>
+        <v>32.412397201021413</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>40.924503525461411</v>
+        <v>40.881630006159753</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.223623895831778</v>
+        <v>41.180750376530121</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>50.687533262900843</v>
+        <v>50.634431752839802</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.030122906784129</v>
+        <v>50.977021396723089</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.323837348139151</v>
+        <v>57.263783482233087</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>57.694794630397716</v>
+        <v>57.634740764491653</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.335478254740437</v>
+        <v>29.304745684157261</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.42511410315061</v>
+        <v>11.413144871814177</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-358.94534800000002</v>
+        <v>-358.56930800000004</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11546092304480149</v>
+        <v>-0.11533996333396061</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29522.045216407187</v>
+        <v>29491.117193673268</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.4962718136598898</v>
+        <v>9.4863232850810792</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19008.200802000003</v>
+        <v>18988.287342</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1143135640243944</v>
+        <v>6.1079080583243561</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48171.300670407189</v>
+        <v>48120.835227673269</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.495124454639482</v>
+        <v>15.478891380071474</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.6095577020843917E-3</v>
+        <v>3.6187563710499485E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.6095577020843917E-3</v>
+        <v>3.6187563710499485E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.95729537366548E-3</v>
+        <v>1.9622833843017328E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3409640540617414</v>
+        <v>2.3385116023785137</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7996423438390297</v>
+        <v>2.7967093694660696</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.033810402826659</v>
+        <v>2.0316797328844509</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4047449773529566</v>
+        <v>1.4032733318664581</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96368061092693658</v>
+        <v>0.96267103534961784</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.78961431879775601</v>
+        <v>0.78878709936144031</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1576178375541935</v>
+        <v>1.1564050885547723</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.275556173228211</v>
+        <v>1.2742198691193729</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9505949518600436E-2</v>
+        <v>5.9595096900573741E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.116528581187162E-2</v>
+        <v>7.1271900343172004E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1698281719030473E-2</v>
+        <v>5.1775732234568064E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5707803186399503E-2</v>
+        <v>3.5761297957860809E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.4496202616343072E-2</v>
+        <v>2.4532901002793522E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0071538352764512E-2</v>
+        <v>2.0101608036733953E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.9425974518408574E-2</v>
+        <v>2.9470058321987059E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.2423898658571704E-2</v>
+        <v>3.2472473728832128E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2828851697674908E-2</v>
+        <v>9.3065418598025765E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8127394232253229E-2</v>
+        <v>5.8275527245077528E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.26818114913999E-2</v>
+        <v>4.2790582672570639E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1389937608330309E-2</v>
+        <v>3.1469932352490168E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6287744050737676E-2</v>
+        <v>2.6354736262895521E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4145449193119917E-2</v>
+        <v>3.4232466138056514E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2518307337413295E-2</v>
+        <v>3.260117764153514E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.495124454639482</v>
+        <v>15.478891380071477</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1359030000000001</v>
+        <v>1.1347130000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>189564.62893609784</v>
+        <v>189366.03635518733</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.536079324295812</v>
+        <v>50.483136481116496</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.04620125830774</v>
+        <v>44.999009746798933</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.523755098491137</v>
+        <v>46.475015665135288</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.410287402601192</v>
+        <v>47.360619216137124</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.296819706711233</v>
+        <v>48.246222767138939</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.592330474747918</v>
+        <v>48.54142395080622</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.009631459891693</v>
+        <v>44.962478259805707</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>47.931913017326877</v>
+        <v>47.881698363002855</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>49.751410235544441</v>
+        <v>49.699289431056471</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.620503666579367</v>
+        <v>51.566424753711601</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.254556190883754</v>
+        <v>52.199813028952541</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>44.975533745750852</v>
+        <v>44.928416267271224</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.310529161641576</v>
+        <v>49.258870235041016</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.108904556829948</v>
+        <v>52.054313983143089</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.060400352316989</v>
+        <v>55.002717718835733</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.078978383957981</v>
+        <v>56.020228663007416</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>44.943741005293198</v>
+        <v>44.896656833672651</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.660223288942667</v>
+        <v>50.607150389483962</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.482884852390193</v>
+        <v>54.425807238391158</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>58.620573145947553</v>
+        <v>58.559160787635548</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.072780580921268</v>
+        <v>60.009846854281498</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>44.914097424446915</v>
+        <v>44.867044308172815</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.981602154831855</v>
+        <v>51.927144946281253</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>56.873466408758546</v>
+        <v>56.813884362557047</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.305227505788956</v>
+        <v>62.239955012687084</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.243464460267575</v>
+        <v>64.176161422325322</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>44.886457722026115</v>
+        <v>44.839433561786016</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.275259785772327</v>
+        <v>53.219447309579316</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.280765318667932</v>
+        <v>59.218661326752063</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.118715934156313</v>
+        <v>66.049448336516676</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>68.598863942661836</v>
+        <v>68.526998080795309</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>44.860686437717682</v>
+        <v>44.813689276110679</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.541777746133633</v>
+        <v>54.484638434486513</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>61.704898486688563</v>
+        <v>61.640254913074301</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.065543118760274</v>
+        <v>69.99214072761302</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.147159905628357</v>
+        <v>73.070529136726691</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>44.836657268199332</v>
+        <v>44.789685280142997</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>55.781725399634198</v>
+        <v>55.723287088241797</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.145983634905164</v>
+        <v>64.078782720279946</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.150371253874866</v>
+        <v>74.072689496020445</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>77.89689554993835</v>
+        <v>77.815288840822845</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>44.814252448135605</v>
+        <v>44.767303931921383</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>56.995660165299086</v>
+        <v>56.935950105904304</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>66.604139308633748</v>
+        <v>66.534363169493986</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.378025547559886</v>
+        <v>78.295914794791727</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>82.856992446560454</v>
+        <v>82.770189417594594</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>44.793362173017904</v>
+        <v>44.746435541971159</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.184127768047944</v>
+        <v>58.12317264067881</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.079484882178619</v>
+        <v>69.007115509961281</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>82.753499921443691</v>
+        <v>82.666805313799799</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.036767294315013</v>
+        <v>87.944537805458793</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.70827823421061</v>
+        <v>44.661440739196763</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>63.762770606085709</v>
+        <v>63.695971154881477</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>81.718298110825458</v>
+        <v>81.632688006131772</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.03553107205155</v>
+        <v>106.92339800965472</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>117.5868255413868</v>
+        <v>117.4636386826548</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.648318309024852</v>
+        <v>44.601543629507553</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>68.780284092540072</v>
+        <v>68.708228170449786</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>94.805251909598439</v>
+        <v>94.705931589313678</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>135.87009591028672</v>
+        <v>135.72775504655695</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>154.28647789716669</v>
+        <v>154.12484357742494</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.606063652286132</v>
+        <v>44.559333239789446</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.293109580326018</v>
+        <v>73.216325910945287</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>108.35623621744674</v>
+        <v>108.24271955176422</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>170.11072941633395</v>
+        <v>169.93251722039341</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>199.86555837727266</v>
+        <v>199.6561742886058</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.576286163228637</v>
+        <v>44.529586946363956</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.352011253075077</v>
+        <v>77.270975378188623</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>122.38770439064128</v>
+        <v>122.25948801281247</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>210.77099217642223</v>
+        <v>210.55018328632337</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>256.47243185041577</v>
+        <v>256.20374500488231</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.036767294315013</v>
+        <v>87.944537805458793</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>82.753499921443691</v>
+        <v>82.666805313799799</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.079484882178619</v>
+        <v>69.007115509961281</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.184127768047944</v>
+        <v>58.12317264067881</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.793362173017904</v>
+        <v>44.746435541971159</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>82.753499921443691</v>
+        <v>82.666805313799799</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.079484882178619</v>
+        <v>69.007115509961281</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.184127768047944</v>
+        <v>58.12317264067881</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.090448611498971</v>
+        <v>69.01806775340836</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.036767294315013</v>
+        <v>87.944537805458793</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.793362173017904</v>
+        <v>44.746435541971159</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>39.340000000000003</v>
+        <v>39.24</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2189068073383065</v>
+        <v>0.21952005351229451</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2859567785331955E-2</v>
+        <v>5.2861894506899848E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>70.717542091997316</v>
+        <v>70.643456650644055</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.536079324295812</v>
+        <v>50.483136481116496</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.188230355938693</v>
+        <v>32.15450917189078</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.446118385069326</v>
+        <v>32.412397201021413</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54118713086973846</v>
+        <v>0.54118330645523538</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>40.924503525461411</v>
+        <v>40.881630006159753</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.223623895831778</v>
+        <v>41.180750376530121</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41706650604169104</v>
+        <v>0.41706207016195496</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>50.687533262900843</v>
+        <v>50.634431752839802</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.030122906784129</v>
+        <v>50.977021396723089</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27839512803770217</v>
+        <v>0.27839004751959096</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.323837348139151</v>
+        <v>57.263783482233087</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>57.694794630397716</v>
+        <v>57.634740764491653</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18415158497248318</v>
+        <v>0.18414608376944142</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>39.340000000000003</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>122300.33865952</v>
+        <v>121989.45828672001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2189068073383065</v>
+        <v>0.21952005351229451</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1359030000000001</v>
+        <v>1.1347130000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>70.717542091997316</v>
+        <v>70.643456650644055</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.446118385069326</v>
+        <v>32.412397201021413</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.223623895831778</v>
+        <v>41.180750376530121</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.030122906784129</v>
+        <v>50.977021396723089</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>57.694794630397716</v>
+        <v>57.634740764491653</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.9505949518600436E-2</v>
+        <v>5.9595096900573741E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.6095577020843917E-3</v>
+        <v>3.6187563710499485E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11546092304480152</v>
+        <v>-0.1153399633339606</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4962718136598898</v>
+        <v>9.4863232850810792</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1143135640243935</v>
+        <v>6.1079080583243561</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.495124454639482</v>
+        <v>15.478891380071477</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.42511410315061</v>
+        <v>11.413144871814177</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>60.976711790696179</v>
+        <v>60.912831083425452</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.04 HKD</v>
+        <v>87.94 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.75 HKD</v>
+        <v>82.67 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.08 HKD</v>
+        <v>69.01 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.18 HKD</v>
+        <v>58.12 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.79 HKD</v>
+        <v>44.75 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>70.717542091997316</v>
+        <v>70.643456650644055</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.188230355938693</v>
+        <v>32.15450917189078</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.446118385069326</v>
+        <v>32.412397201021413</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>40.924503525461411</v>
+        <v>40.881630006159753</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.223623895831778</v>
+        <v>41.180750376530121</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>50.687533262900843</v>
+        <v>50.634431752839802</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.030122906784129</v>
+        <v>50.977021396723089</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.323837348139151</v>
+        <v>57.263783482233087</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>57.694794630397716</v>
+        <v>57.634740764491653</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,15 +21852,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21875,12 +21872,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02F8D53-0B35-4051-AC02-1811B7CDCC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA690CB-520F-4289-88D9-7F732867DC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>39.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>121989.45828672001</v>
+        <v>115958.37905439999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21952005351229451</v>
+        <v>0.23944009247229556</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1347130000000001</v>
+        <v>1.1321619999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>70.643456650644055</v>
+        <v>70.48463987678511</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.412397201021413</v>
+        <v>32.340109183789302</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.180750376530121</v>
+        <v>41.088842521287674</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>50.977021396723089</v>
+        <v>50.863187823474611</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>57.634740764491653</v>
+        <v>57.506003443545133</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9595096900573741E-2</v>
+        <v>6.2553734259727323E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.6187563710499485E-3</v>
+        <v>3.8069705093833782E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.1153399633339606</v>
+        <v>-0.11508066230677137</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4863232850810792</v>
+        <v>9.4649966494470075</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1079080583243561</v>
+        <v>6.0941765919035209</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.478891380071477</v>
+        <v>15.444092579043758</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.413144871814177</v>
+        <v>11.387486460772795</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.94 HKD</v>
+        <v>87.75 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8678134846943142E-2</v>
+        <v>-6.8674214846151632E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.67 HKD</v>
+        <v>82.48 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9230468332552721E-2</v>
+        <v>-4.9226386534339972E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.01 HKD</v>
+        <v>68.85 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8843575792919528E-3</v>
+        <v>9.8889582554112457E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.12 HKD</v>
+        <v>57.99 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9480577660854359E-2</v>
+        <v>6.9485744117173912E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.75 HKD</v>
+        <v>44.65 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1671532834959375</v>
+        <v>0.16715947479487464</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>70.643456650644055</v>
+        <v>70.48463987678511</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.15450917189078</v>
+        <v>32.082221154658669</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.412397201021413</v>
+        <v>32.340109183789302</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>40.881630006159753</v>
+        <v>40.789722150917306</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.180750376530121</v>
+        <v>41.088842521287674</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>50.634431752839802</v>
+        <v>50.520598179591325</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>50.977021396723089</v>
+        <v>50.863187823474611</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.263783482233087</v>
+        <v>57.135046161286567</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>57.634740764491653</v>
+        <v>57.506003443545133</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.304745684157261</v>
+        <v>29.238864350075168</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.413144871814177</v>
+        <v>11.387486460772795</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-358.56930800000004</v>
+        <v>-357.76319199999995</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11533996333396061</v>
+        <v>-0.11508066230677137</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29491.117193673268</v>
+        <v>29424.816869308372</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.4863232850810792</v>
+        <v>9.4649966494470092</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>18988.287342</v>
+        <v>18945.598908</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1079080583243561</v>
+        <v>6.0941765919035209</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48120.835227673269</v>
+        <v>48012.652585308373</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.478891380071474</v>
+        <v>15.444092579043758</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.6187563710499485E-3</v>
+        <v>3.8069705093833782E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.6187563710499485E-3</v>
+        <v>3.8069705093833782E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9622833843017328E-3</v>
+        <v>2.064343163538874E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3385116023785137</v>
+        <v>2.3332542878878293</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7967093694660696</v>
+        <v>2.7904219596968076</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0316797328844509</v>
+        <v>2.0271122211007766</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4032733318664581</v>
+        <v>1.4001185691470819</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96267103534961784</v>
+        <v>0.96050681072966815</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.78878709936144031</v>
+        <v>0.78701379114123737</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1564050885547723</v>
+        <v>1.1538053215820634</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2742198691193729</v>
+        <v>1.2713552373700903</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9595096900573741E-2</v>
+        <v>6.2553734259727323E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1271900343172004E-2</v>
+        <v>7.481024020634873E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1775732234568064E-2</v>
+        <v>5.4346172147473906E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5761297957860809E-2</v>
+        <v>3.7536690861852066E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.4532901002793522E-2</v>
+        <v>2.5750852834575556E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0101608036733953E-2</v>
+        <v>2.1099565446145777E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.9470058321987059E-2</v>
+        <v>3.0933118541074087E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.2472473728832128E-2</v>
+        <v>3.4084590814211536E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3065418598025765E-2</v>
+        <v>9.7905818385697896E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8275527245077528E-2</v>
+        <v>6.130647960045154E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2790582672570639E-2</v>
+        <v>4.5016151851787457E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1469932352490168E-2</v>
+        <v>3.3106706313986982E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6354736262895521E-2</v>
+        <v>2.7725465173083653E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4232466138056514E-2</v>
+        <v>3.6012921481429962E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.260117764153514E-2</v>
+        <v>3.4296788489379067E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.478891380071477</v>
+        <v>15.444092579043758</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1347130000000001</v>
+        <v>1.1321619999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>189366.03635518733</v>
+        <v>188940.3139401431</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.483136481116496</v>
+        <v>50.36964304166235</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>44.999009746798933</v>
+        <v>44.897845422547697</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.475015665135288</v>
+        <v>46.370533064722878</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.360619216137124</v>
+        <v>47.254145650028008</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.246222767138939</v>
+        <v>48.137758235333116</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.54142395080622</v>
+        <v>48.43229576376816</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>44.962478259805707</v>
+        <v>44.861396063654986</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>47.881698363002855</v>
+        <v>47.774053335120009</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>49.699289431056471</v>
+        <v>49.587558193872589</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.566424753711601</v>
+        <v>51.450495924530365</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.199813028952541</v>
+        <v>52.082460250728559</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>44.928416267271224</v>
+        <v>44.827410647438001</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.258870235041016</v>
+        <v>49.148129124319979</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.054313983143089</v>
+        <v>51.93728830795385</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.002717718835733</v>
+        <v>54.879063602860363</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.020228663007416</v>
+        <v>55.894287034314225</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>44.896656833672651</v>
+        <v>44.795722613669255</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.607150389483962</v>
+        <v>50.49337814871155</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.425807238391158</v>
+        <v>54.303450101154567</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>58.559160787635548</v>
+        <v>58.427511269943174</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.009846854281498</v>
+        <v>59.874935983140261</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>44.867044308172815</v>
+        <v>44.766176661437335</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.927144946281253</v>
+        <v>51.810405165598411</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>56.813884362557047</v>
+        <v>56.686158480321716</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.239955012687084</v>
+        <v>62.100030533777108</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.176161422325322</v>
+        <v>64.031884069560022</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>44.839433561786016</v>
+        <v>44.738627988027602</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.219447309579316</v>
+        <v>53.099802245068069</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.218661326752063</v>
+        <v>59.085529155846679</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.049448336516676</v>
+        <v>65.900959562080786</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>68.526998080795309</v>
+        <v>68.372939413886485</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>44.813689276110679</v>
+        <v>44.712941579253965</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.484638434486513</v>
+        <v>54.362149036157255</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>61.640254913074301</v>
+        <v>61.501678647284393</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>69.99214072761302</v>
+        <v>69.834788206758716</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.070529136726691</v>
+        <v>72.906255950619013</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>44.789685280142997</v>
+        <v>44.688991547763401</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>55.723287088241797</v>
+        <v>55.598013027433367</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.078782720279946</v>
+        <v>63.934724289011911</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.072689496020445</v>
+        <v>73.906163307544276</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>77.815288840822845</v>
+        <v>77.640348744223132</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>44.767303931921383</v>
+        <v>44.666660516070557</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>56.935950105904304</v>
+        <v>56.807949802109277</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>66.534363169493986</v>
+        <v>66.38478423592629</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.295914794791727</v>
+        <v>78.119894181084547</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>82.770189417594594</v>
+        <v>82.584109983231642</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>44.746435541971159</v>
+        <v>44.645839041298679</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.12317264067881</v>
+        <v>57.992503287805988</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.007115509961281</v>
+        <v>68.851977469182756</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>82.666805313799799</v>
+        <v>82.480958301951404</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>87.944537805458793</v>
+        <v>87.746825682709044</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.661440739196763</v>
+        <v>44.561035319213296</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>63.695971154881477</v>
+        <v>63.55277333973693</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>81.632688006131772</v>
+        <v>81.449165840523676</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>106.92339800965472</v>
+        <v>106.68301864648302</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>117.4636386826548</v>
+        <v>117.1995633241461</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.601543629507553</v>
+        <v>44.501272866945669</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>68.708228170449786</v>
+        <v>68.553762071918413</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>94.705931589313678</v>
+        <v>94.493018869106578</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>135.72775504655695</v>
+        <v>135.4226192958219</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>154.12484357742494</v>
+        <v>153.77834849367596</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.559333239789446</v>
+        <v>44.459157372328058</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.216325910945287</v>
+        <v>73.05172495246606</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>108.24271955176422</v>
+        <v>107.99937416171707</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>169.93251722039341</v>
+        <v>169.55048418523012</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>199.6561742886058</v>
+        <v>199.20731814558968</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.529586946363956</v>
+        <v>44.42947795290025</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.270975378188623</v>
+        <v>77.097258977486618</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>122.25948801281247</v>
+        <v>121.98463088689543</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>210.55018328632337</v>
+        <v>210.07683582527955</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>256.20374500488231</v>
+        <v>255.62776169147398</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>87.944537805458793</v>
+        <v>87.746825682709044</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>82.666805313799799</v>
+        <v>82.480958301951404</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.007115509961281</v>
+        <v>68.851977469182756</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.12317264067881</v>
+        <v>57.992503287805988</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.746435541971159</v>
+        <v>44.645839041298679</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>82.666805313799799</v>
+        <v>82.480958301951404</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.007115509961281</v>
+        <v>68.851977469182756</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.12317264067881</v>
+        <v>57.992503287805988</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.01806775340836</v>
+        <v>68.862905090392289</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>87.944537805458793</v>
+        <v>87.746825682709044</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.746435541971159</v>
+        <v>44.645839041298679</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>39.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21952005351229451</v>
+        <v>0.23944009247229556</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2861894506899848E-2</v>
+        <v>5.2866898776336831E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>70.643456650644055</v>
+        <v>70.48463987678511</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.483136481116496</v>
+        <v>50.36964304166235</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452494</v>
+        <v>0.21911288198452497</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.15450917189078</v>
+        <v>32.082221154658669</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.412397201021413</v>
+        <v>32.340109183789302</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54118330645523538</v>
+        <v>0.54117508097759504</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>40.881630006159753</v>
+        <v>40.789722150917306</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.180750376530121</v>
+        <v>41.088842521287674</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41706207016195496</v>
+        <v>0.41705252955657457</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>50.634431752839802</v>
+        <v>50.520598179591325</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>50.977021396723089</v>
+        <v>50.863187823474611</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27839004751959096</v>
+        <v>0.27837912043831037</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.263783482233087</v>
+        <v>57.135046161286567</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>57.634740764491653</v>
+        <v>57.506003443545133</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18414608376944142</v>
+        <v>0.18413425188705024</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>39.24</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>121989.45828672001</v>
+        <v>115958.37905439999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21952005351229451</v>
+        <v>0.23944009247229556</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1347130000000001</v>
+        <v>1.1321619999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>70.643456650644055</v>
+        <v>70.48463987678511</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.412397201021413</v>
+        <v>32.340109183789302</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.180750376530121</v>
+        <v>41.088842521287674</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>50.977021396723089</v>
+        <v>50.863187823474611</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>57.634740764491653</v>
+        <v>57.506003443545133</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.9595096900573741E-2</v>
+        <v>6.2553734259727323E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.6187563710499485E-3</v>
+        <v>3.8069705093833782E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.1153399633339606</v>
+        <v>-0.11508066230677137</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4863232850810792</v>
+        <v>9.4649966494470075</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1079080583243561</v>
+        <v>6.0941765919035209</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.478891380071477</v>
+        <v>15.444092579043758</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.413144871814177</v>
+        <v>11.387486460772795</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>60.912831083425452</v>
+        <v>60.775890172293018</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.94 HKD</v>
+        <v>87.75 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.67 HKD</v>
+        <v>82.48 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.01 HKD</v>
+        <v>68.85 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.12 HKD</v>
+        <v>57.99 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.75 HKD</v>
+        <v>44.65 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>70.643456650644055</v>
+        <v>70.48463987678511</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.15450917189078</v>
+        <v>32.082221154658669</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.412397201021413</v>
+        <v>32.340109183789302</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>40.881630006159753</v>
+        <v>40.789722150917306</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.180750376530121</v>
+        <v>41.088842521287674</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>50.634431752839802</v>
+        <v>50.520598179591325</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>50.977021396723089</v>
+        <v>50.863187823474611</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.263783482233087</v>
+        <v>57.135046161286567</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>57.634740764491653</v>
+        <v>57.506003443545133</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA690CB-520F-4289-88D9-7F732867DC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3EAA8-8E71-4315-A8E3-C5EBB8C27FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Other LT liabilities</t>
-  </si>
-  <si>
-    <t>Biological assets</t>
   </si>
   <si>
     <t>Intangible assets</t>
@@ -3258,10 +3255,13 @@
     <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
+    <t>Biological/Mineral assets</t>
+  </si>
+  <si>
+    <t>腾讯音乐</t>
+  </si>
+  <si>
     <t>1698.hk</t>
-  </si>
-  <si>
-    <t>腾讯音乐</t>
   </si>
   <si>
     <t>TMT_01</t>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5341,7 +5341,7 @@
   <sheetData>
     <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F3" s="429">
         <v>46103</v>
@@ -5362,35 +5362,35 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F4" s="431" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="45" t="s">
         <v>557</v>
@@ -5400,26 +5400,26 @@
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>37.299999999999997</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C9" s="48">
         <v>3108803728</v>
@@ -5427,18 +5427,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>115958.37905439999</v>
+        <v>113409.15999743999</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23944009247229556</v>
+        <v>0.24987629123293953</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="B12" s="462" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5463,13 +5463,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5478,27 +5478,27 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1321619999999999</v>
+        <v>1.135421</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C17" s="456">
         <v>0.02</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E17" s="224" t="s">
         <v>558</v>
@@ -5511,10 +5511,10 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>70.48463987678511</v>
+        <v>70.687534375415567</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E18" s="418">
         <v>6</v>
@@ -5522,14 +5522,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
         <v>Low growth</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E19" s="419">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5542,14 +5542,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C21" s="254" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E21" s="442">
         <v>3</v>
@@ -5557,14 +5557,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.340109183789302</v>
+        <v>32.432459888673442</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E22" s="79">
         <v>0.3</v>
@@ -5572,14 +5572,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.088842521287674</v>
+        <v>41.206258319106226</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E23" s="443">
         <v>0.2</v>
@@ -5587,14 +5587,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>50.863187823474611</v>
+        <v>51.008614564053516</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E24" s="443">
         <v>0.1174</v>
@@ -5602,14 +5602,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>57.506003443545133</v>
+        <v>57.670470291434079</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E25" s="444">
         <v>7.2499999999999995E-2</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5630,26 +5630,26 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="B29" s="462" t="s">
+        <v>355</v>
+      </c>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="B30" s="466" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="105">
         <f>scaling_factor</f>
@@ -5657,17 +5657,17 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
-        <v>196</v>
-      </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="B33" s="463" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
@@ -5683,17 +5683,17 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="B36" s="463" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="285">
         <f>Normalized_FCF!C15</f>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
@@ -5718,17 +5718,17 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="B40" s="463" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
@@ -5740,17 +5740,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
-        <v>205</v>
-      </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="B43" s="463" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
@@ -5793,12 +5793,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
@@ -5810,17 +5810,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
-        <v>206</v>
-      </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="B51" s="463" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
@@ -5832,8 +5832,8 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
-        <v>265</v>
+      <c r="B54" s="463" t="s">
+        <v>264</v>
       </c>
       <c r="C54" s="464"/>
       <c r="D54" s="464"/>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="285">
         <f>Normalized_FCF!C17</f>
@@ -5854,26 +5854,26 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
-        <v>270</v>
-      </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="B57" s="462" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
-        <v>282</v>
-      </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="B58" s="462" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
@@ -5899,24 +5899,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.2553734259727323E-2</v>
+        <v>6.4143933883932178E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8069705093833782E-3</v>
+        <v>3.8925438596491228E-3</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
@@ -5925,18 +5925,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C65" s="264" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="264" t="s">
         <v>327</v>
-      </c>
-      <c r="D65" s="264" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
@@ -5991,7 +5991,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6004,18 +6004,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
-        <v>478</v>
-      </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="B73" s="462" t="s">
+        <v>477</v>
+      </c>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6024,23 +6024,23 @@
     <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="B77" s="462" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="285">
         <f>DCF!F4</f>
@@ -6054,11 +6054,11 @@
     <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11508066230677137</v>
+        <v>-0.11541192927957014</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6068,7 +6068,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="337">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6078,7 +6078,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6091,13 +6091,13 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
@@ -6111,7 +6111,7 @@
     <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="291">
         <f>BS!C66</f>
@@ -6125,11 +6125,11 @@
     <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4649966494470075</v>
+        <v>9.4922422415800689</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6142,13 +6142,13 @@
     <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="285">
         <f>DCF!F6</f>
@@ -6162,11 +6162,11 @@
     <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0941765919035209</v>
+        <v>6.1117190650769828</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6179,11 +6179,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.444092579043758</v>
+        <v>15.488549377377483</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6204,40 +6204,40 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
-        <v>485</v>
-      </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="B96" s="462" t="s">
+        <v>484</v>
+      </c>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
-        <v>484</v>
-      </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="B97" s="466" t="s">
+        <v>483</v>
+      </c>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
-        <v>483</v>
-      </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="B98" s="466" t="s">
+        <v>482</v>
+      </c>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6246,7 +6246,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="263">
         <f>E25</f>
@@ -6255,7 +6255,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
@@ -6273,40 +6273,40 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
-        <v>284</v>
-      </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.387486460772795</v>
+        <v>11.420266061550475</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6315,11 +6315,11 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,34 +6327,34 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
-        <v>491</v>
-      </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="B114" s="462" t="s">
+        <v>490</v>
+      </c>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117" s="342" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" s="342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E117" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.75 HKD</v>
+        <v>88 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8674214846151632E-2</v>
+        <v>-6.8679219674525671E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.48 HKD</v>
+        <v>82.72 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9226386534339972E-2</v>
+        <v>-4.9231597936145337E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>68.85 HKD</v>
+        <v>69.05 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8889582554112457E-3</v>
+        <v>9.8830843808505649E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>57.99 HKD</v>
+        <v>58.16 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9485744117173912E-2</v>
+        <v>6.9479147887837003E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.65 HKD</v>
+        <v>44.77 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,25 +6464,25 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16715947479487464</v>
+        <v>0.16715157010712198</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
-        <v>357</v>
-      </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="B124" s="463" t="s">
+        <v>356</v>
+      </c>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>70.48463987678511</v>
+        <v>70.687534375415567</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C127" s="465"/>
       <c r="D127" s="465"/>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6509,31 +6509,31 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="B131" s="467" t="s">
+        <v>284</v>
+      </c>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
-        <v>359</v>
-      </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="B132" s="462" t="s">
+        <v>358</v>
+      </c>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="202">
         <f>E21</f>
@@ -6542,7 +6542,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
@@ -6555,33 +6555,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.082221154658669</v>
+        <v>32.174571859542809</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.340109183789302</v>
+        <v>32.432459888673442</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>40.789722150917306</v>
+        <v>40.907137948735858</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.088842521287674</v>
+        <v>41.206258319106226</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6630,26 +6630,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>50.520598179591325</v>
+        <v>50.66602492017023</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>50.863187823474611</v>
+        <v>51.008614564053516</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.135046161286567</v>
+        <v>57.299513009175513</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>57.506003443545133</v>
+        <v>57.670470291434079</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6691,7 +6691,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6700,22 +6700,22 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
-        <v>360</v>
-      </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="B149" s="461" t="s">
+        <v>359</v>
+      </c>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C152" s="464"/>
       <c r="D152" s="464"/>
@@ -6724,90 +6724,78 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
-        <v>438</v>
-      </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="B158" s="463" t="s">
+        <v>437</v>
+      </c>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
+        <v>293</v>
+      </c>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
-        <v>295</v>
-      </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6910,7 +6910,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="103">
         <v>1000000</v>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="287">
         <v>18367</v>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="287">
         <f>3916+C7</f>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="288">
         <v>941</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="287"/>
       <c r="D8" s="287"/>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="287"/>
       <c r="D9" s="287"/>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="287"/>
       <c r="D10" s="287"/>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="287"/>
       <c r="D11" s="287"/>
@@ -7125,7 +7125,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="287">
         <v>129</v>
@@ -7155,7 +7155,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="287">
         <v>1054</v>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="287">
         <v>1924</v>
@@ -7215,7 +7215,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="289">
         <v>11353</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="287">
         <v>297</v>
@@ -7275,13 +7275,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
@@ -7307,7 +7307,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" s="287">
         <v>10231</v>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23" s="287">
         <v>-10227</v>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" s="287">
         <v>-4649</v>
@@ -7472,15 +7472,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="270">
         <f>BS!C4</f>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="270">
         <f>BS!C6</f>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="271">
         <f>BS!C33+BS!C42</f>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="271">
         <f>BS!G27</f>
@@ -7604,7 +7604,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="270">
         <f>BS!G28</f>
@@ -7635,7 +7635,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7705,7 +7705,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="270">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="267">
         <f>IF(C36="","",C36+C37)</f>
@@ -7803,7 +7803,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="270">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="282">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="282">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="270">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7999,7 +7999,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="271">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -8048,7 +8048,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" s="290">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="285">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="270">
         <f>IF(C$4="","",-C14)</f>
@@ -8195,7 +8195,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="271">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -8244,7 +8244,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="270">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -8293,12 +8293,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="270">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="270">
         <f>IF(C$4="","",C13)</f>
@@ -8396,12 +8396,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="285">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="285">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -8499,7 +8499,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="285">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="285">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -8597,13 +8597,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="270">
         <f>IF(C$4="","",-C19)</f>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="270">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="270">
         <f>IF(C$4="","",-C21)</f>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
@@ -8848,7 +8848,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8903,7 +8903,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="89">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -9002,7 +9002,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -9117,7 +9117,7 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="9"/>
     </row>
@@ -9172,7 +9172,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="260">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -9206,7 +9206,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="260">
         <f t="shared" si="40"/>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="259">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="259">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -9353,7 +9353,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9381,7 +9381,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="96">
         <v>46022</v>
@@ -9397,7 +9397,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -9408,27 +9408,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="164" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18">
         <v>3903</v>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="18">
         <f>15763+8470</f>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="18">
         <v>15</v>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="18">
         <v>0</v>
@@ -9513,7 +9513,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -9534,7 +9534,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18">
         <v>4183</v>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="78">
         <f>SUM(C4:C11)</f>
@@ -9598,7 +9598,7 @@
         <v>2784.75</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="78">
         <f>SUM(G4:G10)</f>
@@ -9616,27 +9616,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C15" s="18">
         <v>365</v>
@@ -9645,7 +9645,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="18">
         <v>13810</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -9665,7 +9665,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -9685,7 +9685,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="18">
         <f>1659+26231</f>
@@ -9697,7 +9697,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -9706,7 +9706,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G18" s="18">
         <v>0</v>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="18">
         <f>1201+2290+287</f>
@@ -9727,7 +9727,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G19" s="18">
         <v>0</v>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>554</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="18">
         <v>0</v>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18">
         <v>2899</v>
@@ -9767,7 +9767,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="18">
         <v>0</v>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="18">
         <v>498</v>
@@ -9790,7 +9790,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="18">
         <f>20521+303</f>
@@ -9803,7 +9803,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78">
         <f>SUM(C15:C23)</f>
@@ -9814,7 +9814,7 @@
         <v>1116.95</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="78">
         <f>SUM(G15:G21)</f>
@@ -9827,19 +9827,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="167" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H26" s="168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
@@ -9850,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="82">
         <f>G32-G30</f>
@@ -9869,7 +9869,7 @@
         <v>116</v>
       </c>
       <c r="F28" s="171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G28" s="287">
         <v>2763</v>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9903,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="82">
         <f>C33+C42</f>
@@ -9913,14 +9913,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="78">
         <f>SUM(C27:C30)</f>
         <v>116</v>
       </c>
       <c r="F31" s="172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="173">
         <f>C31+C40</f>
@@ -9937,7 +9937,7 @@
         <v>14473</v>
       </c>
       <c r="F32" s="174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="175">
         <f>G35+G40</f>
@@ -9963,24 +9963,24 @@
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="179" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="181" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="175">
         <f>C12+C24</f>
@@ -9999,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="173">
         <f>C4+C15</f>
@@ -10015,7 +10015,7 @@
         <v>200</v>
       </c>
       <c r="F37" s="172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="173">
         <f>C6</f>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G38" s="173">
         <f>C7+C17</f>
@@ -10047,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="173">
         <f>C7+C17+C19+C20</f>
@@ -10060,14 +10060,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="78">
         <f>SUM(C36:C39)</f>
         <v>200</v>
       </c>
       <c r="F40" s="181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="175">
         <f>G12+G24</f>
@@ -10087,7 +10087,7 @@
         <v>4683</v>
       </c>
       <c r="F41" s="172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="173">
         <f>C70</f>
@@ -10100,13 +10100,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42" s="81">
         <v>4883</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="184">
         <f>C82</f>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -10130,21 +10130,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F45" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="73">
         <f>G29</f>
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.238864350075168</v>
+        <v>29.32303027236977</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.387486460772795</v>
+        <v>11.420266061550475</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10176,20 +10176,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
@@ -10203,7 +10203,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="163"/>
       <c r="D51" s="89">
@@ -10217,19 +10217,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="223"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
@@ -10260,19 +10260,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" s="223"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
@@ -10283,7 +10283,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95"/>
       <c r="D59" s="89">
@@ -10297,19 +10297,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C61" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F61" s="223"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="89">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -10320,12 +10320,12 @@
         <v>3.4414039632817271E-2</v>
       </c>
       <c r="F62" s="223" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -10336,21 +10336,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="165" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="19">
         <f>G4+G5+G15</f>
@@ -10361,12 +10361,12 @@
         <v>25989.935070518506</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="19">
         <f>G6+G16</f>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="19">
         <f>G18</f>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19">
         <f>G8+G20</f>
@@ -10396,7 +10396,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" s="78">
         <f>SUM(C66:C69)</f>
@@ -10409,19 +10409,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C72" s="209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F72" s="223"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
@@ -10432,12 +10432,12 @@
         <v>-2011.3441549135823</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
@@ -10448,12 +10448,12 @@
         <v>18.921674794950825</v>
       </c>
       <c r="F74" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="261"/>
       <c r="D75" s="262">
@@ -10461,12 +10461,12 @@
         <v>12068.064929481494</v>
       </c>
       <c r="F75" s="223" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C76" s="230"/>
       <c r="D76" s="248">
@@ -10474,7 +10474,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10482,19 +10482,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" s="223"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="19">
         <f>G7+G17</f>
@@ -10508,7 +10508,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" s="19">
         <f>G19</f>
@@ -10522,7 +10522,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="19">
         <f>G9+G21</f>
@@ -10536,7 +10536,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="78">
         <f>SUM(C79:C81)</f>
@@ -10550,7 +10550,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -10561,23 +10561,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="215" t="s">
         <v>242</v>
-      </c>
-      <c r="D85" s="215" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-357.76319199999995</v>
+        <v>-358.79303600000003</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11508066230677137</v>
+        <v>-0.11541192927957014</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10586,15 +10586,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29424.816869308372</v>
+        <v>29509.518067703193</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.4649966494470092</v>
+        <v>9.4922422415800689</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,15 +10603,15 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>18945.598908</v>
+        <v>19000.135014</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.0941765919035209</v>
+        <v>6.1117190650769828</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,15 +10620,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48012.652585308373</v>
+        <v>48150.860045703193</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.444092579043758</v>
+        <v>15.488549377377481</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10673,7 +10673,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="50"/>
       <c r="E1" s="50"/>
@@ -10726,12 +10726,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="53"/>
       <c r="E2" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="53"/>
       <c r="G2" s="35"/>
@@ -10749,7 +10749,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10759,7 +10759,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10826,7 +10826,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="266">
         <f>C26</f>
@@ -10881,7 +10881,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
@@ -10936,7 +10936,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="266">
         <f>C35</f>
@@ -10991,7 +10991,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
@@ -11048,7 +11048,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C9" s="300">
         <f>C61</f>
@@ -11105,7 +11105,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="266">
         <f>C48</f>
@@ -11160,7 +11160,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
@@ -11215,7 +11215,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
@@ -11270,7 +11270,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
@@ -11327,7 +11327,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
@@ -11384,7 +11384,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="266">
         <f>BS!$G$39*BS!D58</f>
@@ -11439,7 +11439,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
@@ -11494,7 +11494,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="266">
         <f>-C4*C83</f>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="272"/>
@@ -11520,14 +11520,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="266">
         <v>0</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="273"/>
@@ -11545,7 +11545,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
@@ -11621,12 +11621,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="53"/>
       <c r="E21" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="35"/>
@@ -11644,7 +11644,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="26"/>
@@ -11665,7 +11665,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
@@ -11722,7 +11722,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
@@ -11779,7 +11779,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="266">
         <f>-C4*C31</f>
@@ -11836,7 +11836,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
@@ -11897,14 +11897,14 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="237"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="60">
         <f>AVERAGE(G29:H29)</f>
@@ -12076,7 +12076,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
@@ -12135,14 +12135,14 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="237"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C35" s="276">
         <f>AVERAGE(G35:K35)</f>
@@ -12203,14 +12203,14 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="237"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12269,21 +12269,21 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="457">
         <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12337,12 +12337,12 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="53"/>
       <c r="E43" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="35"/>
@@ -12360,14 +12360,14 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
@@ -12422,7 +12422,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
@@ -12477,7 +12477,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="278">
         <f>BS!$C$66*C51</f>
@@ -12534,7 +12534,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
@@ -12593,17 +12593,17 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E50" s="237"/>
       <c r="G50" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="84">
         <v>6.0000000000000001E-3</v>
@@ -12627,7 +12627,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="79">
         <v>0.06</v>
@@ -12651,7 +12651,7 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
@@ -12710,17 +12710,17 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="237"/>
       <c r="G55" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="266">
         <f>BS!$C67*C64</f>
@@ -12775,7 +12775,7 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
@@ -12830,7 +12830,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="266">
         <f>BS!$C69*C66</f>
@@ -12885,7 +12885,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
@@ -12940,13 +12940,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="279">
         <v>0</v>
       </c>
       <c r="E60" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="266">
         <f>Data!C58</f>
@@ -12996,7 +12996,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
@@ -13055,17 +13055,17 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="237"/>
       <c r="G63" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="158">
         <f>G64</f>
@@ -13090,7 +13090,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="158">
         <f>G65</f>
@@ -13115,7 +13115,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="158">
         <f>G66</f>
@@ -13140,7 +13140,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
@@ -13170,12 +13170,12 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="51"/>
       <c r="D69" s="53"/>
       <c r="E69" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="35"/>
@@ -13193,7 +13193,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="26"/>
@@ -13214,7 +13214,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
@@ -13271,7 +13271,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
@@ -13328,7 +13328,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
@@ -13385,7 +13385,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
@@ -13442,7 +13442,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
@@ -13499,7 +13499,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
@@ -13556,7 +13556,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
@@ -13613,7 +13613,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
@@ -13728,7 +13728,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
@@ -13785,7 +13785,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
@@ -13842,7 +13842,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13901,7 +13901,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="233">
         <v>0</v>
@@ -13927,7 +13927,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="74">
         <v>0</v>
@@ -13951,7 +13951,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
@@ -14012,7 +14012,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="237"/>
     </row>
@@ -14131,7 +14131,7 @@
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
@@ -14186,7 +14186,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C91" s="292">
         <v>0</v>
@@ -14207,20 +14207,20 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8069705093833782E-3</v>
+        <v>3.8925438596491228E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8069705093833782E-3</v>
+        <v>3.8925438596491228E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.064343163538874E-3</v>
+        <v>2.1107456140350878E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -14266,7 +14266,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="26"/>
@@ -14287,7 +14287,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
@@ -14344,7 +14344,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
@@ -14404,12 +14404,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="51"/>
       <c r="D98" s="53"/>
       <c r="E98" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F98" s="53"/>
       <c r="G98" s="35"/>
@@ -14427,11 +14427,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="237"/>
       <c r="G99" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
@@ -14494,7 +14494,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="281">
         <f>BS!C4</f>
@@ -14551,7 +14551,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C102" s="281">
         <f>BS!C6+BS!C7</f>
@@ -14608,7 +14608,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C103" s="280">
         <f>BS!G30</f>
@@ -14665,7 +14665,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="280">
         <f>BS!G27</f>
@@ -14726,14 +14726,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="238"/>
       <c r="F106" s="25"/>
       <c r="G106" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -14749,7 +14749,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
@@ -14806,7 +14806,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
@@ -14863,7 +14863,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C109" s="91">
         <f>BS!$G$38/C$4</f>
@@ -14894,18 +14894,18 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="237"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -14955,7 +14955,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="459">
@@ -15014,10 +15014,10 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" s="451" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
@@ -15073,7 +15073,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C116" s="22">
         <f>C77</f>
@@ -15130,7 +15130,7 @@
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C117" s="452">
         <f>G117</f>
@@ -15187,7 +15187,7 @@
     </row>
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C118" s="15">
         <f>C100/C104</f>
@@ -15247,7 +15247,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
@@ -15326,12 +15326,12 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C121" s="51"/>
       <c r="D121" s="53"/>
       <c r="E121" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="53"/>
       <c r="G121" s="35"/>
@@ -15349,7 +15349,7 @@
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="161"/>
       <c r="D122" s="26"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3332542878878293</v>
+        <v>2.3399707080858456</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7904219596968076</v>
+        <v>2.7984543659837633</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0271122211007766</v>
+        <v>2.0329473919761174</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4001185691470819</v>
+        <v>1.4041488990970805</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96050681072966815</v>
+        <v>0.96327169039898053</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.78701379114123737</v>
+        <v>0.78927926016892891</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1538053215820634</v>
+        <v>1.1571266232535875</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2713552373700903</v>
+        <v>1.2750149139169</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15428,42 +15428,42 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2553734259727323E-2</v>
+        <v>6.4143933883932178E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.481024020634873E-2</v>
+        <v>7.6712016611397024E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.4346172147473906E-2</v>
+        <v>5.5727724560748836E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.7536690861852066E-2</v>
+        <v>3.8490923769108572E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.5750852834575556E-2</v>
+        <v>2.6405473969270302E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.1099565446145777E-2</v>
+        <v>2.1635944631823712E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.0933118541074087E-2</v>
+        <v>3.1719479804100538E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.4084590814211536E-2</v>
+        <v>3.4951066719213268E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15484,36 +15484,36 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7905818385697896E-2</v>
+        <v>0.10010655224195536</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.130647960045154E-2</v>
+        <v>6.2684530951119588E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5016151851787457E-2</v>
+        <v>4.602802807214014E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3106706313986982E-2</v>
+        <v>3.3850881181790415E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7725465173083653E-2</v>
+        <v>2.8348680124890908E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6012921481429962E-2</v>
+        <v>3.6822422457712112E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4296788489379067E-2</v>
+        <v>3.5067714107835504E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -16261,22 +16261,22 @@
     </row>
     <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
@@ -16287,7 +16287,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F4" s="275">
         <f>-BS!G31</f>
@@ -16298,7 +16298,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="308" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I4" s="305">
         <f>Normalized_FCF!C4</f>
@@ -16308,14 +16308,14 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
@@ -16326,7 +16326,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="308" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
@@ -16336,7 +16336,7 @@
     </row>
     <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16347,7 +16347,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F6" s="284">
         <f>BS!H42</f>
@@ -16358,7 +16358,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="308" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
@@ -16369,14 +16369,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C7" s="275">
         <f>F7</f>
         <v>42407.935070518506</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
@@ -16387,7 +16387,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="312" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I7" s="313">
         <f>Normalized_FCF!C9</f>
@@ -16399,7 +16399,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
@@ -16410,11 +16410,11 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.444092579043758</v>
+        <v>15.488549377377483</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1321619999999999</v>
+        <v>1.135421</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16460,18 +16460,18 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>188940.3139401431</v>
+        <v>189484.19059660297</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="H10" s="308" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I10" s="306">
         <f>Normalized_FCF!C41</f>
@@ -16482,11 +16482,11 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16498,7 +16498,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16513,25 +16513,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C14" s="309" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16546,7 +16546,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16556,14 +16556,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
         <v>2.38559171477595E-2</v>
       </c>
       <c r="E16" s="308" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
@@ -16572,44 +16572,44 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.28146521974317368</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
         <v>0.28146521974317368</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>-1.9775049365010421E-2</v>
       </c>
       <c r="E18" s="308" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
         <v>-1.9775049365010421E-2</v>
       </c>
       <c r="H18" s="140" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.36964304166235</v>
+        <v>50.514635248318989</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16621,41 +16621,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D20" s="121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>529</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>551</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>530</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>552</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>531</v>
-      </c>
       <c r="L20" s="122" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18210,7 +18210,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
@@ -18259,7 +18259,7 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="468" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K52" s="468"/>
       <c r="L52" s="317">
@@ -18272,7 +18272,7 @@
     </row>
     <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="128"/>
       <c r="D54" s="128"/>
@@ -18741,7 +18741,7 @@
     </row>
     <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="275"/>
       <c r="D71" s="111"/>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>44.897845422547697</v>
+        <v>45.027086713310048</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.370533064722878</v>
+        <v>46.504013580106665</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.254145650028008</v>
+        <v>47.39016970018465</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.137758235333116</v>
+        <v>48.27632582026262</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.43229576376816</v>
+        <v>48.571711193621951</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>44.861396063654986</v>
+        <v>44.990532432629969</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>47.774053335120009</v>
+        <v>47.911573972466222</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>49.587558193872589</v>
+        <v>49.730299119777044</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.450495924530365</v>
+        <v>51.59859943464469</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.082460250728559</v>
+        <v>52.232382910168759</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>44.827410647438001</v>
+        <v>44.956449187240615</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.148129124319979</v>
+        <v>49.289605125825211</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>51.93728830795385</v>
+        <v>52.086793080765183</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>54.879063602860363</v>
+        <v>55.037036462117008</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>55.894287034314225</v>
+        <v>56.055182278497327</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>44.795722613669255</v>
+        <v>44.924669937460337</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.49337814871155</v>
+        <v>50.638726534708127</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.303450101154567</v>
+        <v>54.459766020501505</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>58.427511269943174</v>
+        <v>58.595698560479995</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>59.874935983140261</v>
+        <v>60.047289777357932</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>44.766176661437335</v>
+        <v>44.895038935334206</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.810405165598411</v>
+        <v>51.959544697250855</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>56.686158480321716</v>
+        <v>56.849333176599615</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.100030533777108</v>
+        <v>62.278789403540962</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.031884069560022</v>
+        <v>64.216203902042224</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>44.738627988027602</v>
+        <v>44.86741096132382</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.099802245068069</v>
+        <v>53.252653387852128</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.085529155846679</v>
+        <v>59.255610592530573</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>65.900959562080786</v>
+        <v>66.090659646708986</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>68.372939413886485</v>
+        <v>68.569755249031857</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>44.712941579253965</v>
+        <v>44.841650612596183</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.362149036157255</v>
+        <v>54.518633924105131</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>61.501678647284393</v>
+        <v>61.678715123258243</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>69.834788206758716</v>
+        <v>70.035812066211548</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>72.906255950619013</v>
+        <v>73.116121224442963</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>44.688991547763401</v>
+        <v>44.817631639423574</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>55.598013027433367</v>
+        <v>55.75805542812904</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>63.934724289011911</v>
+        <v>64.118764440914106</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>73.906163307544276</v>
+        <v>74.11890687800441</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>77.640348744223132</v>
+        <v>77.863841403893247</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>44.666660516070557</v>
+        <v>44.795236326442108</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>56.807949802109277</v>
+        <v>56.971475082418173</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>66.38478423592629</v>
+        <v>66.575877040511585</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.119894181084547</v>
+        <v>78.344767242657142</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>82.584109983231642</v>
+        <v>82.821833572643186</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>44.645839041298679</v>
+        <v>44.774354915736787</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>57.992503287805988</v>
+        <v>58.159438380323635</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>68.851977469182756</v>
+        <v>69.050172245700665</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>82.480958301951404</v>
+        <v>82.718384962717337</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>87.746825682709044</v>
+        <v>87.99941047613963</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.561035319213296</v>
+        <v>44.689307080768025</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>63.55277333973693</v>
+        <v>63.735714021648363</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>81.449165840523676</v>
+        <v>81.683622421361292</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>106.68301864648302</v>
+        <v>106.99011247030762</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>117.1995633241461</v>
+        <v>117.53692968768189</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.501272866945669</v>
+        <v>44.629372598497675</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>68.553762071918413</v>
+        <v>68.75109841653375</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>94.493018869106578</v>
+        <v>94.765023006760401</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>135.4226192958219</v>
+        <v>135.81244187976759</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>153.77834849367596</v>
+        <v>154.22100920631331</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.459157372328058</v>
+        <v>44.587135871762257</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.05172495246606</v>
+        <v>73.262008968022215</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>107.99937416171707</v>
+        <v>108.31025719823751</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>169.55048418523012</v>
+        <v>170.03854598907063</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>199.20731814558968</v>
+        <v>199.78074902371179</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.42947795290025</v>
+        <v>44.557371018246471</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.097258977486618</v>
+        <v>77.319188318877366</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>121.98463088689543</v>
+        <v>122.33577137037783</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>210.07683582527955</v>
+        <v>210.68155529824773</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>255.62776169147398</v>
+        <v>256.36360238861141</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19265,19 +19265,19 @@
     </row>
     <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" s="153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D89" s="153" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="154" t="s">
         <v>99</v>
       </c>
-      <c r="E89" s="154" t="s">
-        <v>100</v>
-      </c>
       <c r="F89" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G89" s="323"/>
       <c r="H89" s="323"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>87.746825682709044</v>
+        <v>87.99941047613963</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>82.480958301951404</v>
+        <v>82.718384962717337</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>68.851977469182756</v>
+        <v>69.050172245700665</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>57.992503287805988</v>
+        <v>58.159438380323635</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.645839041298679</v>
+        <v>44.774354915736787</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19545,7 +19545,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -19555,16 +19555,16 @@
     </row>
     <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E3" s="97"/>
     </row>
     <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="449">
         <v>2</v>
@@ -19592,7 +19592,7 @@
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="446" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
@@ -19605,7 +19605,7 @@
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="447">
         <f>Normalized_FCF!G8</f>
@@ -19618,7 +19618,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
@@ -19631,7 +19631,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
@@ -19651,7 +19651,7 @@
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C11" s="448"/>
       <c r="D11" s="469"/>
@@ -19661,7 +19661,7 @@
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="249">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19674,7 +19674,7 @@
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="249">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19687,7 +19687,7 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19700,7 +19700,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19710,21 +19710,21 @@
     </row>
     <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="137">
         <v>10</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19734,35 +19734,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C22" s="324">
         <v>0.11</v>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>82.480958301951404</v>
+        <v>82.718384962717337</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19786,7 +19786,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C23" s="324">
         <v>0.08</v>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>68.851977469182756</v>
+        <v>69.050172245700665</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19809,7 +19809,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C24" s="324">
         <v>0.05</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>57.992503287805988</v>
+        <v>58.159438380323635</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19832,11 +19832,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>68.862905090392289</v>
+        <v>69.061131322759749</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19846,33 +19846,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C29" s="324">
         <v>0.12</v>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>87.746825682709044</v>
+        <v>87.99941047613963</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19895,7 +19895,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C30" s="324">
         <v>0</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.645839041298679</v>
+        <v>44.774354915736787</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19922,12 +19922,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19938,7 +19938,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19947,66 +19947,66 @@
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>37.299999999999997</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23944009247229556</v>
+        <v>0.24987629123293953</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2866898776336831E-2</v>
+        <v>5.2860509617634992E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>70.48463987678511</v>
+        <v>70.687534375415567</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F36" s="331" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -20020,24 +20020,24 @@
         <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
         <v>0.28146521974317368</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
@@ -20047,7 +20047,7 @@
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -20057,15 +20057,15 @@
     </row>
     <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E44" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45" s="150">
         <f>C18</f>
@@ -20073,52 +20073,52 @@
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="138">
         <v>2.38559171477595E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.36964304166235</v>
+        <v>50.514635248318989</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E47" s="221" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E49" s="222" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
@@ -20128,19 +20128,19 @@
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E51" s="221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="218" t="str">
         <f>IF(C46&gt;8%,"Y","N")</f>
@@ -20150,23 +20150,23 @@
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452497</v>
+        <v>0.21911288198452494</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
@@ -20176,12 +20176,12 @@
     </row>
     <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C57" s="219">
         <f>Holding_Period</f>
@@ -20191,7 +20191,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C58" s="155">
         <f>C33</f>
@@ -20204,34 +20204,34 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E60" s="413"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C61" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D61" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E61" s="154" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.082221154658669</v>
+        <v>32.174571859542809</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.340109183789302</v>
+        <v>32.432459888673442</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,12 +20251,12 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54117508097759504</v>
+        <v>0.5411855827870955</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>40.789722150917306</v>
+        <v>40.907137948735858</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.088842521287674</v>
+        <v>41.206258319106226</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,33 +20276,33 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41705252955657457</v>
+        <v>0.41706471044437277</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C65" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D65" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E65" s="154" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>50.520598179591325</v>
+        <v>50.66602492017023</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>50.863187823474611</v>
+        <v>51.008614564053516</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,12 +20322,12 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27837912043831037</v>
+        <v>0.27839307149757064</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.135046161286567</v>
+        <v>57.299513009175513</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>57.506003443545133</v>
+        <v>57.670470291434079</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18413425188705024</v>
+        <v>0.18414935814352995</v>
       </c>
     </row>
   </sheetData>
@@ -20377,7 +20377,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B2" s="345"/>
       <c r="C2" s="345"/>
@@ -20391,7 +20391,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20400,7 +20400,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20417,14 +20417,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C5" s="355" t="str">
         <f>Thesis!C5</f>
         <v>1698.hk</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
@@ -20433,7 +20433,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C6" s="352" t="str">
         <f>Thesis!C6</f>
@@ -20443,7 +20443,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C7" s="352" t="str">
         <f>Market_currency</f>
@@ -20454,16 +20454,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>37.299999999999997</v>
+        <v>36.479999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
@@ -20472,18 +20472,18 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>115958.37905439999</v>
+        <v>113409.15999743999</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23944009247229556</v>
+        <v>0.24987629123293953</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,31 +20491,31 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
-        <v>498</v>
-      </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="B12" s="474" t="s">
+        <v>497</v>
+      </c>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C15" s="358" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="351" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E15" s="344" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20524,30 +20524,30 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C16" s="358" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="351" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1321619999999999</v>
+        <v>1.135421</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
         <v>0.02</v>
       </c>
       <c r="D17" s="351" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E17" s="344" t="str">
         <f>Reporting_currency</f>
@@ -20561,10 +20561,10 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>70.48463987678511</v>
+        <v>70.687534375415567</v>
       </c>
       <c r="D18" s="350" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E18" s="426">
         <f>Thesis!E18</f>
@@ -20573,14 +20573,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="343" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20593,14 +20593,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C21" s="361" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="362" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E21" s="363">
         <f>Holding_Period</f>
@@ -20609,14 +20609,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.340109183789302</v>
+        <v>32.432459888673442</v>
       </c>
       <c r="D22" s="365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
@@ -20625,14 +20625,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.088842521287674</v>
+        <v>41.206258319106226</v>
       </c>
       <c r="D23" s="365" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
@@ -20641,14 +20641,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>50.863187823474611</v>
+        <v>51.008614564053516</v>
       </c>
       <c r="D24" s="365" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
@@ -20657,14 +20657,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>57.506003443545133</v>
+        <v>57.670470291434079</v>
       </c>
       <c r="D25" s="365" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E25" s="368">
         <f>Thesis!E25</f>
@@ -20673,7 +20673,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B27" s="345"/>
       <c r="C27" s="345"/>
@@ -20682,26 +20682,26 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
+        <v>498</v>
+      </c>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
-        <v>500</v>
-      </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C32" s="370">
         <f>scaling_factor</f>
@@ -20710,7 +20710,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20719,7 +20719,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
@@ -20736,7 +20736,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20745,7 +20745,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="373">
         <f>Normalized_FCF!C15</f>
@@ -20758,7 +20758,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
@@ -20771,7 +20771,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20780,7 +20780,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="373">
         <f>Normalized_FCF!C9</f>
@@ -20793,7 +20793,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20802,7 +20802,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
@@ -20817,7 +20817,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="376">
         <f>Normalized_FCF!C45</f>
@@ -20832,7 +20832,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
@@ -20845,12 +20845,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="373">
         <f>Normalized_FCF!C13</f>
@@ -20863,7 +20863,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20872,7 +20872,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
@@ -20885,16 +20885,16 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>507</v>
-      </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+        <v>506</v>
+      </c>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="373">
         <f>Normalized_FCF!C17</f>
@@ -20906,26 +20906,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
+        <v>507</v>
+      </c>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
-        <v>509</v>
-      </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
@@ -20951,24 +20951,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.2553734259727323E-2</v>
+        <v>6.4143933883932178E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8069705093833782E-3</v>
+        <v>3.8925438596491228E-3</v>
       </c>
       <c r="E63" s="372" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
@@ -20977,18 +20977,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C65" s="381" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D65" s="381" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
@@ -21043,7 +21043,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B71" s="345"/>
       <c r="C71" s="345"/>
@@ -21056,40 +21056,40 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
-        <v>510</v>
-      </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="B73" s="474" t="s">
+        <v>509</v>
+      </c>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
-        <v>479</v>
-      </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="B74" s="477" t="s">
+        <v>478</v>
+      </c>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
-        <v>511</v>
-      </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="B77" s="474" t="s">
+        <v>510</v>
+      </c>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="373">
         <f>DCF!F4</f>
@@ -21102,11 +21102,11 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11508066230677137</v>
+        <v>-0.11541192927957014</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="388">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -21124,7 +21124,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -21133,12 +21133,12 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
@@ -21151,7 +21151,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C85" s="390">
         <f>BS!C66</f>
@@ -21164,11 +21164,11 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4649966494470075</v>
+        <v>9.4922422415800689</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21177,12 +21177,12 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="373">
         <f>DCF!F6</f>
@@ -21195,11 +21195,11 @@
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0941765919035209</v>
+        <v>6.1117190650769828</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21208,11 +21208,11 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.444092579043758</v>
+        <v>15.488549377377483</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21221,7 +21221,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B94" s="345"/>
       <c r="C94" s="345"/>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
-        <v>514</v>
-      </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="B96" s="474" t="s">
+        <v>513</v>
+      </c>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
-        <v>515</v>
-      </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="B97" s="477" t="s">
+        <v>514</v>
+      </c>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
-        <v>516</v>
-      </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="B98" s="477" t="s">
+        <v>515</v>
+      </c>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21268,13 +21268,13 @@
     <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C101" s="368">
         <f>E25+C103</f>
@@ -21284,7 +21284,7 @@
     <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="383">
         <f>E25</f>
@@ -21294,7 +21294,7 @@
     <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C103" s="383">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -21304,7 +21304,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21317,29 +21317,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C106" s="392"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
-        <v>517</v>
-      </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="B107" s="474" t="s">
+        <v>516</v>
+      </c>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
-        <v>536</v>
-      </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="B108" s="474" t="s">
+        <v>535</v>
+      </c>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21347,17 +21347,17 @@
     <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.387486460772795</v>
+        <v>11.420266061550475</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21367,11 +21367,11 @@
     <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>60.775890172293018</v>
+        <v>60.950837420188194</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
-        <v>518</v>
-      </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="B114" s="474" t="s">
+        <v>517</v>
+      </c>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21397,25 +21397,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C117" s="342" t="s">
         <v>378</v>
       </c>
-      <c r="C117" s="342" t="s">
+      <c r="D117" s="342" t="s">
+        <v>98</v>
+      </c>
+      <c r="E117" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="D117" s="342" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="342" t="s">
+      <c r="F117" s="342" t="s">
         <v>380</v>
-      </c>
-      <c r="F117" s="342" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>87.75 HKD</v>
+        <v>88 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.48 HKD</v>
+        <v>82.72 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>68.85 HKD</v>
+        <v>69.05 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>57.99 HKD</v>
+        <v>58.16 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.65 HKD</v>
+        <v>44.77 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21532,7 +21532,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21541,11 +21541,11 @@
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>70.48463987678511</v>
+        <v>70.687534375415567</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,17 +21553,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
-        <v>520</v>
-      </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="B127" s="472" t="s">
+        <v>519</v>
+      </c>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B129" s="345"/>
       <c r="C129" s="345"/>
@@ -21572,31 +21572,31 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
+        <v>520</v>
+      </c>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
-        <v>522</v>
-      </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C135" s="405">
         <f>E21</f>
@@ -21605,7 +21605,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
@@ -21618,33 +21618,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.082221154658669</v>
+        <v>32.174571859542809</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.340109183789302</v>
+        <v>32.432459888673442</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21665,7 +21665,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>40.789722150917306</v>
+        <v>40.907137948735858</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.088842521287674</v>
+        <v>41.206258319106226</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21686,26 +21686,26 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>50.520598179591325</v>
+        <v>50.66602492017023</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>50.863187823474611</v>
+        <v>51.008614564053516</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21726,7 +21726,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.135046161286567</v>
+        <v>57.299513009175513</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>57.506003443545133</v>
+        <v>57.670470291434079</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21747,7 +21747,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B147" s="345"/>
       <c r="C147" s="345"/>
@@ -21756,51 +21756,51 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
-        <v>523</v>
-      </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="B149" s="475" t="s">
+        <v>522</v>
+      </c>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
-        <v>524</v>
-      </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="B152" s="476" t="s">
+        <v>523</v>
+      </c>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C158" s="470"/>
       <c r="D158" s="470"/>
@@ -21809,58 +21809,55 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
+        <v>387</v>
+      </c>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
-        <v>389</v>
-      </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21875,12 +21872,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3EAA8-8E71-4315-A8E3-C5EBB8C27FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F8DCCC-82E5-4A49-8A99-51B5F1CC9E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>36.479999999999997</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>113409.15999743999</v>
+        <v>114652.68148864001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24987629123293953</v>
+        <v>0.2490437638604216</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.135421</v>
+        <v>1.1456630000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>70.687534375415567</v>
+        <v>71.325167224440747</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.432459888673442</v>
+        <v>32.722688768521046</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.206258319106226</v>
+        <v>41.575258810440246</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.008614564053516</v>
+        <v>51.465644535519957</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>57.670470291434079</v>
+        <v>58.187337261694438</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4143933883932178E-2</v>
+        <v>6.402056072754185E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8925438596491228E-3</v>
+        <v>3.8503253796095438E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11541192927957014</v>
+        <v>-0.11645299596732858</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4922422415800689</v>
+        <v>9.5778664682222256</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1117190650769828</v>
+        <v>6.1668494763204942</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.488549377377483</v>
+        <v>15.628262948575392</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.420266061550475</v>
+        <v>11.523281916464557</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88 HKD</v>
+        <v>88.79 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8679219674525671E-2</v>
+        <v>-6.869476292166872E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.72 HKD</v>
+        <v>83.46 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9231597936145337E-2</v>
+        <v>-4.924778272349533E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.05 HKD</v>
+        <v>69.67 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8830843808505649E-3</v>
+        <v>9.8648422019122876E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.16 HKD</v>
+        <v>58.68 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9479147887837003E-2</v>
+        <v>6.945866235009944E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.77 HKD</v>
+        <v>45.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16715157010712198</v>
+        <v>0.16712702100582852</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>70.687534375415567</v>
+        <v>71.325167224440747</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.174571859542809</v>
+        <v>32.464800739390412</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.432459888673442</v>
+        <v>32.722688768521046</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>40.907137948735858</v>
+        <v>41.276138440069879</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.206258319106226</v>
+        <v>41.575258810440246</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>50.66602492017023</v>
+        <v>51.12305489163667</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.008614564053516</v>
+        <v>51.465644535519957</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.299513009175513</v>
+        <v>57.816379979435872</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>57.670470291434079</v>
+        <v>58.187337261694438</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.32303027236977</v>
+        <v>29.587536984901607</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.420266061550475</v>
+        <v>11.523281916464557</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-358.79303600000003</v>
+        <v>-362.02950800000002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11541192927957014</v>
+        <v>-0.11645299596732857</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29509.518067703193</v>
+        <v>29775.706982695447</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.4922422415800689</v>
+        <v>9.5778664682222256</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19000.135014</v>
+        <v>19171.524642</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1117190650769828</v>
+        <v>6.1668494763204942</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48150.860045703193</v>
+        <v>48585.202116695451</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.488549377377481</v>
+        <v>15.62826294857539</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8925438596491228E-3</v>
+        <v>3.8503253796095438E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8925438596491228E-3</v>
+        <v>3.8503253796095438E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.1107456140350878E-3</v>
+        <v>2.0878524945770064E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3399707080858456</v>
+        <v>2.361078279631744</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.7984543659837633</v>
+        <v>2.8236976630659965</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0329473919761174</v>
+        <v>2.0512854773106493</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4041488990970805</v>
+        <v>1.4168149436960025</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96327169039898053</v>
+        <v>0.97196082742662615</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.78927926016892891</v>
+        <v>0.79639890846031181</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1571266232535875</v>
+        <v>1.1675644175830595</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2750149139169</v>
+        <v>1.2865161128099423</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4143933883932178E-2</v>
+        <v>6.402056072754185E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6712016611397024E-2</v>
+        <v>7.6564470256670181E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5727724560748836E-2</v>
+        <v>5.5620538972631486E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8490923769108572E-2</v>
+        <v>3.8416891098047787E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.6405473969270302E-2</v>
+        <v>2.6354686210049515E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.1635944631823712E-2</v>
+        <v>2.1594330489704765E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.1719479804100538E-2</v>
+        <v>3.1658471192599229E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.4951066719213268E-2</v>
+        <v>3.4883842538230535E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10010655224195536</v>
+        <v>9.9020797879244324E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2684530951119588E-2</v>
+        <v>6.2004655344274455E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.602802807214014E-2</v>
+        <v>4.552880867873297E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3850881181790415E-2</v>
+        <v>3.3483734965068172E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8348680124890908E-2</v>
+        <v>2.8041210709219635E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6822422457712112E-2</v>
+        <v>3.642304694298637E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5067714107835504E-2</v>
+        <v>3.4687370137034677E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.488549377377483</v>
+        <v>15.628262948575392</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.135421</v>
+        <v>1.1456630000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>189484.19059660297</v>
+        <v>191193.42186860731</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.514635248318989</v>
+        <v>50.970299617934558</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.027086713310048</v>
+        <v>45.433250966144655</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.504013580106665</v>
+        <v>46.923500367023109</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.39016970018465</v>
+        <v>47.817650007550192</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.27632582026262</v>
+        <v>48.711799648077267</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.571711193621951</v>
+        <v>49.009849528252964</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>44.990532432629969</v>
+        <v>45.396366949672547</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>47.911573972466222</v>
+        <v>48.343757577160872</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>49.730299119777044</v>
+        <v>50.178888430336528</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.59859943464469</v>
+        <v>52.064041641024204</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.232382910168759</v>
+        <v>52.703542124033881</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>44.956449187240615</v>
+        <v>45.361976258323253</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.289605125825211</v>
+        <v>49.734219181491525</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.086793080765183</v>
+        <v>52.556639009925554</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.037036462117008</v>
+        <v>55.533494892465761</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.055182278497327</v>
+        <v>56.560824834779424</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>44.924669937460337</v>
+        <v>45.32991034564327</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.638726534708127</v>
+        <v>51.0955102626544</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.459766020501505</v>
+        <v>54.951017215945292</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>58.595698560479995</v>
+        <v>59.124257698153549</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.047289777357932</v>
+        <v>60.588942910336542</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>44.895038935334206</v>
+        <v>45.300012058762171</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>51.959544697250855</v>
+        <v>52.42824278966701</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>56.849333176599615</v>
+        <v>57.36213932550362</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.278789403540962</v>
+        <v>62.840571650893331</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.216203902042224</v>
+        <v>64.795462485743528</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>44.86741096132382</v>
+        <v>45.272134868197021</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.252653387852128</v>
+        <v>53.733015893036004</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.255610592530573</v>
+        <v>59.790122428835083</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.090659646708986</v>
+        <v>66.686826650931735</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>68.569755249031857</v>
+        <v>69.188284792928428</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>44.841650612596183</v>
+        <v>45.246142149721372</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.518633924105131</v>
+        <v>55.010416134096573</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>61.678715123258243</v>
+        <v>62.235084434987037</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.035812066211548</v>
+        <v>70.667566091530915</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.116121224442963</v>
+        <v>73.775661001830173</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>44.817631639423574</v>
+        <v>45.221906514779036</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>55.75805542812904</v>
+        <v>56.261017768701301</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.118764440914106</v>
+        <v>64.697144077545673</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.11890687800441</v>
+        <v>74.787492225857349</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>77.863841403893247</v>
+        <v>78.566207718818433</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>44.795236326442108</v>
+        <v>45.199309186161479</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>56.971475082418173</v>
+        <v>57.485383005377258</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>66.575877040511585</v>
+        <v>67.176420920401895</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.344767242657142</v>
+        <v>79.051471721523839</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>82.821833572643186</v>
+        <v>83.568923171524148</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>44.774354915736787</v>
+        <v>45.17823941588869</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.159438380323635</v>
+        <v>58.68406225806703</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.050172245700665</v>
+        <v>69.673035363557815</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>82.718384962717337</v>
+        <v>83.464541409346523</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>87.99941047613963</v>
+        <v>88.793204110480218</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.689307080768025</v>
+        <v>45.092424411803144</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>63.735714021648363</v>
+        <v>64.310638373945636</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>81.683622421361292</v>
+        <v>82.42044485184266</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>106.99011247030762</v>
+        <v>107.95521064263392</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>117.53692968768189</v>
+        <v>118.59716481972653</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.629372598497675</v>
+        <v>45.031949293973462</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>68.75109841653375</v>
+        <v>69.371263756070491</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>94.765023006760401</v>
+        <v>95.619845460841532</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>135.81244187976759</v>
+        <v>137.03753022121327</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>154.22100920631331</v>
+        <v>155.61215097336805</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.587135871762257</v>
+        <v>44.989331573267336</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.262008968022215</v>
+        <v>73.922864717431906</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>108.31025719823751</v>
+        <v>109.28726366035539</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>170.03854598907063</v>
+        <v>171.572368939342</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>199.78074902371179</v>
+        <v>201.5828598103723</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.557371018246471</v>
+        <v>44.959298227597792</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.319188318877366</v>
+        <v>78.016641621891793</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>122.33577137037783</v>
+        <v>123.43929417854804</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>210.68155529824773</v>
+        <v>212.58199618261102</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>256.36360238861141</v>
+        <v>258.67611555832048</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>87.99941047613963</v>
+        <v>88.793204110480218</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>82.718384962717337</v>
+        <v>83.464541409346523</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.050172245700665</v>
+        <v>69.673035363557815</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.159438380323635</v>
+        <v>58.68406225806703</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.774354915736787</v>
+        <v>45.17823941588869</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>82.718384962717337</v>
+        <v>83.464541409346523</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.050172245700665</v>
+        <v>69.673035363557815</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.159438380323635</v>
+        <v>58.68406225806703</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.061131322759749</v>
+        <v>69.684093296342866</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>87.99941047613963</v>
+        <v>88.793204110480218</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.774354915736787</v>
+        <v>45.17823941588869</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>36.479999999999997</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24987629123293953</v>
+        <v>0.2490437638604216</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2860509617634992E-2</v>
+        <v>5.2840667162013577E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>70.687534375415567</v>
+        <v>71.325167224440747</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.514635248318989</v>
+        <v>50.970299617934558</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452494</v>
+        <v>0.21911288198452492</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.174571859542809</v>
+        <v>32.464800739390412</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.432459888673442</v>
+        <v>32.722688768521046</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.5411855827870955</v>
+        <v>0.54121819770079593</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>40.907137948735858</v>
+        <v>41.276138440069879</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.206258319106226</v>
+        <v>41.575258810440246</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41706471044437277</v>
+        <v>0.41710253998263602</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>50.66602492017023</v>
+        <v>51.12305489163667</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.008614564053516</v>
+        <v>51.465644535519957</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27839307149757064</v>
+        <v>0.2784363985636138</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.299513009175513</v>
+        <v>57.816379979435872</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>57.670470291434079</v>
+        <v>58.187337261694438</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18414935814352995</v>
+        <v>0.18419627284441076</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>36.479999999999997</v>
+        <v>36.880000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>113409.15999743999</v>
+        <v>114652.68148864001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24987629123293953</v>
+        <v>0.2490437638604216</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.135421</v>
+        <v>1.1456630000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>70.687534375415567</v>
+        <v>71.325167224440747</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.432459888673442</v>
+        <v>32.722688768521046</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.206258319106226</v>
+        <v>41.575258810440246</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.008614564053516</v>
+        <v>51.465644535519957</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>57.670470291434079</v>
+        <v>58.187337261694438</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4143933883932178E-2</v>
+        <v>6.402056072754185E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8925438596491228E-3</v>
+        <v>3.8503253796095438E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11541192927957014</v>
+        <v>-0.11645299596732858</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.4922422415800689</v>
+        <v>9.5778664682222256</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1117190650769828</v>
+        <v>6.1668494763204942</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.488549377377483</v>
+        <v>15.628262948575392</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.420266061550475</v>
+        <v>11.523281916464557</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>60.950837420188194</v>
+        <v>61.500640952849274</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88 HKD</v>
+        <v>88.79 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>82.72 HKD</v>
+        <v>83.46 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.05 HKD</v>
+        <v>69.67 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.16 HKD</v>
+        <v>58.68 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.77 HKD</v>
+        <v>45.18 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>70.687534375415567</v>
+        <v>71.325167224440747</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.174571859542809</v>
+        <v>32.464800739390412</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.432459888673442</v>
+        <v>32.722688768521046</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>40.907137948735858</v>
+        <v>41.276138440069879</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.206258319106226</v>
+        <v>41.575258810440246</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>50.66602492017023</v>
+        <v>51.12305489163667</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.008614564053516</v>
+        <v>51.465644535519957</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.299513009175513</v>
+        <v>57.816379979435872</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>57.670470291434079</v>
+        <v>58.187337261694438</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F8DCCC-82E5-4A49-8A99-51B5F1CC9E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4592AA-0027-4E67-9D17-2CBDB9B9BDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>36.880000000000003</v>
+        <v>39.78</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>114652.68148864001</v>
+        <v>123668.21229984</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2490437638604216</v>
+        <v>0.21817681151921156</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.325167224440747</v>
+        <v>71.385369427624425</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.722688768521046</v>
+        <v>32.750090772701142</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.575258810440246</v>
+        <v>41.610098048393759</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.465644535519957</v>
+        <v>51.508795090334246</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.187337261694438</v>
+        <v>58.236137335922287</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.402056072754185E-2</v>
+        <v>5.9403498095395614E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8503253796095438E-3</v>
+        <v>3.5696329813976867E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11645299596732858</v>
+        <v>-0.11655128843823877</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5778664682222256</v>
+        <v>9.5859506927060121</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1668494763204942</v>
+        <v>6.1720546225490116</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.628262948575392</v>
+        <v>15.641454026816787</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.523281916464557</v>
+        <v>11.533008174197606</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.79 HKD</v>
+        <v>88.87 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.869476292166872E-2</v>
+        <v>-6.8696216095144758E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.46 HKD</v>
+        <v>83.53 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.924778272349533E-2</v>
+        <v>-4.9249295875662846E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.67 HKD</v>
+        <v>69.73 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8648422019122876E-3</v>
+        <v>9.8631367008609853E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.68 HKD</v>
+        <v>58.73 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.945866235009944E-2</v>
+        <v>6.9456747114085615E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.18 HKD</v>
+        <v>45.22 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712702100582852</v>
+        <v>0.16712472586195914</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.325167224440747</v>
+        <v>71.385369427624425</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.464800739390412</v>
+        <v>32.492202743570509</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.722688768521046</v>
+        <v>32.750090772701142</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.276138440069879</v>
+        <v>41.310977678023391</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.575258810440246</v>
+        <v>41.610098048393759</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.12305489163667</v>
+        <v>51.166205446450959</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.465644535519957</v>
+        <v>51.508795090334246</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.816379979435872</v>
+        <v>57.865180053663721</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.187337261694438</v>
+        <v>58.236137335922287</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.587536984901607</v>
+        <v>29.612510426711633</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.523281916464557</v>
+        <v>11.533008174197606</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-362.02950800000002</v>
+        <v>-362.33508</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11645299596732857</v>
+        <v>-0.11655128843823877</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29775.706982695447</v>
+        <v>29800.839249908637</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5778664682222256</v>
+        <v>9.5859506927060139</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19171.524642</v>
+        <v>19187.706420000002</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1668494763204942</v>
+        <v>6.1720546225490125</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48585.202116695451</v>
+        <v>48626.210589908638</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.62826294857539</v>
+        <v>15.641454026816788</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8503253796095438E-3</v>
+        <v>3.5696329813976867E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8503253796095438E-3</v>
+        <v>3.5696329813976867E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0878524945770064E-3</v>
+        <v>1.935646053293112E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.361078279631744</v>
+        <v>2.3630711542348375</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8236976630659965</v>
+        <v>2.8260810128295697</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0512854773106493</v>
+        <v>2.0530168704485612</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4168149436960025</v>
+        <v>1.4180108102383921</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97196082742662615</v>
+        <v>0.97278121363105241</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79639890846031181</v>
+        <v>0.7970711111451162</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1675644175830595</v>
+        <v>1.1685499035346898</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2865161128099423</v>
+        <v>1.2876020002664519</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.402056072754185E-2</v>
+        <v>5.9403498095395614E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6564470256670181E-2</v>
+        <v>7.1042760503508537E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5620538972631486E-2</v>
+        <v>5.1609272761401738E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8416891098047787E-2</v>
+        <v>3.5646325043700154E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.6354686210049515E-2</v>
+        <v>2.4454027491982212E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.1594330489704765E-2</v>
+        <v>2.0036981175090906E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.1658471192599229E-2</v>
+        <v>2.9375311803285314E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.4883842538230535E-2</v>
+        <v>3.2368074415949015E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9020797879244324E-2</v>
+        <v>9.1802087123844425E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2004655344274455E-2</v>
+        <v>5.7484456739488245E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.552880867873297E-2</v>
+        <v>4.2209715034481447E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3483734965068172E-2</v>
+        <v>3.1042738700646416E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8041210709219635E-2</v>
+        <v>2.5996979662041737E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.642304694298637E-2</v>
+        <v>3.3767772027585158E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4687370137034677E-2</v>
+        <v>3.2158627718799369E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.628262948575392</v>
+        <v>15.641454026816787</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191193.42186860731</v>
+        <v>191354.79920116227</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.970299617934558</v>
+        <v>51.013321239240767</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.433250966144655</v>
+        <v>45.471599026337103</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.923500367023109</v>
+        <v>46.963106276313106</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.817650007550192</v>
+        <v>47.858010626298729</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.711799648077267</v>
+        <v>48.75291497628433</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>49.009849528252964</v>
+        <v>49.051216426279538</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.396366949672547</v>
+        <v>45.434683877809647</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.343757577160872</v>
+        <v>48.384562258447694</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.178888430336528</v>
+        <v>50.22124205885742</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.064041641024204</v>
+        <v>52.107986438287327</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.703542124033881</v>
+        <v>52.748026693435122</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.361976258323253</v>
+        <v>45.400264158902914</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.734219181491525</v>
+        <v>49.776197485712316</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.556639009925554</v>
+        <v>52.600999585350088</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.533494892465761</v>
+        <v>55.580368091269435</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.560824834779424</v>
+        <v>56.608565154240935</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.32991034564327</v>
+        <v>45.368171180901307</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.0955102626544</v>
+        <v>51.138637568348997</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.951017215945292</v>
+        <v>54.997398772867193</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.124257698153549</v>
+        <v>59.17416169016002</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.588942910336542</v>
+        <v>60.640083173916921</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.300012058762171</v>
+        <v>45.338247658289099</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.42824278966701</v>
+        <v>52.472494991909386</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.36213932550362</v>
+        <v>57.410555996660641</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.840571650893331</v>
+        <v>62.89361240789291</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.795462485743528</v>
+        <v>64.850153273718448</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.272134868197021</v>
+        <v>45.310346937904733</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.733015893036004</v>
+        <v>53.778369392597888</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.790122428835083</v>
+        <v>59.840588445795291</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.686826650931735</v>
+        <v>66.743113850022084</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.188284792928428</v>
+        <v>69.246683354630051</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.246142149721372</v>
+        <v>45.284332280203699</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>55.010416134096573</v>
+        <v>55.056847826838393</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.235084434987037</v>
+        <v>62.287614128839969</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.667566091530915</v>
+        <v>70.727213244673251</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.775661001830173</v>
+        <v>73.83793155101327</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.221906514779036</v>
+        <v>45.260076189107167</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.261017768701301</v>
+        <v>56.308505035185718</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.697144077545673</v>
+        <v>64.751751879598274</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.787492225857349</v>
+        <v>74.850616813962574</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.566207718818433</v>
+        <v>78.632521742108082</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.199309186161479</v>
+        <v>45.23745978715236</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.485383005377258</v>
+        <v>57.533903700700577</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.176420920401895</v>
+        <v>67.233121362879317</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>79.051471721523839</v>
+        <v>79.118195333227035</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.568923171524148</v>
+        <v>83.639459750524125</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.17823941588869</v>
+        <v>45.216372232882136</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.68406225806703</v>
+        <v>58.733594701903954</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.673035363557815</v>
+        <v>69.731843080309204</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.464541409346523</v>
+        <v>83.534989884633603</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.793204110480218</v>
+        <v>88.868150258147409</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.092424411803144</v>
+        <v>45.130484796406833</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.310638373945636</v>
+        <v>64.364919944798146</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.42044485184266</v>
+        <v>82.490012054564332</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.95521064263392</v>
+        <v>108.04633053451435</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.59716481972653</v>
+        <v>118.69726708224235</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>45.031949293973462</v>
+        <v>45.069958634387937</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.371263756070491</v>
+        <v>69.429816761668221</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.619845460841532</v>
+        <v>95.700553653879652</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>137.03753022121327</v>
+        <v>137.15319712476509</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.61215097336805</v>
+        <v>155.74349583655317</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.989331573267336</v>
+        <v>45.027304942077663</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.922864717431906</v>
+        <v>73.985259514315231</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.28726366035539</v>
+        <v>109.37950787524194</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.572368939342</v>
+        <v>171.71718506831215</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.5828598103723</v>
+        <v>201.75300637654109</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.959298227597792</v>
+        <v>44.997246246680263</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>78.016641621891793</v>
+        <v>78.082491782408781</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.43929417854804</v>
+        <v>123.54348345364085</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.58199618261102</v>
+        <v>212.76142660002748</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.67611555832048</v>
+        <v>258.89445184372454</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.793204110480218</v>
+        <v>88.868150258147409</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.464541409346523</v>
+        <v>83.534989884633603</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.673035363557815</v>
+        <v>69.731843080309204</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.68406225806703</v>
+        <v>58.733594701903954</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.17823941588869</v>
+        <v>45.216372232882136</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.464541409346523</v>
+        <v>83.534989884633603</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.673035363557815</v>
+        <v>69.731843080309204</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.68406225806703</v>
+        <v>58.733594701903954</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.684093296342866</v>
+        <v>69.742910346572771</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.793204110480218</v>
+        <v>88.868150258147409</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.17823941588869</v>
+        <v>45.216372232882136</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>36.880000000000003</v>
+        <v>39.78</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2490437638604216</v>
+        <v>0.21817681151921156</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2840667162013577E-2</v>
+        <v>5.2838812048675306E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.325167224440747</v>
+        <v>71.385369427624425</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.970299617934558</v>
+        <v>51.013321239240767</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452492</v>
+        <v>0.21911288198452497</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.464800739390412</v>
+        <v>32.492202743570509</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.722688768521046</v>
+        <v>32.750090772701142</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54121819770079593</v>
+        <v>0.54122124694044604</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.276138440069879</v>
+        <v>41.310977678023391</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.575258810440246</v>
+        <v>41.610098048393759</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41710253998263602</v>
+        <v>0.41710607674894729</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.12305489163667</v>
+        <v>51.166205446450959</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.465644535519957</v>
+        <v>51.508795090334246</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.2784363985636138</v>
+        <v>0.27844044930582679</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.816379979435872</v>
+        <v>57.865180053663721</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.187337261694438</v>
+        <v>58.236137335922287</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18419627284441076</v>
+        <v>0.18420065900245519</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>36.880000000000003</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>114652.68148864001</v>
+        <v>123668.21229984</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2490437638604216</v>
+        <v>0.21817681151921156</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.325167224440747</v>
+        <v>71.385369427624425</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.722688768521046</v>
+        <v>32.750090772701142</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.575258810440246</v>
+        <v>41.610098048393759</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.465644535519957</v>
+        <v>51.508795090334246</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.187337261694438</v>
+        <v>58.236137335922287</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.402056072754185E-2</v>
+        <v>5.9403498095395614E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8503253796095438E-3</v>
+        <v>3.5696329813976867E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11645299596732858</v>
+        <v>-0.11655128843823877</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5778664682222256</v>
+        <v>9.5859506927060121</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1668494763204942</v>
+        <v>6.1720546225490116</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.628262948575392</v>
+        <v>15.641454026816787</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.523281916464557</v>
+        <v>11.533008174197606</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.500640952849274</v>
+        <v>61.552550737665051</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.79 HKD</v>
+        <v>88.87 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.46 HKD</v>
+        <v>83.53 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.67 HKD</v>
+        <v>69.73 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.68 HKD</v>
+        <v>58.73 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.18 HKD</v>
+        <v>45.22 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.325167224440747</v>
+        <v>71.385369427624425</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.464800739390412</v>
+        <v>32.492202743570509</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.722688768521046</v>
+        <v>32.750090772701142</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.276138440069879</v>
+        <v>41.310977678023391</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.575258810440246</v>
+        <v>41.610098048393759</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.12305489163667</v>
+        <v>51.166205446450959</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.465644535519957</v>
+        <v>51.508795090334246</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.816379979435872</v>
+        <v>57.865180053663721</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.187337261694438</v>
+        <v>58.236137335922287</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,15 +21852,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21875,12 +21872,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4592AA-0027-4E67-9D17-2CBDB9B9BDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2E2E93-22C8-4784-82DF-15A60FD47073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>39.78</v>
+        <v>39.68</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>123668.21229984</v>
+        <v>123357.33192704</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21817681151921156</v>
+        <v>0.21889015087297162</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.385369427624425</v>
+        <v>71.330334528333438</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.750090772701142</v>
+        <v>32.725040750265556</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.610098048393759</v>
+        <v>41.578249148341108</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.508795090334246</v>
+        <v>51.469348254288903</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.236137335922287</v>
+        <v>58.191525892677788</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9403498095395614E-2</v>
+        <v>5.9507291657873981E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5696329813976867E-3</v>
+        <v>3.5786290322580641E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11655128843823877</v>
+        <v>-0.11646143265304268</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5859506927060121</v>
+        <v>9.5785603571903248</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1720546225490116</v>
+        <v>6.167296246886127</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.641454026816787</v>
+        <v>15.629395171423411</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.533008174197606</v>
+        <v>11.524116745204827</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.87 HKD</v>
+        <v>88.8 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8696216095144758E-2</v>
+        <v>-6.869488774736611E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.53 HKD</v>
+        <v>83.47 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9249295875662846E-2</v>
+        <v>-4.9247912701286208E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.73 HKD</v>
+        <v>69.68 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8631367008609853E-3</v>
+        <v>9.8646957015954551E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.73 HKD</v>
+        <v>58.69 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9456747114085615E-2</v>
+        <v>6.9458497833812402E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.22 HKD</v>
+        <v>45.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712472586195914</v>
+        <v>0.16712682385592822</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.385369427624425</v>
+        <v>71.330334528333438</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.492202743570509</v>
+        <v>32.467152721134923</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.750090772701142</v>
+        <v>32.725040750265556</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.310977678023391</v>
+        <v>41.27912877797074</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.610098048393759</v>
+        <v>41.578249148341108</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.166205446450959</v>
+        <v>51.126758610405616</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.508795090334246</v>
+        <v>51.469348254288903</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.865180053663721</v>
+        <v>57.820568610419222</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.236137335922287</v>
+        <v>58.191525892677788</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.612510426711633</v>
+        <v>29.589680517135559</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.533008174197606</v>
+        <v>11.524116745204827</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-362.33508</v>
+        <v>-362.05573599999997</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11655128843823877</v>
+        <v>-0.11646143265304265</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29800.839249908637</v>
+        <v>29777.864147306296</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5859506927060139</v>
+        <v>9.5785603571903266</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19187.706420000002</v>
+        <v>19172.913563999999</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1720546225490125</v>
+        <v>6.167296246886127</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48626.210589908638</v>
+        <v>48588.721975306296</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.641454026816788</v>
+        <v>15.629395171423411</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5696329813976867E-3</v>
+        <v>3.5786290322580641E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5696329813976867E-3</v>
+        <v>3.5786290322580641E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.935646053293112E-3</v>
+        <v>1.9405241935483871E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3630711542348375</v>
+        <v>2.3612493329844395</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8260810128295697</v>
+        <v>2.823902231866799</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0530168704485612</v>
+        <v>2.0514340870629209</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4180108102383921</v>
+        <v>1.4169175878769933</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97278121363105241</v>
+        <v>0.97203124320218692</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.7970711111451162</v>
+        <v>0.79645660527813877</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1685499035346898</v>
+        <v>1.1676490042779768</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2876020002664519</v>
+        <v>1.2866093172141719</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9403498095395614E-2</v>
+        <v>5.9507291657873981E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1042760503508537E-2</v>
+        <v>7.1166890924062476E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1609272761401738E-2</v>
+        <v>5.1699447758642159E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5646325043700154E-2</v>
+        <v>3.570860856544842E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.4454027491982212E-2</v>
+        <v>2.4496755121022857E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0036981175090906E-2</v>
+        <v>2.0071991060436965E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.9375311803285314E-2</v>
+        <v>2.9426638212650624E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.2368074415949015E-2</v>
+        <v>3.2424629970115221E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1802087123844425E-2</v>
+        <v>9.2033443190184763E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7484456739488245E-2</v>
+        <v>5.7629326842158324E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2209715034481447E-2</v>
+        <v>4.23160903243869E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1042738700646416E-2</v>
+        <v>3.1120971409065383E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5996979662041737E-2</v>
+        <v>2.6062496243851319E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3767772027585158E-2</v>
+        <v>3.3852872259509517E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2158627718799369E-2</v>
+        <v>3.2239672647526189E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.641454026816787</v>
+        <v>15.629395171423411</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191354.79920116227</v>
+        <v>191207.27328391449</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>51.013321239240767</v>
+        <v>50.973992270021846</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.471599026337103</v>
+        <v>45.436542474930562</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.963106276313106</v>
+        <v>46.926899840105904</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.858010626298729</v>
+        <v>47.821114259211129</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.75291497628433</v>
+        <v>48.715328678316332</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>49.051216426279538</v>
+        <v>49.013400151351412</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.434683877809647</v>
+        <v>45.39965578631719</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.384562258447694</v>
+        <v>48.347259943806989</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.22124205885742</v>
+        <v>50.182523746952072</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.107986438287327</v>
+        <v>52.067813531585557</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.748026693435122</v>
+        <v>52.707360344571931</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.400264158902914</v>
+        <v>45.365262603460899</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.776197485712316</v>
+        <v>49.737822283094751</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.600999585350088</v>
+        <v>52.560446587754129</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.580368091269435</v>
+        <v>55.537518134969069</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.608565154240935</v>
+        <v>56.564922504391937</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.368171180901307</v>
+        <v>45.333194367697466</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.138637568348997</v>
+        <v>51.099211985893952</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.997398772867193</v>
+        <v>54.954998259610761</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.17416169016002</v>
+        <v>59.12854108112824</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.640083173916921</v>
+        <v>60.593332405555941</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.338247658289099</v>
+        <v>45.303293914771196</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.472494991909386</v>
+        <v>52.432041065557506</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.410555996660641</v>
+        <v>57.3662950480538</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.89361240789291</v>
+        <v>62.845124270160092</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.850153273718448</v>
+        <v>64.800156731247057</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.310346937904733</v>
+        <v>45.275414704583511</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.778369392597888</v>
+        <v>53.736908695997357</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.840588445795291</v>
+        <v>59.794454051800635</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.743113850022084</v>
+        <v>66.691657920346927</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.246683354630051</v>
+        <v>69.193297285814907</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.284332280203699</v>
+        <v>45.249420103009918</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>55.056847826838393</v>
+        <v>55.014401481043379</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.287614128839969</v>
+        <v>62.239593188440793</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.727213244673251</v>
+        <v>70.672685754106723</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.83793155101327</v>
+        <v>73.781005836972042</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.260076189107167</v>
+        <v>45.225182712265315</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.308505035185718</v>
+        <v>56.265093718151356</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.751751879598274</v>
+        <v>64.701831200162374</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.850616813962574</v>
+        <v>74.792910365270714</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.632521742108082</v>
+        <v>78.571899615336562</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.23745978715236</v>
+        <v>45.202583746536078</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.533903700700577</v>
+        <v>57.489547656578736</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.233121362879317</v>
+        <v>67.181287659518347</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>79.118195333227035</v>
+        <v>79.057198774027825</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.639459750524125</v>
+        <v>83.574977500435196</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.216372232882136</v>
+        <v>45.18151244981884</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.733594701903954</v>
+        <v>58.688313750144026</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.731843080309204</v>
+        <v>69.678082975233465</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.534989884633603</v>
+        <v>83.470588176098133</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.868150258147409</v>
+        <v>88.799636923568499</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.130484796406833</v>
+        <v>45.095691228682256</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.364919944798146</v>
+        <v>64.315297495332146</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.490012054564332</v>
+        <v>82.426415976791873</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>108.04633053451435</v>
+        <v>107.96303168816242</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.69726708224235</v>
+        <v>118.60575684432715</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>45.069958634387937</v>
+        <v>45.035211729603652</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.429816761668221</v>
+        <v>69.376289505258299</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.700553653879652</v>
+        <v>95.626772844525249</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>137.15319712476509</v>
+        <v>137.04745819742297</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.74349583655317</v>
+        <v>155.62342462760213</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>45.027304942077663</v>
+        <v>44.992590921365839</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.985259514315231</v>
+        <v>73.928220217060968</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.37950787524194</v>
+        <v>109.29518120930635</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.71718506831215</v>
+        <v>171.58479886561346</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.75300637654109</v>
+        <v>201.59746391067426</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.997246246680263</v>
+        <v>44.962555399866496</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>78.082491782408781</v>
+        <v>78.022293703921676</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.54348345364085</v>
+        <v>123.44823700153944</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.76142660002748</v>
+        <v>212.59739713881117</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.89445184372454</v>
+        <v>258.6948559013282</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.868150258147409</v>
+        <v>88.799636923568499</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.534989884633603</v>
+        <v>83.470588176098133</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.731843080309204</v>
+        <v>69.678082975233465</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.733594701903954</v>
+        <v>58.688313750144026</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.216372232882136</v>
+        <v>45.18151244981884</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.534989884633603</v>
+        <v>83.470588176098133</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.731843080309204</v>
+        <v>69.678082975233465</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.733594701903954</v>
+        <v>58.688313750144026</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.742910346572771</v>
+        <v>69.689141709134034</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.868150258147409</v>
+        <v>88.799636923568499</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.216372232882136</v>
+        <v>45.18151244981884</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>39.78</v>
+        <v>39.68</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21817681151921156</v>
+        <v>0.21889015087297162</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2838812048675306E-2</v>
+        <v>5.2840507810189008E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.385369427624425</v>
+        <v>71.330334528333438</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>51.013321239240767</v>
+        <v>50.973992270021846</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.492202743570509</v>
+        <v>32.467152721134923</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.750090772701142</v>
+        <v>32.725040750265556</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54122124694044604</v>
+        <v>0.54121845962650439</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.310977678023391</v>
+        <v>41.27912877797074</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.610098048393759</v>
+        <v>41.578249148341108</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41710607674894729</v>
+        <v>0.41710284378624873</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.166205446450959</v>
+        <v>51.126758610405616</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.508795090334246</v>
+        <v>51.469348254288903</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27844044930582679</v>
+        <v>0.27843674651708616</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.865180053663721</v>
+        <v>57.820568610419222</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.236137335922287</v>
+        <v>58.191525892677788</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18420065900245519</v>
+        <v>0.18419664960966542</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>39.78</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>123668.21229984</v>
+        <v>123357.33192704</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21817681151921156</v>
+        <v>0.21889015087297162</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.385369427624425</v>
+        <v>71.330334528333438</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.750090772701142</v>
+        <v>32.725040750265556</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.610098048393759</v>
+        <v>41.578249148341108</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.508795090334246</v>
+        <v>51.469348254288903</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.236137335922287</v>
+        <v>58.191525892677788</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.9403498095395614E-2</v>
+        <v>5.9507291657873981E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5696329813976867E-3</v>
+        <v>3.5786290322580641E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11655128843823877</v>
+        <v>-0.11646143265304268</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5859506927060121</v>
+        <v>9.5785603571903248</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1720546225490116</v>
+        <v>6.167296246886127</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.641454026816787</v>
+        <v>15.629395171423411</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.533008174197606</v>
+        <v>11.524116745204827</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.552550737665051</v>
+        <v>61.505096497978236</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.87 HKD</v>
+        <v>88.8 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.53 HKD</v>
+        <v>83.47 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.73 HKD</v>
+        <v>69.68 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.73 HKD</v>
+        <v>58.69 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.22 HKD</v>
+        <v>45.18 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.385369427624425</v>
+        <v>71.330334528333438</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.492202743570509</v>
+        <v>32.467152721134923</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.750090772701142</v>
+        <v>32.725040750265556</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.310977678023391</v>
+        <v>41.27912877797074</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.610098048393759</v>
+        <v>41.578249148341108</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.166205446450959</v>
+        <v>51.126758610405616</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.508795090334246</v>
+        <v>51.469348254288903</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.865180053663721</v>
+        <v>57.820568610419222</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.236137335922287</v>
+        <v>58.191525892677788</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2E2E93-22C8-4784-82DF-15A60FD47073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C0338B-D913-4F35-9BE0-4A6094F57BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>39.68</v>
+        <v>39.76</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>123357.33192704</v>
+        <v>123606.03622528</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21889015087297162</v>
+        <v>0.21825042499925634</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.330334528333438</v>
+        <v>71.362209945117357</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.725040750265556</v>
+        <v>32.739549360544991</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.578249148341108</v>
+        <v>41.596695570091057</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.469348254288903</v>
+        <v>51.492195290550455</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.191525892677788</v>
+        <v>58.217364194647452</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9507291657873981E-2</v>
+        <v>5.9414097220154873E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5786290322580641E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11646143265304268</v>
+        <v>-0.11651347582274901</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5785603571903248</v>
+        <v>9.5828407325116292</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.167296246886127</v>
+        <v>6.1700522291705129</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.629395171423411</v>
+        <v>15.636379485859393</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.524116745204827</v>
+        <v>11.529266532132771</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.8 HKD</v>
+        <v>88.84 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.869488774736611E-2</v>
+        <v>-6.8695657356826673E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.47 HKD</v>
+        <v>83.51 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9247912701286208E-2</v>
+        <v>-4.9248714075829279E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.68 HKD</v>
+        <v>69.71 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8646957015954551E-3</v>
+        <v>9.8637924579023841E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.69 HKD</v>
+        <v>58.71 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9458497833812402E-2</v>
+        <v>6.9457483513191184E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.18 HKD</v>
+        <v>45.2 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712682385592822</v>
+        <v>0.16712560833375617</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.330334528333438</v>
+        <v>71.362209945117357</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.467152721134923</v>
+        <v>32.481661331414358</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.725040750265556</v>
+        <v>32.739549360544991</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.27912877797074</v>
+        <v>41.29757519972069</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.578249148341108</v>
+        <v>41.596695570091057</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.126758610405616</v>
+        <v>51.149605646667169</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.469348254288903</v>
+        <v>51.492195290550455</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.820568610419222</v>
+        <v>57.846406912388886</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.191525892677788</v>
+        <v>58.217364194647452</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.589680517135559</v>
+        <v>29.602903270193195</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.524116745204827</v>
+        <v>11.529266532132771</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-362.05573599999997</v>
+        <v>-362.21752800000002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11646143265304265</v>
+        <v>-0.11651347582274901</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29777.864147306296</v>
+        <v>29791.170994062402</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5785603571903266</v>
+        <v>9.5828407325116292</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19172.913563999999</v>
+        <v>19181.481371999998</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.167296246886127</v>
+        <v>6.1700522291705129</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48588.721975306296</v>
+        <v>48610.4348380624</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.629395171423411</v>
+        <v>15.636379485859393</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5786290322580641E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5786290322580641E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9405241935483871E-3</v>
+        <v>1.9366197183098592E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3612493329844395</v>
+        <v>2.3623045054733578</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.823902231866799</v>
+        <v>2.8251641502524762</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0514340870629209</v>
+        <v>2.0523508122817531</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4169175878769933</v>
+        <v>1.4175507664392515</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97203124320218692</v>
+        <v>0.97246561521528552</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79645660527813877</v>
+        <v>0.79681251817846965</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1676490042779768</v>
+        <v>1.16817079208277</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2866093172141719</v>
+        <v>1.2871842648643612</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9507291657873981E-2</v>
+        <v>5.9414097220154873E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1166890924062476E-2</v>
+        <v>7.1055436374559272E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1699447758642159E-2</v>
+        <v>5.1618481194209087E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.570860856544842E-2</v>
+        <v>3.5652685272616988E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.4496755121022857E-2</v>
+        <v>2.4458390724730522E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0071991060436965E-2</v>
+        <v>2.0040556292215031E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.9426638212650624E-2</v>
+        <v>2.9380553120794014E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.2424629970115221E-2</v>
+        <v>3.2373849719928606E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2033443190184763E-2</v>
+        <v>9.1848265236079751E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7629326842158324E-2</v>
+        <v>5.7513372462194221E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.23160903243869E-2</v>
+        <v>4.2230947285504833E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1120971409065383E-2</v>
+        <v>3.1058353760354988E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6062496243851319E-2</v>
+        <v>2.6010056613581998E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3852872259509517E-2</v>
+        <v>3.3784757828403865E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2239672647526189E-2</v>
+        <v>3.2174804090891324E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.629395171423411</v>
+        <v>15.636379485859393</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191207.27328391449</v>
+        <v>191292.71815906253</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.973992270021846</v>
+        <v>50.996771039524212</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.436542474930562</v>
+        <v>45.456846721899055</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.926899840105904</v>
+        <v>46.947870083701027</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.821114259211129</v>
+        <v>47.842484100782222</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.715328678316332</v>
+        <v>48.737098117863411</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>49.013400151351412</v>
+        <v>49.03530279022381</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.39965578631719</v>
+        <v>45.419943549715533</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.347259943806989</v>
+        <v>48.368864904322876</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.182523746952072</v>
+        <v>50.204948832580506</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.067813531585557</v>
+        <v>52.09108109745808</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.707360344571931</v>
+        <v>52.73091370499948</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.365262603460899</v>
+        <v>45.385534997563063</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.737822283094751</v>
+        <v>49.760048644791802</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.560446587754129</v>
+        <v>52.58393429676898</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.537518134969069</v>
+        <v>55.562336209206386</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.564922504391937</v>
+        <v>56.590199695254704</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.333194367697466</v>
+        <v>45.35345243145354</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.099211985893952</v>
+        <v>51.122046712383749</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.954998259610761</v>
+        <v>54.979556022944806</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.12854108112824</v>
+        <v>59.154963877309541</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.593332405555941</v>
+        <v>60.620409773656419</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.303293914771196</v>
+        <v>45.323538616899214</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.432041065557506</v>
+        <v>52.455471393942304</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.3662950480538</v>
+        <v>57.391930348604369</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.845124270160092</v>
+        <v>62.87320789744426</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.800156731247057</v>
+        <v>64.82911400471464</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.275414704583511</v>
+        <v>45.295646948317071</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.736908695997357</v>
+        <v>53.760922131132503</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.794454051800635</v>
+        <v>59.821174424793014</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.691657920346927</v>
+        <v>66.721460449751547</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.193297285814907</v>
+        <v>69.224217723861685</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.249420103009918</v>
+        <v>45.26964073052487</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>55.014401481043379</v>
+        <v>55.038985789920126</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.239593188440793</v>
+        <v>62.267406221794161</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.672685754106723</v>
+        <v>70.704267287104528</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.781005836972042</v>
+        <v>73.813976386280984</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.225182712265315</v>
+        <v>45.2453925088072</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.265093718151356</v>
+        <v>56.290236924397497</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.701831200162374</v>
+        <v>64.730744534858275</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.792910365270714</v>
+        <v>74.826333104784553</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.571899615336562</v>
+        <v>78.607011073376185</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.202583746536078</v>
+        <v>45.222783444268586</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.489547656578736</v>
+        <v>57.515238035074645</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.181287659518347</v>
+        <v>67.211308989971769</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>79.057198774027825</v>
+        <v>79.092527097907904</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.574977500435196</v>
+        <v>83.612324686007071</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.18151244981884</v>
+        <v>45.201702731412063</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.688313750144026</v>
+        <v>58.714539821751586</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.678082975233465</v>
+        <v>69.70922004966647</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.470588176098133</v>
+        <v>83.507888713168455</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.799636923568499</v>
+        <v>88.839318854908313</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.095691228682256</v>
+        <v>45.115843159310067</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.315297495332146</v>
+        <v>64.344038099547745</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.426415976791873</v>
+        <v>82.463249904189496</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.96303168816242</v>
+        <v>108.01127717383231</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.60575684432715</v>
+        <v>118.65875824909251</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>45.035211729603652</v>
+        <v>45.055336633732111</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.376289505258299</v>
+        <v>69.407291717115626</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.626772844525249</v>
+        <v>95.669505620983898</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>137.04745819742297</v>
+        <v>137.10870065307813</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.62342462760213</v>
+        <v>155.69296813323894</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.992590921365839</v>
+        <v>45.012696779515672</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.928220217060968</v>
+        <v>73.961256552122265</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.29518120930635</v>
+        <v>109.34402199319665</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.58479886561346</v>
+        <v>171.66147503731224</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.59746391067426</v>
+        <v>201.68755185470573</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.962555399866496</v>
+        <v>44.982647836030125</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>78.022293703921676</v>
+        <v>78.05715955933502</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.44823700153944</v>
+        <v>123.50340236746243</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.59739713881117</v>
+        <v>212.69240062766045</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.6948559013282</v>
+        <v>258.81045898108715</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.799636923568499</v>
+        <v>88.839318854908313</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.470588176098133</v>
+        <v>83.507888713168455</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.678082975233465</v>
+        <v>69.70922004966647</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.688313750144026</v>
+        <v>58.714539821751586</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.18151244981884</v>
+        <v>45.201702731412063</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.470588176098133</v>
+        <v>83.507888713168455</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.678082975233465</v>
+        <v>69.70922004966647</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.688313750144026</v>
+        <v>58.714539821751586</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.689141709134034</v>
+        <v>69.720283725388143</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.799636923568499</v>
+        <v>88.839318854908313</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.18151244981884</v>
+        <v>45.201702731412063</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>39.68</v>
+        <v>39.76</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21889015087297162</v>
+        <v>0.21825042499925634</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2840507810189008E-2</v>
+        <v>5.2839525330907737E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.330334528333438</v>
+        <v>71.362209945117357</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.973992270021846</v>
+        <v>50.996771039524212</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.467152721134923</v>
+        <v>32.481661331414358</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.725040750265556</v>
+        <v>32.739549360544991</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54121845962650439</v>
+        <v>0.54122007452229903</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.27912877797074</v>
+        <v>41.29757519972069</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.578249148341108</v>
+        <v>41.596695570091057</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41710284378624873</v>
+        <v>0.41710471687911721</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.126758610405616</v>
+        <v>51.149605646667169</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.469348254288903</v>
+        <v>51.492195290550455</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27843674651708616</v>
+        <v>0.27843889181470649</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.820568610419222</v>
+        <v>57.846406912388886</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.191525892677788</v>
+        <v>58.217364194647452</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18419664960966542</v>
+        <v>0.18419897254554241</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>39.68</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>123357.33192704</v>
+        <v>123606.03622528</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21889015087297162</v>
+        <v>0.21825042499925634</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.330334528333438</v>
+        <v>71.362209945117357</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.725040750265556</v>
+        <v>32.739549360544991</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.578249148341108</v>
+        <v>41.596695570091057</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.469348254288903</v>
+        <v>51.492195290550455</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.191525892677788</v>
+        <v>58.217364194647452</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.9507291657873981E-2</v>
+        <v>5.9414097220154873E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5786290322580641E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11646143265304268</v>
+        <v>-0.11651347582274901</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5785603571903248</v>
+        <v>9.5828407325116292</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.167296246886127</v>
+        <v>6.1700522291705129</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.629395171423411</v>
+        <v>15.636379485859393</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.524116745204827</v>
+        <v>11.529266532132771</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.505096497978236</v>
+        <v>61.53258130648463</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.8 HKD</v>
+        <v>88.84 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.47 HKD</v>
+        <v>83.51 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.68 HKD</v>
+        <v>69.71 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.69 HKD</v>
+        <v>58.71 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.18 HKD</v>
+        <v>45.2 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.330334528333438</v>
+        <v>71.362209945117357</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.467152721134923</v>
+        <v>32.481661331414358</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.725040750265556</v>
+        <v>32.739549360544991</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.27912877797074</v>
+        <v>41.29757519972069</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.578249148341108</v>
+        <v>41.596695570091057</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.126758610405616</v>
+        <v>51.149605646667169</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.469348254288903</v>
+        <v>51.492195290550455</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.820568610419222</v>
+        <v>57.846406912388886</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.191525892677788</v>
+        <v>58.217364194647452</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,15 +21852,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21875,12 +21872,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C0338B-D913-4F35-9BE0-4A6094F57BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ACFBD5-BEE5-4B9D-8983-5D74EE2453C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>39.76</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>123606.03622528</v>
+        <v>119067.18278239999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21825042499925634</v>
+        <v>0.23328498495961489</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.362209945117357</v>
+        <v>71.310661419537112</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.739549360544991</v>
+        <v>32.716086217358715</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.596695570091057</v>
+        <v>41.566864247417307</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.492195290550455</v>
+        <v>51.455247349096226</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.217364194647452</v>
+        <v>58.175578815680886</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9414097220154873E-2</v>
+        <v>6.1634414979476117E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5714285714285713E-3</v>
+        <v>3.7075718015665794E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11651347582274901</v>
+        <v>-0.11642931225923954</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5828407325116292</v>
+        <v>9.5759185630467076</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1700522291705129</v>
+        <v>6.1655952890699828</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.636379485859393</v>
+        <v>15.625084539857452</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.529266532132771</v>
+        <v>11.520938361085236</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.84 HKD</v>
+        <v>88.78 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8695657356826673E-2</v>
+        <v>-6.8694412410698361E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.51 HKD</v>
+        <v>83.45 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9248714075829279E-2</v>
+        <v>-4.924741774542718E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.71 HKD</v>
+        <v>69.66 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8637924579023841E-3</v>
+        <v>9.8652535752968076E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.71 HKD</v>
+        <v>58.67 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9457483513191184E-2</v>
+        <v>6.9459124312399451E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.2 HKD</v>
+        <v>45.17 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712560833375617</v>
+        <v>0.16712757460344926</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.362209945117357</v>
+        <v>71.310661419537112</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.481661331414358</v>
+        <v>32.458198188228081</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.739549360544991</v>
+        <v>32.716086217358715</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.29757519972069</v>
+        <v>41.267743877046939</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.596695570091057</v>
+        <v>41.566864247417307</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.149605646667169</v>
+        <v>51.112657705212939</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.492195290550455</v>
+        <v>51.455247349096226</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.846406912388886</v>
+        <v>57.804621533422321</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.217364194647452</v>
+        <v>58.175578815680886</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.602903270193195</v>
+        <v>29.581519599232799</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.529266532132771</v>
+        <v>11.520938361085236</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-362.21752800000002</v>
+        <v>-361.95587999999998</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11651347582274901</v>
+        <v>-0.11642931225923954</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29791.170994062402</v>
+        <v>29769.651327824013</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5828407325116292</v>
+        <v>9.5759185630467094</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19181.481371999998</v>
+        <v>19167.625619999999</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1700522291705129</v>
+        <v>6.1655952890699828</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48610.4348380624</v>
+        <v>48575.321067824014</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.636379485859393</v>
+        <v>15.625084539857454</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5714285714285713E-3</v>
+        <v>3.7075718015665794E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5714285714285713E-3</v>
+        <v>3.7075718015665794E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9366197183098592E-3</v>
+        <v>2.0104438642297652E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3623045054733578</v>
+        <v>2.3605980937139353</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8251641502524762</v>
+        <v>2.8231233916131391</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0523508122817531</v>
+        <v>2.0508682957169229</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4175507664392515</v>
+        <v>1.4165267979830996</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97246561521528552</v>
+        <v>0.97176315422535275</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79681251817846965</v>
+        <v>0.79623694028496583</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.16817079208277</v>
+        <v>1.1673269633672063</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2871842648643612</v>
+        <v>1.2862544667113209</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9414097220154873E-2</v>
+        <v>6.1634414979476117E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1055436374559272E-2</v>
+        <v>7.3710793514703374E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1618481194209087E-2</v>
+        <v>5.3547475083992768E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5652685272616988E-2</v>
+        <v>3.6985033889898163E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.4458390724730522E-2</v>
+        <v>2.537240611554446E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0040556292215031E-2</v>
+        <v>2.0789476247649239E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.9380553120794014E-2</v>
+        <v>3.0478510792877452E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.2373849719928606E-2</v>
+        <v>3.3583667538154595E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1848265236079751E-2</v>
+        <v>9.5349530699387244E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7513372462194221E-2</v>
+        <v>5.97057882270716E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2230947285504833E-2</v>
+        <v>4.384079540657107E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1058353760354988E-2</v>
+        <v>3.2242301449392018E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6010056613581998E-2</v>
+        <v>2.7001562688146744E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3784757828403865E-2</v>
+        <v>3.507263632525686E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2174804090891324E-2</v>
+        <v>3.3401310983128957E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.636379485859393</v>
+        <v>15.625084539857452</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191292.71815906253</v>
+        <v>191154.53777503406</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.996771039524212</v>
+        <v>50.959933498219605</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.456846721899055</v>
+        <v>45.424010947504691</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.947870083701027</v>
+        <v>46.913957267887042</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.842484100782222</v>
+        <v>47.807925060116467</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.737098117863411</v>
+        <v>48.701892852345878</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>49.03530279022381</v>
+        <v>48.999882116422356</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.419943549715533</v>
+        <v>45.38713443234478</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.368864904322876</v>
+        <v>48.333925632238596</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.204948832580506</v>
+        <v>50.168683264415769</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.09108109745808</v>
+        <v>52.053453080773615</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.73091370499948</v>
+        <v>52.692823504933052</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.385534997563063</v>
+        <v>45.352750735225975</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.760048644791802</v>
+        <v>49.724104450484859</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.58393429676898</v>
+        <v>52.545950267346527</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.562336209206386</v>
+        <v>55.522200729775726</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.590199695254704</v>
+        <v>56.549321738156323</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.35345243145354</v>
+        <v>45.320691343973017</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.122046712383749</v>
+        <v>51.085118678138535</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.979556022944806</v>
+        <v>54.93984151505304</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.154963877309541</v>
+        <v>59.1122332616101</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.620409773656419</v>
+        <v>60.576620592431432</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.323538616899214</v>
+        <v>45.290799137676565</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.455471393942304</v>
+        <v>52.41758015975752</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.391930348604369</v>
+        <v>57.350473260995251</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.87320789744426</v>
+        <v>62.827791406445648</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.82911400471464</v>
+        <v>64.782284664028779</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.295646948317071</v>
+        <v>45.26292761665421</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.760922131132503</v>
+        <v>53.722087903999885</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.821174424793014</v>
+        <v>59.777962571594408</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.721460449751547</v>
+        <v>66.673264171730025</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.224217723861685</v>
+        <v>69.174213577957914</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.26964073052487</v>
+        <v>45.236940184465539</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>55.038985789920126</v>
+        <v>54.999228352908517</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.267406221794161</v>
+        <v>62.22242733191802</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.704267287104528</v>
+        <v>70.653194026709642</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.813976386280984</v>
+        <v>73.760656826070417</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.2453925088072</v>
+        <v>45.212709478462116</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.290236924397497</v>
+        <v>56.249575645546315</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.730744534858275</v>
+        <v>64.683986251404761</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.826333104784553</v>
+        <v>74.772282268227016</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.607011073376185</v>
+        <v>78.550229262327747</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.222783444268586</v>
+        <v>45.190116745591794</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.515238035074645</v>
+        <v>57.473691876100794</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.211308989971769</v>
+        <v>67.16275886962913</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>79.092527097907904</v>
+        <v>79.035394574133093</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.612324686007071</v>
+        <v>83.551927284340067</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.201702731412063</v>
+        <v>45.169051260398021</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.714539821751586</v>
+        <v>58.672127346573738</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.70922004966647</v>
+        <v>69.65886556210684</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.507888713168455</v>
+        <v>83.447566750875055</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.839318854908313</v>
+        <v>88.775145731569708</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.115843159310067</v>
+        <v>45.083253708997908</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.344038099547745</v>
+        <v>64.297559153667834</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.463249904189496</v>
+        <v>82.403682537226146</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>108.01127717383231</v>
+        <v>107.93325517747553</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.65875824909251</v>
+        <v>118.57304503982353</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>45.055336633732111</v>
+        <v>45.022790890336879</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.407291717115626</v>
+        <v>69.357155327627595</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.669505620983898</v>
+        <v>95.600398709054673</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>137.10870065307813</v>
+        <v>137.00966011932329</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.69296813323894</v>
+        <v>155.58050324521693</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>45.012696779515672</v>
+        <v>44.980181837038984</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.961256552122265</v>
+        <v>73.907830604015331</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.34402199319665</v>
+        <v>109.26503728799906</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.66147503731224</v>
+        <v>171.53747529089313</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.68755185470573</v>
+        <v>201.54186275771735</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.982647836030125</v>
+        <v>44.950154599421758</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>78.05715955933502</v>
+        <v>78.000774933783759</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.50340236746243</v>
+        <v>123.41418962725885</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.69240062766045</v>
+        <v>212.53876217303704</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.81045898108715</v>
+        <v>258.6235071255395</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.839318854908313</v>
+        <v>88.775145731569708</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.507888713168455</v>
+        <v>83.447566750875055</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.70922004966647</v>
+        <v>69.65886556210684</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.714539821751586</v>
+        <v>58.672127346573738</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.201702731412063</v>
+        <v>45.169051260398021</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.507888713168455</v>
+        <v>83.447566750875055</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.70922004966647</v>
+        <v>69.65886556210684</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.714539821751586</v>
+        <v>58.672127346573738</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.720283725388143</v>
+        <v>69.669921245977207</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.839318854908313</v>
+        <v>88.775145731569708</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.201702731412063</v>
+        <v>45.169051260398021</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>39.76</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21825042499925634</v>
+        <v>0.23328498495961489</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2839525330907737E-2</v>
+        <v>5.2841114622481762E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.362209945117357</v>
+        <v>71.310661419537112</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.996771039524212</v>
+        <v>50.959933498219605</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.481661331414358</v>
+        <v>32.458198188228081</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.739549360544991</v>
+        <v>32.716086217358715</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54122007452229903</v>
+        <v>0.54121746221252365</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.29757519972069</v>
+        <v>41.267743877046939</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.596695570091057</v>
+        <v>41.566864247417307</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41710471687911721</v>
+        <v>0.41710168690106753</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.149605646667169</v>
+        <v>51.112657705212939</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.492195290550455</v>
+        <v>51.455247349096226</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27843889181470649</v>
+        <v>0.27843542150909095</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.846406912388886</v>
+        <v>57.804621533422321</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.217364194647452</v>
+        <v>58.175578815680886</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18419897254554241</v>
+        <v>0.18419521488630564</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>39.76</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>123606.03622528</v>
+        <v>119067.18278239999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21825042499925634</v>
+        <v>0.23328498495961489</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.362209945117357</v>
+        <v>71.310661419537112</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.739549360544991</v>
+        <v>32.716086217358715</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.596695570091057</v>
+        <v>41.566864247417307</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.492195290550455</v>
+        <v>51.455247349096226</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.217364194647452</v>
+        <v>58.175578815680886</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>5.9414097220154873E-2</v>
+        <v>6.1634414979476117E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5714285714285713E-3</v>
+        <v>3.7075718015665794E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11651347582274901</v>
+        <v>-0.11642931225923954</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5828407325116292</v>
+        <v>9.5759185630467076</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1700522291705129</v>
+        <v>6.1655952890699828</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.636379485859393</v>
+        <v>15.625084539857452</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.529266532132771</v>
+        <v>11.520938361085236</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.53258130648463</v>
+        <v>61.488133217728198</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.84 HKD</v>
+        <v>88.78 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.51 HKD</v>
+        <v>83.45 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.71 HKD</v>
+        <v>69.66 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.71 HKD</v>
+        <v>58.67 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.2 HKD</v>
+        <v>45.17 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.362209945117357</v>
+        <v>71.310661419537112</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.481661331414358</v>
+        <v>32.458198188228081</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.739549360544991</v>
+        <v>32.716086217358715</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.29757519972069</v>
+        <v>41.267743877046939</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.596695570091057</v>
+        <v>41.566864247417307</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.149605646667169</v>
+        <v>51.112657705212939</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.492195290550455</v>
+        <v>51.455247349096226</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.846406912388886</v>
+        <v>57.804621533422321</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.217364194647452</v>
+        <v>58.175578815680886</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ACFBD5-BEE5-4B9D-8983-5D74EE2453C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652DCF9-5DF1-4669-816A-AB777C4917D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>38.299999999999997</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>119067.18278239999</v>
+        <v>114528.32933952</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23328498495961489</v>
+        <v>0.24904630147475521</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.310661419537112</v>
+        <v>71.247657666050159</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.716086217358715</v>
+        <v>32.687409042353273</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.566864247417307</v>
+        <v>41.530403741927174</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.455247349096226</v>
+        <v>51.410088753985512</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.175578815680886</v>
+        <v>58.124507796943981</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1634414979476117E-2</v>
+        <v>6.4020425606441583E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.7075718015665794E-3</v>
+        <v>3.8545059717698146E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11642931225923954</v>
+        <v>-0.11632644568161686</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5759185630467076</v>
+        <v>9.5674581337006952</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1655952890699828</v>
+        <v>6.1601479178360021</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.625084539857452</v>
+        <v>15.611279605855081</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.520938361085236</v>
+        <v>11.51075948536047</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.78 HKD</v>
+        <v>88.7 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8694412410698361E-2</v>
+        <v>-6.8692888363658999E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.45 HKD</v>
+        <v>83.37 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.924741774542718E-2</v>
+        <v>-4.9245830794359416E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.66 HKD</v>
+        <v>69.6 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8652535752968076E-3</v>
+        <v>9.8670422567087787E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.67 HKD</v>
+        <v>58.62 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9459124312399451E-2</v>
+        <v>6.9461132958275218E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.17 HKD</v>
+        <v>45.13 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712757460344926</v>
+        <v>0.16712998168677815</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.310661419537112</v>
+        <v>71.247657666050159</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.458198188228081</v>
+        <v>32.42952101322264</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.716086217358715</v>
+        <v>32.687409042353273</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.267743877046939</v>
+        <v>41.231283371556806</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.566864247417307</v>
+        <v>41.530403741927174</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.112657705212939</v>
+        <v>51.067499110102226</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.455247349096226</v>
+        <v>51.410088753985512</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.804621533422321</v>
+        <v>57.753550514685415</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.175578815680886</v>
+        <v>58.124507796943981</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.581519599232799</v>
+        <v>29.555384001392316</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.520938361085236</v>
+        <v>11.51075948536047</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-361.95587999999998</v>
+        <v>-361.63608799999997</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11642931225923954</v>
+        <v>-0.11632644568161686</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29769.651327824013</v>
+        <v>29743.349513532645</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5759185630467094</v>
+        <v>9.5674581337006952</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19167.625619999999</v>
+        <v>19150.690812000001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1655952890699828</v>
+        <v>6.1601479178360021</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48575.321067824014</v>
+        <v>48532.404237532646</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.625084539857454</v>
+        <v>15.611279605855081</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.7075718015665794E-3</v>
+        <v>3.8545059717698146E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.7075718015665794E-3</v>
+        <v>3.8545059717698146E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0104438642297652E-3</v>
+        <v>2.0901194353963081E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3605980937139353</v>
+        <v>2.3585124793413077</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8231233916131391</v>
+        <v>2.8206291310539493</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0508682957169229</v>
+        <v>2.0490563310265744</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4165267979830996</v>
+        <v>1.4152752809811362</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97176315422535275</v>
+        <v>0.97090459079321279</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79623694028496583</v>
+        <v>0.79553345619290583</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1673269633672063</v>
+        <v>1.1662956171592951</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2862544667113209</v>
+        <v>1.2851180467464938</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1634414979476117E-2</v>
+        <v>6.4020425606441583E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.3710793514703374E-2</v>
+        <v>7.6564308660530642E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3547475083992768E-2</v>
+        <v>5.5620421580525901E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.6985033889898163E-2</v>
+        <v>3.8416810015774593E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.537240611554446E-2</v>
+        <v>2.6354630586134981E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.0789476247649239E-2</v>
+        <v>2.1594284912945325E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.0478510792877452E-2</v>
+        <v>3.16584043745737E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.3583667538154595E-2</v>
+        <v>3.4883768912771271E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5349530699387244E-2</v>
+        <v>9.9128312317766851E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.97057882270716E-2</v>
+        <v>6.2071978531401797E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.384079540657107E-2</v>
+        <v>4.5578242781532899E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2242301449392018E-2</v>
+        <v>3.3520090811935785E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7001562688146744E-2</v>
+        <v>2.8071657192074381E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.507263632525686E-2</v>
+        <v>3.6462594225226318E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3401310983128957E-2</v>
+        <v>3.4725032862482054E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.625084539857452</v>
+        <v>15.611279605855081</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>191154.53777503406</v>
+        <v>190985.65063899924</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.959933498219605</v>
+        <v>50.9149098366251</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.424010947504691</v>
+        <v>45.383878334356027</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.913957267887042</v>
+        <v>46.872508270781061</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.807925060116467</v>
+        <v>47.765686232636099</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.701892852345878</v>
+        <v>48.658864194491123</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.999882116422356</v>
+        <v>48.956590181776136</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.38713443234478</v>
+        <v>45.347034400002748</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.333925632238596</v>
+        <v>48.291222077468923</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.168683264415769</v>
+        <v>50.12435868110331</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.053453080773615</v>
+        <v>52.007463282603723</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.692823504933052</v>
+        <v>52.646268815962983</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.352750735225975</v>
+        <v>45.312681081258425</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.724104450484859</v>
+        <v>49.680172657443038</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.545950267346527</v>
+        <v>52.49952534249686</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.522200729775726</v>
+        <v>55.473146254916038</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.549321738156323</v>
+        <v>56.49935979059164</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.320691343973017</v>
+        <v>45.280650014830165</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.085118678138535</v>
+        <v>51.039984414061045</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.93984151505304</v>
+        <v>54.8913015609631</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.1122332616101</v>
+        <v>59.060006953532998</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.576620592431432</v>
+        <v>60.523100482045344</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.290799137676565</v>
+        <v>45.250784218626663</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.41758015975752</v>
+        <v>52.371268651309443</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.350473260995251</v>
+        <v>57.299803487250784</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.827791406445648</v>
+        <v>62.77228236189179</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.782284664028779</v>
+        <v>64.725048803190489</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.26292761665421</v>
+        <v>45.222937322399602</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.722087903999885</v>
+        <v>53.674623848615582</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.777962571594408</v>
+        <v>59.725148084351666</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.673264171730025</v>
+        <v>66.614357609703717</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.174213577957914</v>
+        <v>69.113097399631101</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.236940184465539</v>
+        <v>45.196972850393024</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.999228352908517</v>
+        <v>54.950635929894325</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.22242733191802</v>
+        <v>62.167453133180516</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.653194026709642</v>
+        <v>70.590771152893666</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.760656826070417</v>
+        <v>73.695488474701961</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.212709478462116</v>
+        <v>45.172763552484795</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.249575645546315</v>
+        <v>56.199878526950421</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.683986251404761</v>
+        <v>64.626837238294897</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.772282268227016</v>
+        <v>74.706220134656704</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.550229262327747</v>
+        <v>78.480829271046318</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.190116745591794</v>
+        <v>45.150190780542395</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.473691876100794</v>
+        <v>57.422913237354983</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.16275886962913</v>
+        <v>67.103419833654812</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>79.035394574133093</v>
+        <v>78.965565933963873</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.551927284340067</v>
+        <v>83.478108237858166</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.169051260398021</v>
+        <v>45.12914390693642</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.672127346573738</v>
+        <v>58.620289876911919</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.65886556210684</v>
+        <v>69.597321188422853</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.447566750875055</v>
+        <v>83.373839908072014</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.775145731569708</v>
+        <v>88.696711914155856</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.083253708997908</v>
+        <v>45.043422158616387</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.297559153667834</v>
+        <v>64.240751553147931</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.403682537226146</v>
+        <v>82.330877977604288</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.93325517747553</v>
+        <v>107.83789495970613</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.57304503982353</v>
+        <v>118.46828445071698</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>45.022790890336879</v>
+        <v>44.983012759520484</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.357155327627595</v>
+        <v>69.295877518253334</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.600398709054673</v>
+        <v>95.515934705585607</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>137.00966011932329</v>
+        <v>136.88861057806739</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.58050324521693</v>
+        <v>155.44304615985669</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.980181837038984</v>
+        <v>44.940441351789701</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.907830604015331</v>
+        <v>73.842532222995743</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.26503728799906</v>
+        <v>109.1685004260909</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.53747529089313</v>
+        <v>171.38592004526973</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.54186275771735</v>
+        <v>201.36379830584266</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.950154599421758</v>
+        <v>44.910440643567085</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>78.000774933783759</v>
+        <v>77.931860391443337</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.41418962725885</v>
+        <v>123.30515183367672</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.53876217303704</v>
+        <v>212.35098183960844</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.6235071255395</v>
+        <v>258.39501041320347</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.775145731569708</v>
+        <v>88.696711914155856</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.447566750875055</v>
+        <v>83.373839908072014</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.65886556210684</v>
+        <v>69.597321188422853</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.672127346573738</v>
+        <v>58.620289876911919</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.169051260398021</v>
+        <v>45.12914390693642</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.447566750875055</v>
+        <v>83.373839908072014</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.65886556210684</v>
+        <v>69.597321188422853</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.672127346573738</v>
+        <v>58.620289876911919</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.669921245977207</v>
+        <v>69.608367104474951</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.775145731569708</v>
+        <v>88.696711914155856</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.169051260398021</v>
+        <v>45.12914390693642</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>38.299999999999997</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23328498495961489</v>
+        <v>0.24904630147475521</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2841114622481762E-2</v>
+        <v>5.2843060213283687E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.310661419537112</v>
+        <v>71.247657666050159</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.959933498219605</v>
+        <v>50.9149098366251</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452497</v>
+        <v>0.21911288198452492</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.458198188228081</v>
+        <v>32.42952101322264</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.716086217358715</v>
+        <v>32.687409042353273</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54121746221252365</v>
+        <v>0.5412142642560307</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.267743877046939</v>
+        <v>41.231283371556806</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.566864247417307</v>
+        <v>41.530403741927174</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41710168690106753</v>
+        <v>0.41709797764037082</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.112657705212939</v>
+        <v>51.067499110102226</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.455247349096226</v>
+        <v>51.410088753985512</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27843542150909095</v>
+        <v>0.27843117320497313</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.804621533422321</v>
+        <v>57.753550514685415</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.175578815680886</v>
+        <v>58.124507796943981</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18419521488630564</v>
+        <v>0.18419061480752963</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>38.299999999999997</v>
+        <v>36.840000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>119067.18278239999</v>
+        <v>114528.32933952</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23328498495961489</v>
+        <v>0.24904630147475521</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.310661419537112</v>
+        <v>71.247657666050159</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.716086217358715</v>
+        <v>32.687409042353273</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.566864247417307</v>
+        <v>41.530403741927174</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.455247349096226</v>
+        <v>51.410088753985512</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.175578815680886</v>
+        <v>58.124507796943981</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.1634414979476117E-2</v>
+        <v>6.4020425606441583E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.7075718015665794E-3</v>
+        <v>3.8545059717698146E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11642931225923954</v>
+        <v>-0.11632644568161686</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5759185630467076</v>
+        <v>9.5674581337006952</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1655952890699828</v>
+        <v>6.1601479178360021</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.625084539857452</v>
+        <v>15.611279605855081</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.520938361085236</v>
+        <v>11.51075948536047</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.488133217728198</v>
+        <v>61.433807775914772</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.78 HKD</v>
+        <v>88.7 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.45 HKD</v>
+        <v>83.37 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.66 HKD</v>
+        <v>69.6 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.67 HKD</v>
+        <v>58.62 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.17 HKD</v>
+        <v>45.13 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.310661419537112</v>
+        <v>71.247657666050159</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.458198188228081</v>
+        <v>32.42952101322264</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.716086217358715</v>
+        <v>32.687409042353273</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.267743877046939</v>
+        <v>41.231283371556806</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.566864247417307</v>
+        <v>41.530403741927174</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.112657705212939</v>
+        <v>51.067499110102226</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.455247349096226</v>
+        <v>51.410088753985512</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.804621533422321</v>
+        <v>57.753550514685415</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.175578815680886</v>
+        <v>58.124507796943981</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652DCF9-5DF1-4669-816A-AB777C4917D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EFD5BA-C598-41F5-A2A0-8D4BAD4F537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24904630147475521</v>
+        <v>0.2486391565252648</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.247657666050159</v>
+        <v>71.17768116514172</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.687409042353273</v>
+        <v>32.655558108849206</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.530403741927174</v>
+        <v>41.489908081679232</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.410088753985512</v>
+        <v>51.359932369692579</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.124507796943981</v>
+        <v>58.067784649651202</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4020425606441583E-2</v>
+        <v>6.3957547393776598E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11632644568161686</v>
+        <v>-0.11621219466062091</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5674581337006952</v>
+        <v>9.5580613722531496</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1601479178360021</v>
+        <v>6.1540976754773116</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.611279605855081</v>
+        <v>15.595946853069842</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.51075948536047</v>
+        <v>11.499454093745218</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.7 HKD</v>
+        <v>88.61 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8692888363658999E-2</v>
+        <v>-6.8691192485189095E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.37 HKD</v>
+        <v>83.29 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9245830794359416E-2</v>
+        <v>-4.9244064919553375E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.6 HKD</v>
+        <v>69.53 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8670422567087787E-3</v>
+        <v>9.8690326066035779E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.62 HKD</v>
+        <v>58.56 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9461132958275218E-2</v>
+        <v>6.9463368073310022E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.13 HKD</v>
+        <v>45.08 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16712998168677815</v>
+        <v>0.16713266016268385</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.247657666050159</v>
+        <v>71.17768116514172</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.42952101322264</v>
+        <v>32.397670079718573</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.687409042353273</v>
+        <v>32.655558108849206</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.231283371556806</v>
+        <v>41.190787711308865</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.530403741927174</v>
+        <v>41.489908081679232</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.067499110102226</v>
+        <v>51.017342725809293</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.410088753985512</v>
+        <v>51.359932369692579</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.753550514685415</v>
+        <v>57.696827367392636</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.124507796943981</v>
+        <v>58.067784649651202</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.555384001392316</v>
+        <v>29.526355926320477</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.51075948536047</v>
+        <v>11.499454093745218</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-361.63608799999997</v>
+        <v>-361.28090400000002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11632644568161686</v>
+        <v>-0.11621219466062091</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29743.349513532645</v>
+        <v>29714.136826513386</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5674581337006952</v>
+        <v>9.5580613722531496</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19150.690812000001</v>
+        <v>19131.881796000001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1601479178360021</v>
+        <v>6.1540976754773116</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48532.404237532646</v>
+        <v>48484.737718513388</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.611279605855081</v>
+        <v>15.59594685306984</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3585124793413077</v>
+        <v>2.3561960459867297</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8206291310539493</v>
+        <v>2.8178588258478934</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.0490563310265744</v>
+        <v>2.047043832694607</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4152752809811362</v>
+        <v>1.413885256168679</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.97090459079321279</v>
+        <v>0.96995100848320759</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79553345619290583</v>
+        <v>0.7947521161538984</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1662956171592951</v>
+        <v>1.1651501298690856</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2851180467464938</v>
+        <v>1.2838558569831879</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4020425606441583E-2</v>
+        <v>6.3957547393776598E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6564308660530642E-2</v>
+        <v>7.6489110365035098E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5620421580525901E-2</v>
+        <v>5.5565793504196707E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8416810015774593E-2</v>
+        <v>3.8379078614784984E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.6354630586134981E-2</v>
+        <v>2.632874615861041E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.1594284912945325E-2</v>
+        <v>2.1573075899942951E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.16584043745737E-2</v>
+        <v>3.1627310799920885E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.4883768912771271E-2</v>
+        <v>3.484950751854473E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.611279605855081</v>
+        <v>15.595946853069842</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>190985.65063899924</v>
+        <v>190798.07243652584</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.9149098366251</v>
+        <v>50.864903319201957</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.383878334356027</v>
+        <v>45.339304167183009</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.872508270781061</v>
+        <v>46.826472032888653</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.765686232636099</v>
+        <v>47.718772752312056</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.658864194491123</v>
+        <v>48.611073471735445</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.956590181776136</v>
+        <v>48.908507044876586</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.347034400002748</v>
+        <v>45.302496419417338</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.291222077468923</v>
+        <v>48.243792437586407</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.12435868110331</v>
+        <v>50.075128610309633</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>52.007463282603723</v>
+        <v>51.956383704399215</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.646268815962983</v>
+        <v>52.594561829399382</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.312681081258425</v>
+        <v>45.268176841081036</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.680172657443038</v>
+        <v>49.631378847779992</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.49952534249686</v>
+        <v>52.447962481300195</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.473146254916038</v>
+        <v>55.41866282631694</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.49935979059164</v>
+        <v>56.443868457525738</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.280650014830165</v>
+        <v>45.236177234240671</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>51.039984414061045</v>
+        <v>50.989855053563922</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.8913015609631</v>
+        <v>54.837389596143851</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.060006953532998</v>
+        <v>59.002000658791246</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.523100482045344</v>
+        <v>60.463657197387278</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.250784218626663</v>
+        <v>45.206340770986259</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.371268651309443</v>
+        <v>52.319831758527201</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.299803487250784</v>
+        <v>57.243525991510886</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.77228236189179</v>
+        <v>62.710630023869527</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.725048803190489</v>
+        <v>64.661478538781168</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.222937322399602</v>
+        <v>45.178521224828287</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.674623848615582</v>
+        <v>53.62190685429546</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.725148084351666</v>
+        <v>59.666488515516846</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.614357609703717</v>
+        <v>66.548931744370151</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.113097399631101</v>
+        <v>69.045217375481542</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.196972850393024</v>
+        <v>45.152582254051623</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.950635929894325</v>
+        <v>54.896665689313352</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.167453133180516</v>
+        <v>62.106394833396962</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.590771152893666</v>
+        <v>70.521439818734436</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.695488474701961</v>
+        <v>73.623107815672157</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.172763552484795</v>
+        <v>45.128396733513945</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.199878526950421</v>
+        <v>56.144681331988188</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.626837238294897</v>
+        <v>64.563363433220331</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.706220134656704</v>
+        <v>74.632846776817743</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.480829271046318</v>
+        <v>78.403748648318739</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.150190780542395</v>
+        <v>45.105846131614008</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.422913237354983</v>
+        <v>57.3665148283132</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.103419833654812</v>
+        <v>67.037513631643819</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.965565933963873</v>
+        <v>78.888009222945911</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.478108237858166</v>
+        <v>83.396119494532442</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.12914390693642</v>
+        <v>45.084819929376302</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.620289876911919</v>
+        <v>58.562715454085954</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.597321188422853</v>
+        <v>69.52896557970665</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.373839908072014</v>
+        <v>83.291953572784848</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.696711914155856</v>
+        <v>88.609597674261423</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>45.043422158616387</v>
+        <v>44.999182373410036</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.240751553147931</v>
+        <v>64.177656945455865</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.330877977604288</v>
+        <v>82.250015996364198</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.83789495970613</v>
+        <v>107.73198104194644</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.46828445071698</v>
+        <v>118.35192980431803</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.983012759520484</v>
+        <v>44.938832305925992</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.295877518253334</v>
+        <v>69.227817975035293</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.515934705585607</v>
+        <v>95.422122907266228</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>136.88861057806739</v>
+        <v>136.75416424963691</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.44304615985669</v>
+        <v>155.29037643263842</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.940441351789701</v>
+        <v>44.896302710070152</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.842532222995743</v>
+        <v>73.770007143681511</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.1685004260909</v>
+        <v>109.06127964270677</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.38592004526973</v>
+        <v>171.21759188708728</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.36379830584266</v>
+        <v>201.16602711621113</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.910440643567085</v>
+        <v>44.866331467301627</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.931860391443337</v>
+        <v>77.855318943231254</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.30515183367672</v>
+        <v>123.18404661629894</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.35098183960844</v>
+        <v>212.14241949299409</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.39501041320347</v>
+        <v>258.14122552717021</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.696711914155856</v>
+        <v>88.609597674261423</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.373839908072014</v>
+        <v>83.291953572784848</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.597321188422853</v>
+        <v>69.52896557970665</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.620289876911919</v>
+        <v>58.562715454085954</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.12914390693642</v>
+        <v>45.084819929376302</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.373839908072014</v>
+        <v>83.291953572784848</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.597321188422853</v>
+        <v>69.52896557970665</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.620289876911919</v>
+        <v>58.562715454085954</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.608367104474951</v>
+        <v>69.540000646917122</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.696711914155856</v>
+        <v>88.609597674261423</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.12914390693642</v>
+        <v>45.084819929376302</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24904630147475521</v>
+        <v>0.2486391565252648</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2843060213283687E-2</v>
+        <v>5.2845225163868831E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.247657666050159</v>
+        <v>71.17768116514172</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.9149098366251</v>
+        <v>50.864903319201957</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.42952101322264</v>
+        <v>32.397670079718573</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.687409042353273</v>
+        <v>32.655558108849206</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.5412142642560307</v>
+        <v>0.54121070573957097</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.231283371556806</v>
+        <v>41.190787711308865</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.530403741927174</v>
+        <v>41.489908081679232</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41709797764037082</v>
+        <v>0.41709385017169764</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.067499110102226</v>
+        <v>51.017342725809293</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.410088753985512</v>
+        <v>51.359932369692579</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27843117320497313</v>
+        <v>0.27842644591735599</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.753550514685415</v>
+        <v>57.696827367392636</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.124507796943981</v>
+        <v>58.067784649651202</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18419061480752963</v>
+        <v>0.18418549608372048</v>
       </c>
     </row>
   </sheetData>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24904630147475521</v>
+        <v>0.2486391565252648</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.247657666050159</v>
+        <v>71.17768116514172</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.687409042353273</v>
+        <v>32.655558108849206</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.530403741927174</v>
+        <v>41.489908081679232</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.410088753985512</v>
+        <v>51.359932369692579</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.124507796943981</v>
+        <v>58.067784649651202</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4020425606441583E-2</v>
+        <v>6.3957547393776598E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11632644568161686</v>
+        <v>-0.11621219466062091</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5674581337006952</v>
+        <v>9.5580613722531496</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1601479178360021</v>
+        <v>6.1540976754773116</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.611279605855081</v>
+        <v>15.595946853069842</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.51075948536047</v>
+        <v>11.499454093745218</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.433807775914772</v>
+        <v>61.373470032240597</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.7 HKD</v>
+        <v>88.61 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.37 HKD</v>
+        <v>83.29 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.6 HKD</v>
+        <v>69.53 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.62 HKD</v>
+        <v>58.56 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.13 HKD</v>
+        <v>45.08 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.247657666050159</v>
+        <v>71.17768116514172</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.42952101322264</v>
+        <v>32.397670079718573</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.687409042353273</v>
+        <v>32.655558108849206</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.231283371556806</v>
+        <v>41.190787711308865</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.530403741927174</v>
+        <v>41.489908081679232</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.067499110102226</v>
+        <v>51.017342725809293</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.410088753985512</v>
+        <v>51.359932369692579</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.753550514685415</v>
+        <v>57.696827367392636</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.124507796943981</v>
+        <v>58.067784649651202</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,15 +21852,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21875,12 +21872,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1698.hk_Valuation.xlsx
+++ b/financial_models/opportunities/1698.hk_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EFD5BA-C598-41F5-A2A0-8D4BAD4F537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD579D2A-63DE-4ED7-8A0D-FBCD8F3F074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>36.840000000000003</v>
+        <v>36.58</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>114528.32933952</v>
+        <v>113720.04037023999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2486391565252648</v>
+        <v>0.28771195315421721</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>71.17768116514172</v>
+        <v>77.548465199945866</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>32.655558108849206</v>
+        <v>35.555323258964883</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>41.489908081679232</v>
+        <v>45.176704398116819</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>51.359932369692579</v>
+        <v>55.92625803829123</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>58.067784649651202</v>
+        <v>63.231960001166449</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
-        <v>-650.63867420757288</v>
+        <v>0</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.3957547393776598E-2</v>
+        <v>6.4485548866475562E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8545059717698146E-3</v>
+        <v>3.8819026790595955E-3</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11621219466062091</v>
+        <v>-0.11634464046165091</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5580613722531496</v>
+        <v>9.5689545930415427</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1540976754773116</v>
+        <v>6.161111435079957</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>15.595946853069842</v>
+        <v>15.613721387659851</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>11.499454093745218</v>
+        <v>11.512559899149734</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.61 HKD</v>
+        <v>96.97 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.8691192485189095E-2</v>
+        <v>-7.0220800135227857E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.29 HKD</v>
+        <v>91.05 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.9244064919553375E-2</v>
+        <v>-5.0440054169133899E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.53 HKD</v>
+        <v>75.71 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.8690326066035779E-3</v>
+        <v>9.8845823437928599E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.56 HKD</v>
+        <v>63.49 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.9463368073310022E-2</v>
+        <v>7.1033031487934856E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.08 HKD</v>
+        <v>48.47 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16713266016268385</v>
+        <v>0.17208956655680616</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>71.17768116514172</v>
+        <v>77.548465199945866</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>32.397670079718573</v>
+        <v>35.29743522983425</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>32.655558108849206</v>
+        <v>35.555323258964883</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>41.190787711308865</v>
+        <v>44.877584027746451</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>41.489908081679232</v>
+        <v>45.176704398116819</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>51.017342725809293</v>
+        <v>55.583668394407944</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>51.359932369692579</v>
+        <v>55.92625803829123</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>57.696827367392636</v>
+        <v>62.861002718907883</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>58.067784649651202</v>
+        <v>63.231960001166449</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7075,7 +7075,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" hidden="1">
       <c r="B9" s="38" t="s">
         <v>133</v>
       </c>
@@ -7091,7 +7091,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" hidden="1">
       <c r="B10" s="38" t="s">
         <v>137</v>
       </c>
@@ -7107,7 +7107,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" hidden="1">
       <c r="B11" s="38" t="s">
         <v>132</v>
       </c>
@@ -7279,79 +7279,49 @@
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" hidden="1">
       <c r="B19" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
-      <c r="E19" s="287">
-        <v>1004</v>
-      </c>
-      <c r="F19" s="287">
-        <v>1160</v>
-      </c>
-      <c r="G19" s="287">
-        <v>1001</v>
-      </c>
-      <c r="H19" s="287">
-        <v>824</v>
-      </c>
-      <c r="I19" s="287">
-        <v>583</v>
-      </c>
+      <c r="E19" s="287"/>
+      <c r="F19" s="287"/>
+      <c r="G19" s="287"/>
+      <c r="H19" s="287"/>
+      <c r="I19" s="287"/>
       <c r="J19" s="287"/>
       <c r="K19" s="287"/>
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" hidden="1">
       <c r="B20" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
-      <c r="E20" s="287">
-        <v>1164</v>
-      </c>
-      <c r="F20" s="287">
-        <v>1053</v>
-      </c>
-      <c r="G20" s="287">
-        <v>2758</v>
-      </c>
-      <c r="H20" s="287">
-        <v>501</v>
-      </c>
-      <c r="I20" s="287">
-        <v>286</v>
-      </c>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="287"/>
+      <c r="I20" s="287"/>
       <c r="J20" s="287"/>
       <c r="K20" s="287"/>
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" hidden="1">
       <c r="B21" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
-      <c r="E21" s="287">
-        <v>-786</v>
-      </c>
-      <c r="F21" s="287">
-        <v>-875</v>
-      </c>
-      <c r="G21" s="287">
-        <v>-579</v>
-      </c>
-      <c r="H21" s="287">
-        <v>505</v>
-      </c>
-      <c r="I21" s="287">
-        <v>-1148</v>
-      </c>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="287"/>
+      <c r="I21" s="287"/>
       <c r="J21" s="287"/>
       <c r="K21" s="287"/>
       <c r="L21" s="287"/>
@@ -8399,7 +8369,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" hidden="1">
       <c r="B55" s="38" t="s">
         <v>133</v>
       </c>
@@ -8448,7 +8418,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" hidden="1">
       <c r="B56" s="38" t="s">
         <v>137</v>
       </c>
@@ -8497,7 +8467,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" hidden="1">
       <c r="B57" s="38" t="s">
         <v>132</v>
       </c>
@@ -8601,7 +8571,7 @@
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" hidden="1">
       <c r="B61" s="26" t="s">
         <v>43</v>
       </c>
@@ -8615,23 +8585,23 @@
       </c>
       <c r="E61" s="270">
         <f t="shared" si="29"/>
-        <v>-1004</v>
+        <v>0</v>
       </c>
       <c r="F61" s="270">
         <f t="shared" si="29"/>
-        <v>-1160</v>
+        <v>0</v>
       </c>
       <c r="G61" s="270">
         <f t="shared" si="29"/>
-        <v>-1001</v>
+        <v>0</v>
       </c>
       <c r="H61" s="270">
         <f t="shared" si="29"/>
-        <v>-824</v>
+        <v>0</v>
       </c>
       <c r="I61" s="270">
         <f t="shared" si="29"/>
-        <v>-583</v>
+        <v>0</v>
       </c>
       <c r="J61" s="270" t="str">
         <f t="shared" si="29"/>
@@ -8650,7 +8620,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" hidden="1">
       <c r="B62" s="26" t="s">
         <v>49</v>
       </c>
@@ -8664,23 +8634,23 @@
       </c>
       <c r="E62" s="270">
         <f t="shared" si="30"/>
-        <v>-1164</v>
+        <v>0</v>
       </c>
       <c r="F62" s="270">
         <f t="shared" si="30"/>
-        <v>-1053</v>
+        <v>0</v>
       </c>
       <c r="G62" s="270">
         <f t="shared" si="30"/>
-        <v>-2758</v>
+        <v>0</v>
       </c>
       <c r="H62" s="270">
         <f t="shared" si="30"/>
-        <v>-501</v>
+        <v>0</v>
       </c>
       <c r="I62" s="270">
         <f t="shared" si="30"/>
-        <v>-286</v>
+        <v>0</v>
       </c>
       <c r="J62" s="270" t="str">
         <f t="shared" si="30"/>
@@ -8699,7 +8669,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" hidden="1">
       <c r="B63" s="26" t="s">
         <v>48</v>
       </c>
@@ -8713,23 +8683,23 @@
       </c>
       <c r="E63" s="270">
         <f t="shared" si="31"/>
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="F63" s="270">
         <f t="shared" si="31"/>
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="G63" s="270">
         <f t="shared" si="31"/>
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="H63" s="270">
         <f t="shared" si="31"/>
-        <v>-505</v>
+        <v>0</v>
       </c>
       <c r="I63" s="270">
         <f t="shared" si="31"/>
-        <v>1148</v>
+        <v>0</v>
       </c>
       <c r="J63" s="270" t="str">
         <f t="shared" si="31"/>
@@ -9198,11 +9168,26 @@
         <f t="shared" si="40"/>
         <v>2800</v>
       </c>
-      <c r="I77" s="291"/>
-      <c r="J77" s="291"/>
-      <c r="K77" s="291"/>
-      <c r="L77" s="291"/>
-      <c r="M77" s="291"/>
+      <c r="I77" s="282">
+        <f t="shared" ref="I77:M77" si="41">IF(I$4="","",I28)</f>
+        <v>2198</v>
+      </c>
+      <c r="J77" s="282" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K77" s="282" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L77" s="282" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M77" s="282" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
@@ -9232,58 +9217,73 @@
         <f t="shared" si="40"/>
         <v>18</v>
       </c>
-      <c r="I78" s="291"/>
-      <c r="J78" s="291"/>
-      <c r="K78" s="291"/>
-      <c r="L78" s="291"/>
-      <c r="M78" s="291"/>
+      <c r="I78" s="282">
+        <f t="shared" ref="I78:M78" si="42">IF(I$4="","",I29)</f>
+        <v>26</v>
+      </c>
+      <c r="J78" s="282" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K78" s="282" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L78" s="282" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M78" s="282" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C79" s="259">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <f t="shared" ref="C79:M79" si="43">IF(C$4="","",C30)</f>
         <v>19472</v>
       </c>
       <c r="D79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>20718</v>
       </c>
       <c r="E79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>18334</v>
       </c>
       <c r="F79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>17882</v>
       </c>
       <c r="G79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>16199</v>
       </c>
       <c r="H79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>15542</v>
       </c>
       <c r="I79" s="270">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>9000</v>
       </c>
       <c r="J79" s="270" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K79" s="270" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="L79" s="270" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M79" s="270" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -9292,53 +9292,53 @@
         <v>27</v>
       </c>
       <c r="C80" s="259">
-        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <f t="shared" ref="C80:M80" si="44">IF(C$4="","",C31)</f>
         <v>83050</v>
       </c>
       <c r="D80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>69726</v>
       </c>
       <c r="E80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>57202</v>
       </c>
       <c r="F80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>49127</v>
       </c>
       <c r="G80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>51055</v>
       </c>
       <c r="H80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>52731</v>
       </c>
       <c r="I80" s="270">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>43678</v>
       </c>
       <c r="J80" s="270" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="K80" s="270" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="L80" s="270" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M80" s="270" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:M80">
     <cfRule type="expression" dxfId="6" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -10163,11 +10163,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>29.526355926320477</v>
+        <v>29.560006799824578</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.499454093745218</v>
+        <v>11.512559899149734</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10573,11 +10573,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-361.28090400000002</v>
+        <v>-361.69265200000001</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.11621219466062091</v>
+        <v>-0.11634464046165091</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>29714.136826513386</v>
+        <v>29748.001711910274</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>9.5580613722531496</v>
+        <v>9.5689545930415445</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10607,11 +10607,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>19131.881796000001</v>
+        <v>19153.686198000003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.1540976754773116</v>
+        <v>6.1611114350799578</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>48484.737718513388</v>
+        <v>48539.995257910276</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>15.59594685306984</v>
+        <v>15.613721387659851</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11401,23 +11401,23 @@
       </c>
       <c r="I15" s="266">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>1004</v>
+        <v>0</v>
       </c>
       <c r="J15" s="266">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="K15" s="266">
         <f>IF(Data!G61="","",-Data!G61)</f>
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L15" s="266">
         <f>IF(Data!H61="","",-Data!H61)</f>
-        <v>824</v>
+        <v>0</v>
       </c>
       <c r="M15" s="266">
         <f>IF(Data!I61="","",-Data!I61)</f>
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="N15" s="266" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
-        <v>-650.63867420757288</v>
+        <v>0</v>
       </c>
       <c r="E16" s="237"/>
       <c r="G16" s="266">
@@ -11456,23 +11456,23 @@
       </c>
       <c r="I16" s="266">
         <f>Data!E62</f>
-        <v>-1164</v>
+        <v>0</v>
       </c>
       <c r="J16" s="266">
         <f>Data!F62</f>
-        <v>-1053</v>
+        <v>0</v>
       </c>
       <c r="K16" s="266">
         <f>Data!G62</f>
-        <v>-2758</v>
+        <v>0</v>
       </c>
       <c r="L16" s="266">
         <f>Data!H62</f>
-        <v>-501</v>
+        <v>0</v>
       </c>
       <c r="M16" s="266">
         <f>Data!I62</f>
-        <v>-286</v>
+        <v>0</v>
       </c>
       <c r="N16" s="266" t="str">
         <f>Data!J62</f>
@@ -13804,23 +13804,23 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" si="33"/>
-        <v>3.6177572787546845E-2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="6">
         <f t="shared" si="33"/>
-        <v>4.0932989872613713E-2</v>
+        <v>0</v>
       </c>
       <c r="K81" s="6">
         <f t="shared" si="33"/>
-        <v>3.2038151325054408E-2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="6">
         <f t="shared" si="33"/>
-        <v>2.826467258944191E-2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="6">
         <f t="shared" si="33"/>
-        <v>2.2922072815915705E-2</v>
+        <v>0</v>
       </c>
       <c r="N81" s="6" t="str">
         <f t="shared" si="33"/>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
-        <v>1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
@@ -13863,23 +13863,23 @@
       </c>
       <c r="I82" s="6">
         <f t="shared" si="34"/>
-        <v>4.1942923032574228E-2</v>
+        <v>0</v>
       </c>
       <c r="J82" s="6">
         <f t="shared" si="34"/>
-        <v>3.7157274427467447E-2</v>
+        <v>0</v>
       </c>
       <c r="K82" s="6">
         <f t="shared" si="34"/>
-        <v>8.8272948406093968E-2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="6">
         <f t="shared" si="34"/>
-        <v>1.7185195348677667E-2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="6">
         <f t="shared" si="34"/>
-        <v>1.1244790437996383E-2</v>
+        <v>0</v>
       </c>
       <c r="N82" s="6" t="str">
         <f t="shared" si="34"/>
@@ -14211,16 +14211,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8545059717698146E-3</v>
+        <v>3.8819026790595955E-3</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8545059717698146E-3</v>
+        <v>3.8819026790595955E-3</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0901194353963081E-3</v>
+        <v>2.1049753963914707E-3</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -14525,11 +14525,11 @@
       </c>
       <c r="L101" s="282">
         <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="282">
+        <v>2198</v>
+      </c>
+      <c r="M101" s="282" t="str">
         <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N101" s="282" t="str">
         <f>IF(N$4="","",Data!K77)</f>
@@ -14582,11 +14582,11 @@
       </c>
       <c r="L102" s="282">
         <f>IF(L$4="","",Data!I78)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="282">
+        <v>26</v>
+      </c>
+      <c r="M102" s="282" t="str">
         <f>IF(M$4="","",Data!J78)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N102" s="282" t="str">
         <f>IF(N$4="","",Data!K78)</f>
@@ -14780,11 +14780,11 @@
       </c>
       <c r="L107" s="91">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="91">
+        <v>7.5395328096593828E-2</v>
+      </c>
+      <c r="M107" s="91" t="e">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="N107" s="91" t="str">
         <f t="shared" si="42"/>
@@ -14837,11 +14837,11 @@
       </c>
       <c r="L108" s="91">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="91">
+        <v>8.9184646520083701E-4</v>
+      </c>
+      <c r="M108" s="91" t="e">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="N108" s="91" t="str">
         <f t="shared" si="43"/>
@@ -15375,38 +15375,38 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3561960459867297</v>
+        <v>2.3588813775356758</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.8178588258478934</v>
+        <v>2.8210703095520673</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.047043832694607</v>
+        <v>2.0493768267573773</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.413885256168679</v>
+        <v>1.4154966461425509</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.96995100848320759</v>
+        <v>0.97105645132122975</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.7947521161538984</v>
+        <v>0.79565788667954496</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1651501298690856</v>
+        <v>1.1664780390676115</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2838558569831879</v>
+        <v>1.2853190538351342</v>
       </c>
       <c r="N123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15432,38 +15432,38 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.3957547393776598E-2</v>
+        <v>6.4485548866475562E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6489110365035098E-2</v>
+        <v>7.7120566144124311E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5565793504196707E-2</v>
+        <v>5.6024516860507856E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8379078614784984E-2</v>
+        <v>3.8695917062398881E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.632874615861041E-2</v>
+        <v>2.6546103097901307E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>2.1573075899942951E-2</v>
+        <v>2.1751172407860717E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>3.1627310799920885E-2</v>
+        <v>3.1888410034653134E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>3.484950751854473E-2</v>
+        <v>3.5137207595274313E-2</v>
       </c>
       <c r="N124" s="74" t="str">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
@@ -15489,31 +15489,31 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9128312317766851E-2</v>
+        <v>9.9832887528336009E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2071978531401797E-2</v>
+        <v>6.2513168099968361E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5578242781532899E-2</v>
+        <v>4.5902199673911209E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3520090811935785E-2</v>
+        <v>3.3758341867460753E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8071657192074381E-2</v>
+        <v>2.8271182366211598E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6462594225226318E-2</v>
+        <v>3.6721759739128973E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4725032862482054E-2</v>
+        <v>3.4971848295621624E-2</v>
       </c>
       <c r="N125" s="22" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>15.595946853069842</v>
+        <v>15.613721387659851</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>190798.07243652584</v>
+        <v>191015.52296839675</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16595,21 +16595,21 @@
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="308" t="s">
         <v>422</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="140" t="s">
         <v>96</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>50.864903319201957</v>
+        <v>54.913930535364223</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16684,19 +16684,19 @@
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>5893.5649559544136</v>
+        <v>6559.7252124670104</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>-8.0119798039642642E-2</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297657</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>5495.1654600973552</v>
+        <v>6116.2939043981442</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16733,11 +16733,11 @@
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>6034.1613532486008</v>
+        <v>6716.2134736476919</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297657</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>5245.9278993255639</v>
+        <v>5838.8845734571687</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16782,11 +16782,11 @@
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>6178.1118065479104</v>
+        <v>6876.4349058216958</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>5007.9947045734207</v>
+        <v>5574.0573613770557</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16839,11 +16839,11 @@
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>6325.4963299345109</v>
+        <v>7040.4785672069384</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796611</v>
+        <v>0.19472625187297651</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>4780.8531574099216</v>
+        <v>5321.2415962395562</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16896,11 +16896,11 @@
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>6476.3968462998864</v>
+        <v>7208.4356405868048</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>4564.0137941526327</v>
+        <v>5079.8924894010815</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16953,11 +16953,11 @@
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>6630.8972328812279</v>
+        <v>7380.3994839936004</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>4357.0093511302275</v>
+        <v>4849.4899615363729</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -17002,11 +17002,11 @@
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>6789.0833678841482</v>
+        <v>7556.4656826011169</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796611</v>
+        <v>0.19472625187297651</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>4159.3937577834995</v>
+        <v>4629.5375219279022</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -17051,11 +17051,11 @@
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>6951.0431782176247</v>
+        <v>7736.7321018551374</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796611</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>3970.7411754350496</v>
+        <v>4419.561198585975</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -17100,11 +17100,11 @@
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>7116.8666883676842</v>
+        <v>7921.298941871406</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796614</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>3790.6450796563408</v>
+        <v>4219.1085168940745</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17149,19 +17149,19 @@
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>7286.646070437032</v>
+        <v>8110.2687931313249</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.17495120250796611</v>
+        <v>0.19472625187297654</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>3618.7173842547172</v>
+        <v>4027.7475245785604</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -18234,11 +18234,11 @@
       </c>
       <c r="G51" s="299">
         <f>F18</f>
-        <v>-1.9775049365010421E-2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>102515.57230132102</v>
+        <v>114103.09198612347</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>50911.610095721546</v>
+        <v>56666.241035450097</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18264,7 +18264,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>95902.071859540272</v>
+        <v>106742.05568384599</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18288,7 +18288,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>95902.071859540272</v>
+        <v>106742.05568384599</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18323,19 +18323,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>80877.062331605935</v>
+        <v>90018.74228108619</v>
       </c>
       <c r="C56" s="118">
-        <v>84920.915448186221</v>
+        <v>94519.679395140483</v>
       </c>
       <c r="D56" s="118">
-        <v>87347.227318134406</v>
+        <v>97220.241663573062</v>
       </c>
       <c r="E56" s="118">
-        <v>89773.539188082563</v>
+        <v>99920.803932005656</v>
       </c>
       <c r="F56" s="118">
-        <v>90582.309811398634</v>
+        <v>100820.99135481651</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18349,19 +18349,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>80776.976034054125</v>
+        <v>89907.343049147676</v>
       </c>
       <c r="C57" s="118">
-        <v>88774.841872968304</v>
+        <v>98809.222061518347</v>
       </c>
       <c r="D57" s="118">
-        <v>93754.545012303643</v>
+        <v>104351.79001110824</v>
       </c>
       <c r="E57" s="118">
-        <v>98869.985878629072</v>
+        <v>110045.43836732373</v>
       </c>
       <c r="F57" s="118">
-        <v>100605.29677340202</v>
+        <v>111976.89457642348</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18375,19 +18375,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>80683.655476896238</v>
+        <v>89803.474301419425</v>
       </c>
       <c r="C58" s="118">
-        <v>92547.916694433254</v>
+        <v>103008.77432230784</v>
       </c>
       <c r="D58" s="118">
-        <v>100206.66912391459</v>
+        <v>111533.20932610867</v>
       </c>
       <c r="E58" s="118">
-        <v>108284.49014576804</v>
+        <v>120524.08099968085</v>
       </c>
       <c r="F58" s="118">
-        <v>111072.19224887405</v>
+        <v>123626.88208989643</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18401,19 +18401,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>80596.643302390061</v>
+        <v>89706.626984190298</v>
       </c>
       <c r="C59" s="118">
-        <v>96241.836100063287</v>
+        <v>107120.22408811576</v>
       </c>
       <c r="D59" s="118">
-        <v>106703.9129845578</v>
+        <v>118764.84835659864</v>
       </c>
       <c r="E59" s="118">
-        <v>118028.17288378603</v>
+        <v>131369.10973806449</v>
       </c>
       <c r="F59" s="118">
-        <v>122002.65652162806</v>
+        <v>135792.83641632041</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18427,19 +18427,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>80515.513069750275</v>
+        <v>89616.326455305345</v>
       </c>
       <c r="C60" s="118">
-        <v>99858.260692987795</v>
+        <v>111145.4196630326</v>
       </c>
       <c r="D60" s="118">
-        <v>113246.59211695376</v>
+        <v>126047.05828939972</v>
       </c>
       <c r="E60" s="118">
-        <v>128112.54382942703</v>
+        <v>142593.33528548246</v>
       </c>
       <c r="F60" s="118">
-        <v>133417.22061065788</v>
+        <v>148497.60923272587</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18453,19 +18453,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>80439.867165191026</v>
+        <v>89532.130157976702</v>
       </c>
       <c r="C61" s="118">
-        <v>103398.8162385083</v>
+        <v>115086.17057553861</v>
       </c>
       <c r="D61" s="118">
-        <v>119835.02425027557</v>
+        <v>133380.19276718539</v>
       </c>
       <c r="E61" s="118">
-        <v>138549.51515778276</v>
+        <v>154210.0162716214</v>
       </c>
       <c r="F61" s="118">
-        <v>145337.32483416691</v>
+        <v>161765.06429507938</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18479,19 +18479,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>80369.334853247667</v>
+        <v>89453.625451842789</v>
       </c>
       <c r="C62" s="118">
-        <v>106865.09439496195</v>
+        <v>118944.24839197805</v>
       </c>
       <c r="D62" s="118">
-        <v>126469.52933557864</v>
+        <v>140764.60790565494</v>
       </c>
       <c r="E62" s="118">
-        <v>149351.41555356351</v>
+        <v>166232.87491461833</v>
       </c>
       <c r="F62" s="118">
-        <v>157785.35908156098</v>
+        <v>175620.1222622924</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18505,19 +18505,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>80303.570459827286</v>
+        <v>89380.427590645646</v>
       </c>
       <c r="C63" s="118">
-        <v>110258.65342925221</v>
+        <v>122721.38751296769</v>
       </c>
       <c r="D63" s="118">
-        <v>133150.42956133839</v>
+        <v>148200.662310827</v>
       </c>
       <c r="E63" s="118">
-        <v>160531.00477437157</v>
+        <v>178676.11323044734</v>
       </c>
       <c r="F63" s="118">
-        <v>170784.70486904934</v>
+        <v>190088.80750544253</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18531,19 +18531,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>80242.251678083339</v>
+        <v>89312.17783661568</v>
       </c>
       <c r="C64" s="118">
-        <v>113581.01891736855</v>
+        <v>126419.28595309739</v>
       </c>
       <c r="D64" s="118">
-        <v>139878.04936909641</v>
+        <v>155688.71709645487</v>
       </c>
       <c r="E64" s="118">
-        <v>172101.48872317988</v>
+        <v>191554.42980906754</v>
       </c>
       <c r="F64" s="118">
-        <v>184359.77925784842</v>
+        <v>205198.2969901308</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18557,19 +18557,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>80185.077988811594</v>
+        <v>89248.541702322007</v>
       </c>
       <c r="C65" s="118">
-        <v>116833.68443020975</v>
+        <v>130039.60610427341</v>
       </c>
       <c r="D65" s="118">
-        <v>146652.7154692164</v>
+        <v>163229.13590156258</v>
       </c>
       <c r="E65" s="118">
-        <v>184076.53504782065</v>
+        <v>204883.03717714999</v>
       </c>
       <c r="F65" s="118">
-        <v>198536.08071748007</v>
+        <v>220976.97132379125</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18583,19 +18583,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>79952.215441431166</v>
+        <v>88989.35828201416</v>
       </c>
       <c r="C66" s="277">
-        <v>132101.63041861926</v>
+        <v>147033.31551296788</v>
       </c>
       <c r="D66" s="118">
-        <v>181243.33604396001</v>
+        <v>201729.5965895844</v>
       </c>
       <c r="E66" s="118">
-        <v>250532.97451881587</v>
+        <v>278851.16763581889</v>
       </c>
       <c r="F66" s="118">
-        <v>279410.35540564789</v>
+        <v>310992.6108690832</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18618,19 +18618,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>79788.113718882625</v>
+        <v>88806.70784635155</v>
       </c>
       <c r="C67" s="277">
-        <v>145833.84578558247</v>
+        <v>162317.7079034659</v>
       </c>
       <c r="D67" s="118">
-        <v>217060.45313739951</v>
+        <v>241595.18690573791</v>
       </c>
       <c r="E67" s="118">
-        <v>329449.0462823055</v>
+        <v>366687.26505471749</v>
       </c>
       <c r="F67" s="118">
-        <v>379852.0445815305</v>
+        <v>422787.40498671471</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18653,19 +18653,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>79672.468778782364</v>
+        <v>88677.991350488795</v>
       </c>
       <c r="C68" s="277">
-        <v>158184.80242557934</v>
+        <v>176064.71540655941</v>
       </c>
       <c r="D68" s="118">
-        <v>254147.55523529719</v>
+        <v>282874.31091761874</v>
       </c>
       <c r="E68" s="118">
-        <v>423160.75326140609</v>
+        <v>470991.37497261306</v>
       </c>
       <c r="F68" s="118">
-        <v>504595.45604832424</v>
+        <v>561630.78881353443</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18688,19 +18688,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>79590.972058558531</v>
+        <v>88587.282909268411</v>
       </c>
       <c r="C69" s="277">
-        <v>169293.43463433982</v>
+        <v>188428.97631153293</v>
       </c>
       <c r="D69" s="118">
-        <v>292549.6728158833</v>
+        <v>325617.08897947508</v>
       </c>
       <c r="E69" s="118">
-        <v>534442.06553016673</v>
+        <v>594851.01429469965</v>
       </c>
       <c r="F69" s="118">
-        <v>659520.35657568579</v>
+        <v>734067.12974187545</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18797,23 +18797,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18828,23 +18828,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>45.339304167183009</v>
+        <v>48.756753683555374</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>46.826472032888653</v>
+        <v>50.413905298350151</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>47.718772752312056</v>
+        <v>51.408196267227012</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>48.611073471735445</v>
+        <v>52.402487236103887</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>48.908507044876586</v>
+        <v>52.733917559062832</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18859,23 +18859,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>45.302496419417338</v>
+        <v>48.715738798784528</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>48.243792437586407</v>
+        <v>51.993225865643332</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>50.075128610309633</v>
+        <v>54.033884331875306</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>51.956383704399215</v>
+        <v>56.130167467694804</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>52.594561829399382</v>
+        <v>56.841289550654082</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18890,23 +18890,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>45.268176841081036</v>
+        <v>48.677496481981841</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>49.631378847779992</v>
+        <v>53.53941383362266</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>52.447962481300195</v>
+        <v>56.677933851521132</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>55.41866282631694</v>
+        <v>59.988186168921757</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>56.443868457525738</v>
+        <v>61.130573122292482</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18921,23 +18921,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>45.236177234240671</v>
+        <v>48.641839310137868</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>50.989855053563922</v>
+        <v>55.053164291784235</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>54.837389596143851</v>
+        <v>59.340473227947705</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>59.002000658791246</v>
+        <v>63.981100628932886</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>60.463657197387278</v>
+        <v>65.609824964003465</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>45.206340770986259</v>
+        <v>48.608592529863763</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>52.319831758527201</v>
+        <v>56.535157747327048</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>57.243525991510886</v>
+        <v>62.021631760852785</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>62.710630023869527</v>
+        <v>68.113627482650671</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>64.661478538781168</v>
+        <v>70.287458588913736</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18983,23 +18983,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>45.178521224828287</v>
+        <v>48.577593200936853</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>53.62190685429546</v>
+        <v>57.986060431075259</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>59.666488515516846</v>
+        <v>64.721539654127824</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>66.548931744370151</v>
+        <v>72.390648282302664</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>69.045217375481542</v>
+        <v>75.172260136605615</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19015,23 +19015,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>45.152582254051623</v>
+        <v>48.548689397741612</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>54.896665689313352</v>
+        <v>59.406524596982599</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>62.106394833396962</v>
+        <v>67.440328022181035</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>70.521439818734436</v>
+        <v>76.817215263760673</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>73.623107815672157</v>
+        <v>80.27340487638638</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>45.128396733513945</v>
+        <v>48.521739464692416</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>56.144681331988188</v>
+        <v>60.797188815353408</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>64.563363433220331</v>
+        <v>70.178128896304486</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>74.632846776817743</v>
+        <v>81.398557314500437</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>78.403748648318739</v>
+        <v>85.60047444147213</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>45.105846131614008</v>
+        <v>48.496611321989207</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>57.3665148283132</v>
+        <v>62.158678259912243</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>67.037513631643819</v>
+        <v>72.935075231086202</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.888009222945911</v>
+        <v>86.140086150231085</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>83.396119494532442</v>
+        <v>91.163474826456792</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19110,23 +19110,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>45.084819929376302</v>
+        <v>48.473181818303246</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>58.562715454085954</v>
+        <v>63.49160498885098</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>69.52896557970665</v>
+        <v>75.711300910866356</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>83.291953572784848</v>
+        <v>91.047402707490775</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>88.609597674261423</v>
+        <v>96.972855181872006</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19142,23 +19142,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.999182373410036</v>
+        <v>48.37775586308382</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.177656945455865</v>
+        <v>69.748336037155838</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>82.250015996364198</v>
+        <v>89.886371342372115</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>107.73198104194644</v>
+        <v>118.28093290949815</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>118.35192980431803</v>
+        <v>130.1147451148548</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19174,23 +19174,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>44.938832305925992</v>
+        <v>48.310507764136581</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.227817975035293</v>
+        <v>75.375732041419383</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>95.422122907266228</v>
+        <v>104.56405416555044</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>136.75416424963691</v>
+        <v>150.62036067454972</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.29037643263842</v>
+        <v>171.27526766896909</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>44.896302710070152</v>
+        <v>48.263117022261149</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>73.770007143681511</v>
+        <v>80.437094843226461</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>109.06127964270677</v>
+        <v>119.76217075331684</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>171.21759188708728</v>
+        <v>189.02296879818925</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>201.16602711621113</v>
+        <v>222.39451947849548</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19238,23 +19238,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>44.866331467301627</v>
+        <v>48.229720057132589</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>77.855318943231254</v>
+        <v>84.989359050704891</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>123.18404661629894</v>
+        <v>135.49917437970549</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.14241949299409</v>
+        <v>234.62551691413202</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>258.14122552717021</v>
+        <v>285.88200076909834</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>88.609597674261423</v>
+        <v>96.972855181872006</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>83.291953572784848</v>
+        <v>91.047402707490775</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>69.52896557970665</v>
+        <v>75.711300910866356</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>58.562715454085954</v>
+        <v>63.49160498885098</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>45.084819929376302</v>
+        <v>48.473181818303246</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>83.291953572784848</v>
+        <v>91.047402707490775</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>69.52896557970665</v>
+        <v>75.711300910866356</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>58.562715454085954</v>
+        <v>63.49160498885098</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>69.540000646917122</v>
+        <v>75.723597289687405</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>88.609597674261423</v>
+        <v>96.972855181872006</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>45.084819929376302</v>
+        <v>48.473181818303246</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>36.840000000000003</v>
+        <v>36.58</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2486391565252648</v>
+        <v>0.28771195315421721</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.2845225163868831E-2</v>
+        <v>8.2828432574639149E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>71.17768116514172</v>
+        <v>77.548465199945866</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>50.864903319201957</v>
+        <v>54.913930535364223</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.21911288198452492</v>
+        <v>0.20134146236682388</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20239,11 +20239,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>32.397670079718573</v>
+        <v>35.29743522983425</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>32.655558108849206</v>
+        <v>35.555323258964883</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54121070573957097</v>
+        <v>0.54150835651883789</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>41.190787711308865</v>
+        <v>44.877584027746451</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>41.489908081679232</v>
+        <v>45.176704398116819</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41709385017169764</v>
+        <v>0.417439090746204</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>51.017342725809293</v>
+        <v>55.583668394407944</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>51.359932369692579</v>
+        <v>55.92625803829123</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.27842644591735599</v>
+        <v>0.27882185812324412</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20335,11 +20335,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>57.696827367392636</v>
+        <v>62.861002718907883</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>58.067784649651202</v>
+        <v>63.231960001166449</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.18418549608372048</v>
+        <v>0.18461364982358686</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>36.840000000000003</v>
+        <v>36.58</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20476,14 +20476,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>114528.32933952</v>
+        <v>113720.04037023999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2486391565252648</v>
+        <v>0.28771195315421721</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20491,13 +20491,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>71.17768116514172</v>
+        <v>77.548465199945866</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>32.655558108849206</v>
+        <v>35.555323258964883</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>41.489908081679232</v>
+        <v>45.176704398116819</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>51.359932369692579</v>
+        <v>55.92625803829123</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>58.067784649651202</v>
+        <v>63.231960001166449</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20682,22 +20682,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
-        <v>-650.63867420757288</v>
+        <v>0</v>
       </c>
       <c r="D38" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20887,10 +20887,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20906,22 +20906,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.3957547393776598E-2</v>
+        <v>6.4485548866475562E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8545059717698146E-3</v>
+        <v>3.8819026790595955E-3</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -21056,22 +21056,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21079,13 +21079,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.11621219466062091</v>
+        <v>-0.11634464046165091</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.5580613722531496</v>
+        <v>9.5689545930415427</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1540976754773116</v>
+        <v>6.161111435079957</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>15.595946853069842</v>
+        <v>15.613721387659851</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21234,33 +21234,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21323,23 +21323,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>11.499454093745218</v>
+        <v>11.512559899149734</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>61.373470032240597</v>
+        <v>61.443416722638709</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21383,13 +21383,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>88.61 HKD</v>
+        <v>96.97 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>83.29 HKD</v>
+        <v>91.05 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>69.53 HKD</v>
+        <v>75.71 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>58.56 HKD</v>
+        <v>63.49 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>45.08 HKD</v>
+        <v>48.47 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>71.17768116514172</v>
+        <v>77.548465199945866</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21572,22 +21572,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21652,11 +21652,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>32.397670079718573</v>
+        <v>35.29743522983425</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>32.655558108849206</v>
+        <v>35.555323258964883</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21673,11 +21673,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>41.190787711308865</v>
+        <v>44.877584027746451</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>41.489908081679232</v>
+        <v>45.176704398116819</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21713,11 +21713,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>51.017342725809293</v>
+        <v>55.583668394407944</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>51.359932369692579</v>
+        <v>55.92625803829123</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21734,11 +21734,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>57.696827367392636</v>
+        <v>62.861002718907883</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>58.067784649651202</v>
+        <v>63.231960001166449</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21756,13 +21756,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21770,13 +21770,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21813,22 +21813,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21852,12 +21852,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21872,15 +21875,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
